--- a/Excel/GiftPackEquipConfig.xlsx
+++ b/Excel/GiftPackEquipConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="34">
   <si>
     <t>#</t>
   </si>
@@ -93,6 +93,42 @@
   </si>
   <si>
     <t>攻击套-4幸运 道术加 攻击的 2项链</t>
+  </si>
+  <si>
+    <t>2004,2004,2001,2003,2003,2003</t>
+  </si>
+  <si>
+    <t>金色战士平衡套</t>
+  </si>
+  <si>
+    <t>2005,2005,2001,2003,2003,2003</t>
+  </si>
+  <si>
+    <t>金色法师平衡套</t>
+  </si>
+  <si>
+    <t>2006,2006,2001,2003,2003,2003</t>
+  </si>
+  <si>
+    <t>金色道士平衡套</t>
+  </si>
+  <si>
+    <t>2002,2002,2011,2003,2003,2003</t>
+  </si>
+  <si>
+    <t>金色战士防御套</t>
+  </si>
+  <si>
+    <t>2005,2005,2001,2011,34,34</t>
+  </si>
+  <si>
+    <t>金色法师攻击套</t>
+  </si>
+  <si>
+    <t>2006,2006,2001,2011,2003,2003</t>
+  </si>
+  <si>
+    <t>金色道士攻击套</t>
   </si>
 </sst>
 </file>
@@ -1069,7 +1105,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I56"/>
+  <dimension ref="A1:I107"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
@@ -2317,6 +2353,1110 @@
         <v>21</v>
       </c>
     </row>
+    <row r="59" customHeight="1" spans="3:9">
+      <c r="C59" s="1">
+        <v>101</v>
+      </c>
+      <c r="D59" s="3">
+        <v>21205801</v>
+      </c>
+      <c r="E59" s="6">
+        <v>11002</v>
+      </c>
+      <c r="F59" s="6">
+        <v>11002</v>
+      </c>
+      <c r="G59" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="H59" s="3">
+        <v>6</v>
+      </c>
+      <c r="I59" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="60" customHeight="1" spans="3:9">
+      <c r="C60" s="1">
+        <v>102</v>
+      </c>
+      <c r="D60" s="3">
+        <v>21205802</v>
+      </c>
+      <c r="E60" s="6">
+        <v>11002</v>
+      </c>
+      <c r="F60" s="6">
+        <v>11002</v>
+      </c>
+      <c r="G60" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="H60" s="3">
+        <v>6</v>
+      </c>
+      <c r="I60" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="61" customHeight="1" spans="3:9">
+      <c r="C61" s="1">
+        <v>103</v>
+      </c>
+      <c r="D61" s="3">
+        <v>21205803</v>
+      </c>
+      <c r="E61" s="6">
+        <v>11005</v>
+      </c>
+      <c r="F61" s="6">
+        <v>11005</v>
+      </c>
+      <c r="G61" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="H61" s="3">
+        <v>6</v>
+      </c>
+      <c r="I61" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="62" customHeight="1" spans="3:9">
+      <c r="C62" s="1">
+        <v>104</v>
+      </c>
+      <c r="D62" s="3">
+        <v>21205804</v>
+      </c>
+      <c r="E62" s="6">
+        <v>11005</v>
+      </c>
+      <c r="F62" s="6">
+        <v>11005</v>
+      </c>
+      <c r="G62" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="H62" s="3">
+        <v>6</v>
+      </c>
+      <c r="I62" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="63" customHeight="1" spans="3:9">
+      <c r="C63" s="1">
+        <v>105</v>
+      </c>
+      <c r="D63" s="3">
+        <v>21205805</v>
+      </c>
+      <c r="E63" s="6">
+        <v>11006</v>
+      </c>
+      <c r="F63" s="6">
+        <v>11006</v>
+      </c>
+      <c r="G63" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="H63" s="3">
+        <v>6</v>
+      </c>
+      <c r="I63" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="64" customHeight="1" spans="3:9">
+      <c r="C64" s="1">
+        <v>106</v>
+      </c>
+      <c r="D64" s="3">
+        <v>21205807</v>
+      </c>
+      <c r="E64" s="6">
+        <v>11008</v>
+      </c>
+      <c r="F64" s="6">
+        <v>11008</v>
+      </c>
+      <c r="G64" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="H64" s="3">
+        <v>6</v>
+      </c>
+      <c r="I64" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="65" customHeight="1" spans="3:9">
+      <c r="C65" s="1">
+        <v>107</v>
+      </c>
+      <c r="D65" s="3">
+        <v>21205809</v>
+      </c>
+      <c r="E65" s="6">
+        <v>11010</v>
+      </c>
+      <c r="F65" s="6">
+        <v>11010</v>
+      </c>
+      <c r="G65" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="H65" s="3">
+        <v>6</v>
+      </c>
+      <c r="I65" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="66" customHeight="1" spans="3:9">
+      <c r="C66" s="1">
+        <v>108</v>
+      </c>
+      <c r="D66" s="3">
+        <v>21205810</v>
+      </c>
+      <c r="E66" s="6">
+        <v>11010</v>
+      </c>
+      <c r="F66" s="6">
+        <v>11010</v>
+      </c>
+      <c r="G66" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="H66" s="3">
+        <v>6</v>
+      </c>
+      <c r="I66" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="67" customHeight="1" spans="3:9">
+      <c r="C67" s="1">
+        <v>109</v>
+      </c>
+      <c r="D67" s="3">
+        <v>22205801</v>
+      </c>
+      <c r="E67" s="6">
+        <v>12002</v>
+      </c>
+      <c r="F67" s="6">
+        <v>12002</v>
+      </c>
+      <c r="G67" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H67" s="3">
+        <v>6</v>
+      </c>
+      <c r="I67" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="68" customHeight="1" spans="3:9">
+      <c r="C68" s="1">
+        <v>110</v>
+      </c>
+      <c r="D68" s="3">
+        <v>22205802</v>
+      </c>
+      <c r="E68" s="6">
+        <v>12002</v>
+      </c>
+      <c r="F68" s="6">
+        <v>12002</v>
+      </c>
+      <c r="G68" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H68" s="3">
+        <v>6</v>
+      </c>
+      <c r="I68" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="69" customHeight="1" spans="3:9">
+      <c r="C69" s="1">
+        <v>111</v>
+      </c>
+      <c r="D69" s="3">
+        <v>22205803</v>
+      </c>
+      <c r="E69" s="6">
+        <v>12005</v>
+      </c>
+      <c r="F69" s="6">
+        <v>12005</v>
+      </c>
+      <c r="G69" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H69" s="3">
+        <v>6</v>
+      </c>
+      <c r="I69" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="70" customHeight="1" spans="3:9">
+      <c r="C70" s="1">
+        <v>112</v>
+      </c>
+      <c r="D70" s="3">
+        <v>22205804</v>
+      </c>
+      <c r="E70" s="6">
+        <v>12005</v>
+      </c>
+      <c r="F70" s="6">
+        <v>12005</v>
+      </c>
+      <c r="G70" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H70" s="3">
+        <v>6</v>
+      </c>
+      <c r="I70" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="71" customHeight="1" spans="3:9">
+      <c r="C71" s="1">
+        <v>113</v>
+      </c>
+      <c r="D71" s="3">
+        <v>22205805</v>
+      </c>
+      <c r="E71" s="6">
+        <v>12006</v>
+      </c>
+      <c r="F71" s="6">
+        <v>12006</v>
+      </c>
+      <c r="G71" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H71" s="3">
+        <v>6</v>
+      </c>
+      <c r="I71" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="72" customHeight="1" spans="3:9">
+      <c r="C72" s="1">
+        <v>114</v>
+      </c>
+      <c r="D72" s="3">
+        <v>22205807</v>
+      </c>
+      <c r="E72" s="6">
+        <v>12008</v>
+      </c>
+      <c r="F72" s="6">
+        <v>12008</v>
+      </c>
+      <c r="G72" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H72" s="3">
+        <v>6</v>
+      </c>
+      <c r="I72" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="73" customHeight="1" spans="3:9">
+      <c r="C73" s="1">
+        <v>115</v>
+      </c>
+      <c r="D73" s="3">
+        <v>22205809</v>
+      </c>
+      <c r="E73" s="6">
+        <v>12010</v>
+      </c>
+      <c r="F73" s="6">
+        <v>12110</v>
+      </c>
+      <c r="G73" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H73" s="3">
+        <v>6</v>
+      </c>
+      <c r="I73" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="74" customHeight="1" spans="3:9">
+      <c r="C74" s="1">
+        <v>116</v>
+      </c>
+      <c r="D74" s="3">
+        <v>22205810</v>
+      </c>
+      <c r="E74" s="6">
+        <v>12010</v>
+      </c>
+      <c r="F74" s="6">
+        <v>12110</v>
+      </c>
+      <c r="G74" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H74" s="3">
+        <v>6</v>
+      </c>
+      <c r="I74" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="75" customHeight="1" spans="3:9">
+      <c r="C75" s="1">
+        <v>117</v>
+      </c>
+      <c r="D75" s="3">
+        <v>23205801</v>
+      </c>
+      <c r="E75" s="6">
+        <v>13002</v>
+      </c>
+      <c r="F75" s="6">
+        <v>13002</v>
+      </c>
+      <c r="G75" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="H75" s="3">
+        <v>6</v>
+      </c>
+      <c r="I75" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="76" customHeight="1" spans="3:9">
+      <c r="C76" s="1">
+        <v>118</v>
+      </c>
+      <c r="D76" s="3">
+        <v>23205802</v>
+      </c>
+      <c r="E76" s="6">
+        <v>13002</v>
+      </c>
+      <c r="F76" s="6">
+        <v>13002</v>
+      </c>
+      <c r="G76" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="H76" s="3">
+        <v>6</v>
+      </c>
+      <c r="I76" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="77" customHeight="1" spans="3:9">
+      <c r="C77" s="1">
+        <v>119</v>
+      </c>
+      <c r="D77" s="3">
+        <v>23205803</v>
+      </c>
+      <c r="E77" s="6">
+        <v>13005</v>
+      </c>
+      <c r="F77" s="6">
+        <v>13005</v>
+      </c>
+      <c r="G77" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="H77" s="3">
+        <v>6</v>
+      </c>
+      <c r="I77" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="78" customHeight="1" spans="3:9">
+      <c r="C78" s="1">
+        <v>120</v>
+      </c>
+      <c r="D78" s="3">
+        <v>23205804</v>
+      </c>
+      <c r="E78" s="6">
+        <v>13005</v>
+      </c>
+      <c r="F78" s="6">
+        <v>13005</v>
+      </c>
+      <c r="G78" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="H78" s="3">
+        <v>6</v>
+      </c>
+      <c r="I78" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="79" customHeight="1" spans="3:9">
+      <c r="C79" s="1">
+        <v>121</v>
+      </c>
+      <c r="D79" s="3">
+        <v>23205805</v>
+      </c>
+      <c r="E79" s="6">
+        <v>13008</v>
+      </c>
+      <c r="F79" s="6">
+        <v>13008</v>
+      </c>
+      <c r="G79" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="H79" s="3">
+        <v>6</v>
+      </c>
+      <c r="I79" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="80" customHeight="1" spans="3:9">
+      <c r="C80" s="1">
+        <v>122</v>
+      </c>
+      <c r="D80" s="3">
+        <v>23205807</v>
+      </c>
+      <c r="E80" s="6">
+        <v>13009</v>
+      </c>
+      <c r="F80" s="6">
+        <v>13009</v>
+      </c>
+      <c r="G80" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="H80" s="3">
+        <v>6</v>
+      </c>
+      <c r="I80" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="81" customHeight="1" spans="3:9">
+      <c r="C81" s="1">
+        <v>123</v>
+      </c>
+      <c r="D81" s="3">
+        <v>23205809</v>
+      </c>
+      <c r="E81" s="6">
+        <v>13010</v>
+      </c>
+      <c r="F81" s="6">
+        <v>13010</v>
+      </c>
+      <c r="G81" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="H81" s="3">
+        <v>6</v>
+      </c>
+      <c r="I81" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="82" customHeight="1" spans="3:9">
+      <c r="C82" s="1">
+        <v>124</v>
+      </c>
+      <c r="D82" s="3">
+        <v>23205810</v>
+      </c>
+      <c r="E82" s="6">
+        <v>13010</v>
+      </c>
+      <c r="F82" s="6">
+        <v>13010</v>
+      </c>
+      <c r="G82" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="H82" s="3">
+        <v>6</v>
+      </c>
+      <c r="I82" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="84" customHeight="1" spans="3:9">
+      <c r="C84" s="1">
+        <v>125</v>
+      </c>
+      <c r="D84" s="3">
+        <v>21205801</v>
+      </c>
+      <c r="E84" s="6">
+        <v>11002</v>
+      </c>
+      <c r="F84" s="6">
+        <v>11002</v>
+      </c>
+      <c r="G84" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H84" s="3">
+        <v>6</v>
+      </c>
+      <c r="I84" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="85" customHeight="1" spans="3:9">
+      <c r="C85" s="1">
+        <v>126</v>
+      </c>
+      <c r="D85" s="3">
+        <v>21205802</v>
+      </c>
+      <c r="E85" s="6">
+        <v>11002</v>
+      </c>
+      <c r="F85" s="6">
+        <v>11002</v>
+      </c>
+      <c r="G85" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H85" s="3">
+        <v>6</v>
+      </c>
+      <c r="I85" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="86" customHeight="1" spans="3:9">
+      <c r="C86" s="1">
+        <v>127</v>
+      </c>
+      <c r="D86" s="3">
+        <v>21205803</v>
+      </c>
+      <c r="E86" s="6">
+        <v>11005</v>
+      </c>
+      <c r="F86" s="6">
+        <v>11005</v>
+      </c>
+      <c r="G86" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H86" s="3">
+        <v>6</v>
+      </c>
+      <c r="I86" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="87" customHeight="1" spans="3:9">
+      <c r="C87" s="1">
+        <v>128</v>
+      </c>
+      <c r="D87" s="3">
+        <v>21205804</v>
+      </c>
+      <c r="E87" s="6">
+        <v>11005</v>
+      </c>
+      <c r="F87" s="6">
+        <v>11005</v>
+      </c>
+      <c r="G87" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H87" s="3">
+        <v>6</v>
+      </c>
+      <c r="I87" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="88" customHeight="1" spans="3:9">
+      <c r="C88" s="1">
+        <v>129</v>
+      </c>
+      <c r="D88" s="3">
+        <v>21205805</v>
+      </c>
+      <c r="E88" s="6">
+        <v>11006</v>
+      </c>
+      <c r="F88" s="6">
+        <v>11006</v>
+      </c>
+      <c r="G88" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H88" s="3">
+        <v>6</v>
+      </c>
+      <c r="I88" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="89" customHeight="1" spans="3:9">
+      <c r="C89" s="1">
+        <v>130</v>
+      </c>
+      <c r="D89" s="3">
+        <v>21205807</v>
+      </c>
+      <c r="E89" s="6">
+        <v>11008</v>
+      </c>
+      <c r="F89" s="6">
+        <v>11008</v>
+      </c>
+      <c r="G89" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H89" s="3">
+        <v>6</v>
+      </c>
+      <c r="I89" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="90" customHeight="1" spans="3:9">
+      <c r="C90" s="1">
+        <v>131</v>
+      </c>
+      <c r="D90" s="3">
+        <v>21205809</v>
+      </c>
+      <c r="E90" s="6">
+        <v>11010</v>
+      </c>
+      <c r="F90" s="6">
+        <v>11010</v>
+      </c>
+      <c r="G90" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H90" s="3">
+        <v>6</v>
+      </c>
+      <c r="I90" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="91" customHeight="1" spans="3:9">
+      <c r="C91" s="1">
+        <v>132</v>
+      </c>
+      <c r="D91" s="3">
+        <v>21205810</v>
+      </c>
+      <c r="E91" s="6">
+        <v>11010</v>
+      </c>
+      <c r="F91" s="6">
+        <v>11010</v>
+      </c>
+      <c r="G91" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H91" s="3">
+        <v>6</v>
+      </c>
+      <c r="I91" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="92" customHeight="1" spans="3:9">
+      <c r="C92" s="1">
+        <v>133</v>
+      </c>
+      <c r="D92" s="3">
+        <v>22205801</v>
+      </c>
+      <c r="E92" s="6">
+        <v>12002</v>
+      </c>
+      <c r="F92" s="6">
+        <v>12002</v>
+      </c>
+      <c r="G92" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="H92" s="3">
+        <v>6</v>
+      </c>
+      <c r="I92" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="93" customHeight="1" spans="3:9">
+      <c r="C93" s="1">
+        <v>134</v>
+      </c>
+      <c r="D93" s="3">
+        <v>22205802</v>
+      </c>
+      <c r="E93" s="6">
+        <v>12002</v>
+      </c>
+      <c r="F93" s="6">
+        <v>12002</v>
+      </c>
+      <c r="G93" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="H93" s="3">
+        <v>6</v>
+      </c>
+      <c r="I93" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="94" customHeight="1" spans="3:9">
+      <c r="C94" s="1">
+        <v>135</v>
+      </c>
+      <c r="D94" s="3">
+        <v>22205803</v>
+      </c>
+      <c r="E94" s="6">
+        <v>12005</v>
+      </c>
+      <c r="F94" s="6">
+        <v>12005</v>
+      </c>
+      <c r="G94" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="H94" s="3">
+        <v>6</v>
+      </c>
+      <c r="I94" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="95" customHeight="1" spans="3:9">
+      <c r="C95" s="1">
+        <v>136</v>
+      </c>
+      <c r="D95" s="3">
+        <v>22205804</v>
+      </c>
+      <c r="E95" s="6">
+        <v>12005</v>
+      </c>
+      <c r="F95" s="6">
+        <v>12005</v>
+      </c>
+      <c r="G95" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="H95" s="3">
+        <v>6</v>
+      </c>
+      <c r="I95" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="96" customHeight="1" spans="3:9">
+      <c r="C96" s="1">
+        <v>137</v>
+      </c>
+      <c r="D96" s="3">
+        <v>22205805</v>
+      </c>
+      <c r="E96" s="6">
+        <v>12006</v>
+      </c>
+      <c r="F96" s="6">
+        <v>12006</v>
+      </c>
+      <c r="G96" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="H96" s="3">
+        <v>6</v>
+      </c>
+      <c r="I96" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="97" customHeight="1" spans="3:9">
+      <c r="C97" s="1">
+        <v>138</v>
+      </c>
+      <c r="D97" s="3">
+        <v>22205807</v>
+      </c>
+      <c r="E97" s="6">
+        <v>12008</v>
+      </c>
+      <c r="F97" s="6">
+        <v>12008</v>
+      </c>
+      <c r="G97" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="H97" s="3">
+        <v>6</v>
+      </c>
+      <c r="I97" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="98" customHeight="1" spans="3:9">
+      <c r="C98" s="1">
+        <v>139</v>
+      </c>
+      <c r="D98" s="3">
+        <v>22205809</v>
+      </c>
+      <c r="E98" s="6">
+        <v>12010</v>
+      </c>
+      <c r="F98" s="6">
+        <v>12110</v>
+      </c>
+      <c r="G98" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="H98" s="3">
+        <v>6</v>
+      </c>
+      <c r="I98" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="99" customHeight="1" spans="3:9">
+      <c r="C99" s="1">
+        <v>140</v>
+      </c>
+      <c r="D99" s="3">
+        <v>22205810</v>
+      </c>
+      <c r="E99" s="6">
+        <v>12010</v>
+      </c>
+      <c r="F99" s="6">
+        <v>12110</v>
+      </c>
+      <c r="G99" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="H99" s="3">
+        <v>6</v>
+      </c>
+      <c r="I99" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="100" customHeight="1" spans="3:9">
+      <c r="C100" s="1">
+        <v>141</v>
+      </c>
+      <c r="D100" s="3">
+        <v>23205801</v>
+      </c>
+      <c r="E100" s="6">
+        <v>13002</v>
+      </c>
+      <c r="F100" s="6">
+        <v>13002</v>
+      </c>
+      <c r="G100" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="H100" s="3">
+        <v>6</v>
+      </c>
+      <c r="I100" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="101" customHeight="1" spans="3:9">
+      <c r="C101" s="1">
+        <v>142</v>
+      </c>
+      <c r="D101" s="3">
+        <v>23205802</v>
+      </c>
+      <c r="E101" s="6">
+        <v>13002</v>
+      </c>
+      <c r="F101" s="6">
+        <v>13002</v>
+      </c>
+      <c r="G101" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="H101" s="3">
+        <v>6</v>
+      </c>
+      <c r="I101" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="102" customHeight="1" spans="3:9">
+      <c r="C102" s="1">
+        <v>143</v>
+      </c>
+      <c r="D102" s="3">
+        <v>23205803</v>
+      </c>
+      <c r="E102" s="6">
+        <v>13005</v>
+      </c>
+      <c r="F102" s="6">
+        <v>13005</v>
+      </c>
+      <c r="G102" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="H102" s="3">
+        <v>6</v>
+      </c>
+      <c r="I102" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="103" customHeight="1" spans="3:9">
+      <c r="C103" s="1">
+        <v>144</v>
+      </c>
+      <c r="D103" s="3">
+        <v>23205804</v>
+      </c>
+      <c r="E103" s="6">
+        <v>13005</v>
+      </c>
+      <c r="F103" s="6">
+        <v>13005</v>
+      </c>
+      <c r="G103" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="H103" s="3">
+        <v>6</v>
+      </c>
+      <c r="I103" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="104" customHeight="1" spans="3:9">
+      <c r="C104" s="1">
+        <v>145</v>
+      </c>
+      <c r="D104" s="3">
+        <v>23205805</v>
+      </c>
+      <c r="E104" s="6">
+        <v>13008</v>
+      </c>
+      <c r="F104" s="6">
+        <v>13008</v>
+      </c>
+      <c r="G104" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="H104" s="3">
+        <v>6</v>
+      </c>
+      <c r="I104" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="105" customHeight="1" spans="3:9">
+      <c r="C105" s="1">
+        <v>146</v>
+      </c>
+      <c r="D105" s="3">
+        <v>23205807</v>
+      </c>
+      <c r="E105" s="6">
+        <v>13009</v>
+      </c>
+      <c r="F105" s="6">
+        <v>13009</v>
+      </c>
+      <c r="G105" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="H105" s="3">
+        <v>6</v>
+      </c>
+      <c r="I105" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="106" customHeight="1" spans="3:9">
+      <c r="C106" s="1">
+        <v>147</v>
+      </c>
+      <c r="D106" s="3">
+        <v>23205809</v>
+      </c>
+      <c r="E106" s="6">
+        <v>13010</v>
+      </c>
+      <c r="F106" s="6">
+        <v>13010</v>
+      </c>
+      <c r="G106" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="H106" s="3">
+        <v>6</v>
+      </c>
+      <c r="I106" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="107" customHeight="1" spans="3:9">
+      <c r="C107" s="1">
+        <v>148</v>
+      </c>
+      <c r="D107" s="3">
+        <v>23205810</v>
+      </c>
+      <c r="E107" s="6">
+        <v>13010</v>
+      </c>
+      <c r="F107" s="6">
+        <v>13010</v>
+      </c>
+      <c r="G107" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="H107" s="3">
+        <v>6</v>
+      </c>
+      <c r="I107" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:D5" errorStyle="warning">

--- a/Excel/GiftPackEquipConfig.xlsx
+++ b/Excel/GiftPackEquipConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="32">
   <si>
     <t>#</t>
   </si>
@@ -95,40 +95,34 @@
     <t>攻击套-4幸运 道术加 攻击的 2项链</t>
   </si>
   <si>
-    <t>2004,2004,2001,2003,2003,2003</t>
+    <t>2004,2004,2001,2003,2003,2003,2011</t>
   </si>
   <si>
     <t>金色战士平衡套</t>
   </si>
   <si>
-    <t>2005,2005,2001,2003,2003,2003</t>
+    <t>2005,2005,2001,2003,2003,2003,2011</t>
   </si>
   <si>
     <t>金色法师平衡套</t>
   </si>
   <si>
-    <t>2006,2006,2001,2003,2003,2003</t>
+    <t>2006,2006,2001,2003,2003,2003,2011</t>
   </si>
   <si>
     <t>金色道士平衡套</t>
   </si>
   <si>
-    <t>2002,2002,2011,2003,2003,2003</t>
+    <t>2002,2002,2002,2011,2003,2003,2003</t>
   </si>
   <si>
     <t>金色战士防御套</t>
   </si>
   <si>
-    <t>2005,2005,2001,2011,34,34</t>
+    <t>2005,2005,2001,2011,34,34,34</t>
   </si>
   <si>
     <t>金色法师攻击套</t>
-  </si>
-  <si>
-    <t>2006,2006,2001,2011,2003,2003</t>
-  </si>
-  <si>
-    <t>金色道士攻击套</t>
   </si>
 </sst>
 </file>
@@ -1105,14 +1099,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I107"/>
+  <dimension ref="A1:I109"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
     <col min="2" max="2" width="9" style="2"/>
     <col min="3" max="4" width="9.875" style="1" customWidth="1"/>
     <col min="5" max="6" width="12.25" style="3" customWidth="1"/>
-    <col min="7" max="7" width="23.375" style="3" customWidth="1"/>
+    <col min="7" max="7" width="31.25" style="3" customWidth="1"/>
     <col min="8" max="8" width="12.25" style="3" customWidth="1"/>
     <col min="9" max="9" width="13.75" style="2" customWidth="1"/>
     <col min="10" max="16368" width="9" style="2"/>
@@ -2370,7 +2364,7 @@
         <v>22</v>
       </c>
       <c r="H59" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I59" s="2" t="s">
         <v>23</v>
@@ -2393,7 +2387,7 @@
         <v>22</v>
       </c>
       <c r="H60" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I60" s="2" t="s">
         <v>23</v>
@@ -2416,7 +2410,7 @@
         <v>22</v>
       </c>
       <c r="H61" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I61" s="2" t="s">
         <v>23</v>
@@ -2439,7 +2433,7 @@
         <v>22</v>
       </c>
       <c r="H62" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I62" s="2" t="s">
         <v>23</v>
@@ -2462,7 +2456,7 @@
         <v>22</v>
       </c>
       <c r="H63" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I63" s="2" t="s">
         <v>23</v>
@@ -2485,7 +2479,7 @@
         <v>22</v>
       </c>
       <c r="H64" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I64" s="2" t="s">
         <v>23</v>
@@ -2508,7 +2502,7 @@
         <v>22</v>
       </c>
       <c r="H65" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I65" s="2" t="s">
         <v>23</v>
@@ -2531,41 +2525,23 @@
         <v>22</v>
       </c>
       <c r="H66" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I66" s="2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="67" customHeight="1" spans="3:9">
-      <c r="C67" s="1">
-        <v>109</v>
-      </c>
-      <c r="D67" s="3">
-        <v>22205801</v>
-      </c>
-      <c r="E67" s="6">
-        <v>12002</v>
-      </c>
-      <c r="F67" s="6">
-        <v>12002</v>
-      </c>
-      <c r="G67" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="H67" s="3">
-        <v>6</v>
-      </c>
-      <c r="I67" s="2" t="s">
-        <v>25</v>
-      </c>
+    <row r="67" customHeight="1" spans="4:6">
+      <c r="D67" s="3"/>
+      <c r="E67" s="6"/>
+      <c r="F67" s="6"/>
     </row>
     <row r="68" customHeight="1" spans="3:9">
       <c r="C68" s="1">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D68" s="3">
-        <v>22205802</v>
+        <v>22205801</v>
       </c>
       <c r="E68" s="6">
         <v>12002</v>
@@ -2577,7 +2553,7 @@
         <v>24</v>
       </c>
       <c r="H68" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I68" s="2" t="s">
         <v>25</v>
@@ -2585,22 +2561,22 @@
     </row>
     <row r="69" customHeight="1" spans="3:9">
       <c r="C69" s="1">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D69" s="3">
-        <v>22205803</v>
+        <v>22205802</v>
       </c>
       <c r="E69" s="6">
-        <v>12005</v>
+        <v>12002</v>
       </c>
       <c r="F69" s="6">
-        <v>12005</v>
+        <v>12002</v>
       </c>
       <c r="G69" s="7" t="s">
         <v>24</v>
       </c>
       <c r="H69" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I69" s="2" t="s">
         <v>25</v>
@@ -2608,10 +2584,10 @@
     </row>
     <row r="70" customHeight="1" spans="3:9">
       <c r="C70" s="1">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D70" s="3">
-        <v>22205804</v>
+        <v>22205803</v>
       </c>
       <c r="E70" s="6">
         <v>12005</v>
@@ -2623,7 +2599,7 @@
         <v>24</v>
       </c>
       <c r="H70" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I70" s="2" t="s">
         <v>25</v>
@@ -2631,22 +2607,22 @@
     </row>
     <row r="71" customHeight="1" spans="3:9">
       <c r="C71" s="1">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D71" s="3">
-        <v>22205805</v>
+        <v>22205804</v>
       </c>
       <c r="E71" s="6">
-        <v>12006</v>
+        <v>12005</v>
       </c>
       <c r="F71" s="6">
-        <v>12006</v>
+        <v>12005</v>
       </c>
       <c r="G71" s="7" t="s">
         <v>24</v>
       </c>
       <c r="H71" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I71" s="2" t="s">
         <v>25</v>
@@ -2654,22 +2630,22 @@
     </row>
     <row r="72" customHeight="1" spans="3:9">
       <c r="C72" s="1">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D72" s="3">
-        <v>22205807</v>
+        <v>22205805</v>
       </c>
       <c r="E72" s="6">
-        <v>12008</v>
+        <v>12006</v>
       </c>
       <c r="F72" s="6">
-        <v>12008</v>
+        <v>12006</v>
       </c>
       <c r="G72" s="7" t="s">
         <v>24</v>
       </c>
       <c r="H72" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I72" s="2" t="s">
         <v>25</v>
@@ -2677,22 +2653,22 @@
     </row>
     <row r="73" customHeight="1" spans="3:9">
       <c r="C73" s="1">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D73" s="3">
-        <v>22205809</v>
+        <v>22205807</v>
       </c>
       <c r="E73" s="6">
-        <v>12010</v>
+        <v>12008</v>
       </c>
       <c r="F73" s="6">
-        <v>12110</v>
+        <v>12008</v>
       </c>
       <c r="G73" s="7" t="s">
         <v>24</v>
       </c>
       <c r="H73" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I73" s="2" t="s">
         <v>25</v>
@@ -2700,10 +2676,10 @@
     </row>
     <row r="74" customHeight="1" spans="3:9">
       <c r="C74" s="1">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D74" s="3">
-        <v>22205810</v>
+        <v>22205809</v>
       </c>
       <c r="E74" s="6">
         <v>12010</v>
@@ -2715,7 +2691,7 @@
         <v>24</v>
       </c>
       <c r="H74" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I74" s="2" t="s">
         <v>25</v>
@@ -2723,68 +2699,50 @@
     </row>
     <row r="75" customHeight="1" spans="3:9">
       <c r="C75" s="1">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D75" s="3">
-        <v>23205801</v>
+        <v>22205810</v>
       </c>
       <c r="E75" s="6">
-        <v>13002</v>
+        <v>12010</v>
       </c>
       <c r="F75" s="6">
-        <v>13002</v>
+        <v>12110</v>
       </c>
       <c r="G75" s="7" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H75" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I75" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="76" customHeight="1" spans="3:9">
-      <c r="C76" s="1">
-        <v>118</v>
-      </c>
-      <c r="D76" s="3">
-        <v>23205802</v>
-      </c>
-      <c r="E76" s="6">
-        <v>13002</v>
-      </c>
-      <c r="F76" s="6">
-        <v>13002</v>
-      </c>
-      <c r="G76" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="H76" s="3">
-        <v>6</v>
-      </c>
-      <c r="I76" s="2" t="s">
-        <v>27</v>
-      </c>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="76" customHeight="1" spans="4:6">
+      <c r="D76" s="3"/>
+      <c r="E76" s="6"/>
+      <c r="F76" s="6"/>
     </row>
     <row r="77" customHeight="1" spans="3:9">
       <c r="C77" s="1">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D77" s="3">
-        <v>23205803</v>
+        <v>23205801</v>
       </c>
       <c r="E77" s="6">
-        <v>13005</v>
+        <v>13002</v>
       </c>
       <c r="F77" s="6">
-        <v>13005</v>
+        <v>13002</v>
       </c>
       <c r="G77" s="7" t="s">
         <v>26</v>
       </c>
       <c r="H77" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I77" s="2" t="s">
         <v>27</v>
@@ -2792,22 +2750,22 @@
     </row>
     <row r="78" customHeight="1" spans="3:9">
       <c r="C78" s="1">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D78" s="3">
-        <v>23205804</v>
+        <v>23205802</v>
       </c>
       <c r="E78" s="6">
-        <v>13005</v>
+        <v>13002</v>
       </c>
       <c r="F78" s="6">
-        <v>13005</v>
+        <v>13002</v>
       </c>
       <c r="G78" s="7" t="s">
         <v>26</v>
       </c>
       <c r="H78" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I78" s="2" t="s">
         <v>27</v>
@@ -2815,22 +2773,22 @@
     </row>
     <row r="79" customHeight="1" spans="3:9">
       <c r="C79" s="1">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D79" s="3">
-        <v>23205805</v>
+        <v>23205803</v>
       </c>
       <c r="E79" s="6">
-        <v>13008</v>
+        <v>13005</v>
       </c>
       <c r="F79" s="6">
-        <v>13008</v>
+        <v>13005</v>
       </c>
       <c r="G79" s="7" t="s">
         <v>26</v>
       </c>
       <c r="H79" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I79" s="2" t="s">
         <v>27</v>
@@ -2838,22 +2796,22 @@
     </row>
     <row r="80" customHeight="1" spans="3:9">
       <c r="C80" s="1">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D80" s="3">
-        <v>23205807</v>
+        <v>23205804</v>
       </c>
       <c r="E80" s="6">
-        <v>13009</v>
+        <v>13005</v>
       </c>
       <c r="F80" s="6">
-        <v>13009</v>
+        <v>13005</v>
       </c>
       <c r="G80" s="7" t="s">
         <v>26</v>
       </c>
       <c r="H80" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I80" s="2" t="s">
         <v>27</v>
@@ -2861,22 +2819,22 @@
     </row>
     <row r="81" customHeight="1" spans="3:9">
       <c r="C81" s="1">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D81" s="3">
-        <v>23205809</v>
+        <v>23205805</v>
       </c>
       <c r="E81" s="6">
-        <v>13010</v>
+        <v>13008</v>
       </c>
       <c r="F81" s="6">
-        <v>13010</v>
+        <v>13008</v>
       </c>
       <c r="G81" s="7" t="s">
         <v>26</v>
       </c>
       <c r="H81" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I81" s="2" t="s">
         <v>27</v>
@@ -2884,91 +2842,91 @@
     </row>
     <row r="82" customHeight="1" spans="3:9">
       <c r="C82" s="1">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D82" s="3">
-        <v>23205810</v>
+        <v>23205807</v>
       </c>
       <c r="E82" s="6">
-        <v>13010</v>
+        <v>13009</v>
       </c>
       <c r="F82" s="6">
-        <v>13010</v>
+        <v>13009</v>
       </c>
       <c r="G82" s="7" t="s">
         <v>26</v>
       </c>
       <c r="H82" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I82" s="2" t="s">
         <v>27</v>
       </c>
     </row>
+    <row r="83" customHeight="1" spans="3:9">
+      <c r="C83" s="1">
+        <v>123</v>
+      </c>
+      <c r="D83" s="3">
+        <v>23205809</v>
+      </c>
+      <c r="E83" s="6">
+        <v>13010</v>
+      </c>
+      <c r="F83" s="6">
+        <v>13010</v>
+      </c>
+      <c r="G83" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="H83" s="3">
+        <v>7</v>
+      </c>
+      <c r="I83" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
     <row r="84" customHeight="1" spans="3:9">
       <c r="C84" s="1">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D84" s="3">
-        <v>21205801</v>
+        <v>23205810</v>
       </c>
       <c r="E84" s="6">
-        <v>11002</v>
+        <v>13010</v>
       </c>
       <c r="F84" s="6">
-        <v>11002</v>
+        <v>13010</v>
       </c>
       <c r="G84" s="7" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H84" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I84" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="85" customHeight="1" spans="3:9">
-      <c r="C85" s="1">
-        <v>126</v>
-      </c>
-      <c r="D85" s="3">
-        <v>21205802</v>
-      </c>
-      <c r="E85" s="6">
-        <v>11002</v>
-      </c>
-      <c r="F85" s="6">
-        <v>11002</v>
-      </c>
-      <c r="G85" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="H85" s="3">
-        <v>6</v>
-      </c>
-      <c r="I85" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="86" customHeight="1" spans="3:9">
       <c r="C86" s="1">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D86" s="3">
-        <v>21205803</v>
+        <v>21205801</v>
       </c>
       <c r="E86" s="6">
-        <v>11005</v>
+        <v>11002</v>
       </c>
       <c r="F86" s="6">
-        <v>11005</v>
+        <v>11002</v>
       </c>
       <c r="G86" s="7" t="s">
         <v>28</v>
       </c>
       <c r="H86" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I86" s="2" t="s">
         <v>29</v>
@@ -2976,22 +2934,22 @@
     </row>
     <row r="87" customHeight="1" spans="3:9">
       <c r="C87" s="1">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D87" s="3">
-        <v>21205804</v>
+        <v>21205802</v>
       </c>
       <c r="E87" s="6">
-        <v>11005</v>
+        <v>11002</v>
       </c>
       <c r="F87" s="6">
-        <v>11005</v>
+        <v>11002</v>
       </c>
       <c r="G87" s="7" t="s">
         <v>28</v>
       </c>
       <c r="H87" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I87" s="2" t="s">
         <v>29</v>
@@ -2999,22 +2957,22 @@
     </row>
     <row r="88" customHeight="1" spans="3:9">
       <c r="C88" s="1">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D88" s="3">
-        <v>21205805</v>
+        <v>21205803</v>
       </c>
       <c r="E88" s="6">
-        <v>11006</v>
+        <v>11005</v>
       </c>
       <c r="F88" s="6">
-        <v>11006</v>
+        <v>11005</v>
       </c>
       <c r="G88" s="7" t="s">
         <v>28</v>
       </c>
       <c r="H88" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I88" s="2" t="s">
         <v>29</v>
@@ -3022,22 +2980,22 @@
     </row>
     <row r="89" customHeight="1" spans="3:9">
       <c r="C89" s="1">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D89" s="3">
-        <v>21205807</v>
+        <v>21205804</v>
       </c>
       <c r="E89" s="6">
-        <v>11008</v>
+        <v>11005</v>
       </c>
       <c r="F89" s="6">
-        <v>11008</v>
+        <v>11005</v>
       </c>
       <c r="G89" s="7" t="s">
         <v>28</v>
       </c>
       <c r="H89" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I89" s="2" t="s">
         <v>29</v>
@@ -3045,22 +3003,22 @@
     </row>
     <row r="90" customHeight="1" spans="3:9">
       <c r="C90" s="1">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D90" s="3">
-        <v>21205809</v>
+        <v>21205805</v>
       </c>
       <c r="E90" s="6">
-        <v>11010</v>
+        <v>11006</v>
       </c>
       <c r="F90" s="6">
-        <v>11010</v>
+        <v>11006</v>
       </c>
       <c r="G90" s="7" t="s">
         <v>28</v>
       </c>
       <c r="H90" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I90" s="2" t="s">
         <v>29</v>
@@ -3068,22 +3026,22 @@
     </row>
     <row r="91" customHeight="1" spans="3:9">
       <c r="C91" s="1">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D91" s="3">
-        <v>21205810</v>
+        <v>21205807</v>
       </c>
       <c r="E91" s="6">
-        <v>11010</v>
+        <v>11008</v>
       </c>
       <c r="F91" s="6">
-        <v>11010</v>
+        <v>11008</v>
       </c>
       <c r="G91" s="7" t="s">
         <v>28</v>
       </c>
       <c r="H91" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I91" s="2" t="s">
         <v>29</v>
@@ -3091,68 +3049,68 @@
     </row>
     <row r="92" customHeight="1" spans="3:9">
       <c r="C92" s="1">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D92" s="3">
-        <v>22205801</v>
+        <v>21205809</v>
       </c>
       <c r="E92" s="6">
-        <v>12002</v>
+        <v>11010</v>
       </c>
       <c r="F92" s="6">
-        <v>12002</v>
+        <v>11010</v>
       </c>
       <c r="G92" s="7" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H92" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I92" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="93" customHeight="1" spans="3:9">
       <c r="C93" s="1">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D93" s="3">
-        <v>22205802</v>
+        <v>21205810</v>
       </c>
       <c r="E93" s="6">
-        <v>12002</v>
+        <v>11010</v>
       </c>
       <c r="F93" s="6">
-        <v>12002</v>
+        <v>11010</v>
       </c>
       <c r="G93" s="7" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H93" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I93" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="94" customHeight="1" spans="3:9">
       <c r="C94" s="1">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D94" s="3">
-        <v>22205803</v>
+        <v>22205801</v>
       </c>
       <c r="E94" s="6">
-        <v>12005</v>
+        <v>12002</v>
       </c>
       <c r="F94" s="6">
-        <v>12005</v>
+        <v>12002</v>
       </c>
       <c r="G94" s="7" t="s">
         <v>30</v>
       </c>
       <c r="H94" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I94" s="2" t="s">
         <v>31</v>
@@ -3160,22 +3118,22 @@
     </row>
     <row r="95" customHeight="1" spans="3:9">
       <c r="C95" s="1">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D95" s="3">
-        <v>22205804</v>
+        <v>22205802</v>
       </c>
       <c r="E95" s="6">
-        <v>12005</v>
+        <v>12002</v>
       </c>
       <c r="F95" s="6">
-        <v>12005</v>
+        <v>12002</v>
       </c>
       <c r="G95" s="7" t="s">
         <v>30</v>
       </c>
       <c r="H95" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I95" s="2" t="s">
         <v>31</v>
@@ -3183,22 +3141,22 @@
     </row>
     <row r="96" customHeight="1" spans="3:9">
       <c r="C96" s="1">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D96" s="3">
-        <v>22205805</v>
+        <v>22205803</v>
       </c>
       <c r="E96" s="6">
-        <v>12006</v>
+        <v>12005</v>
       </c>
       <c r="F96" s="6">
-        <v>12006</v>
+        <v>12005</v>
       </c>
       <c r="G96" s="7" t="s">
         <v>30</v>
       </c>
       <c r="H96" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I96" s="2" t="s">
         <v>31</v>
@@ -3206,22 +3164,22 @@
     </row>
     <row r="97" customHeight="1" spans="3:9">
       <c r="C97" s="1">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D97" s="3">
-        <v>22205807</v>
+        <v>22205804</v>
       </c>
       <c r="E97" s="6">
-        <v>12008</v>
+        <v>12005</v>
       </c>
       <c r="F97" s="6">
-        <v>12008</v>
+        <v>12005</v>
       </c>
       <c r="G97" s="7" t="s">
         <v>30</v>
       </c>
       <c r="H97" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I97" s="2" t="s">
         <v>31</v>
@@ -3229,22 +3187,22 @@
     </row>
     <row r="98" customHeight="1" spans="3:9">
       <c r="C98" s="1">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D98" s="3">
-        <v>22205809</v>
+        <v>22205805</v>
       </c>
       <c r="E98" s="6">
-        <v>12010</v>
+        <v>12006</v>
       </c>
       <c r="F98" s="6">
-        <v>12110</v>
+        <v>12006</v>
       </c>
       <c r="G98" s="7" t="s">
         <v>30</v>
       </c>
       <c r="H98" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I98" s="2" t="s">
         <v>31</v>
@@ -3252,22 +3210,22 @@
     </row>
     <row r="99" customHeight="1" spans="3:9">
       <c r="C99" s="1">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D99" s="3">
-        <v>22205810</v>
+        <v>22205807</v>
       </c>
       <c r="E99" s="6">
-        <v>12010</v>
+        <v>12008</v>
       </c>
       <c r="F99" s="6">
-        <v>12110</v>
+        <v>12008</v>
       </c>
       <c r="G99" s="7" t="s">
         <v>30</v>
       </c>
       <c r="H99" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I99" s="2" t="s">
         <v>31</v>
@@ -3275,187 +3233,89 @@
     </row>
     <row r="100" customHeight="1" spans="3:9">
       <c r="C100" s="1">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D100" s="3">
-        <v>23205801</v>
+        <v>22205809</v>
       </c>
       <c r="E100" s="6">
-        <v>13002</v>
+        <v>12010</v>
       </c>
       <c r="F100" s="6">
-        <v>13002</v>
+        <v>12110</v>
       </c>
       <c r="G100" s="7" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H100" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I100" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="101" customHeight="1" spans="3:9">
       <c r="C101" s="1">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D101" s="3">
-        <v>23205802</v>
+        <v>22205810</v>
       </c>
       <c r="E101" s="6">
-        <v>13002</v>
+        <v>12010</v>
       </c>
       <c r="F101" s="6">
-        <v>13002</v>
+        <v>12110</v>
       </c>
       <c r="G101" s="7" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H101" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I101" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="102" customHeight="1" spans="3:9">
-      <c r="C102" s="1">
-        <v>143</v>
-      </c>
-      <c r="D102" s="3">
-        <v>23205803</v>
-      </c>
-      <c r="E102" s="6">
-        <v>13005</v>
-      </c>
-      <c r="F102" s="6">
-        <v>13005</v>
-      </c>
-      <c r="G102" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="H102" s="3">
-        <v>6</v>
-      </c>
-      <c r="I102" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="103" customHeight="1" spans="3:9">
-      <c r="C103" s="1">
-        <v>144</v>
-      </c>
-      <c r="D103" s="3">
-        <v>23205804</v>
-      </c>
-      <c r="E103" s="6">
-        <v>13005</v>
-      </c>
-      <c r="F103" s="6">
-        <v>13005</v>
-      </c>
-      <c r="G103" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="H103" s="3">
-        <v>6</v>
-      </c>
-      <c r="I103" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="104" customHeight="1" spans="3:9">
-      <c r="C104" s="1">
-        <v>145</v>
-      </c>
-      <c r="D104" s="3">
-        <v>23205805</v>
-      </c>
-      <c r="E104" s="6">
-        <v>13008</v>
-      </c>
-      <c r="F104" s="6">
-        <v>13008</v>
-      </c>
-      <c r="G104" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="H104" s="3">
-        <v>6</v>
-      </c>
-      <c r="I104" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="105" customHeight="1" spans="3:9">
-      <c r="C105" s="1">
-        <v>146</v>
-      </c>
-      <c r="D105" s="3">
-        <v>23205807</v>
-      </c>
-      <c r="E105" s="6">
-        <v>13009</v>
-      </c>
-      <c r="F105" s="6">
-        <v>13009</v>
-      </c>
-      <c r="G105" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="H105" s="3">
-        <v>6</v>
-      </c>
-      <c r="I105" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="106" customHeight="1" spans="3:9">
-      <c r="C106" s="1">
-        <v>147</v>
-      </c>
-      <c r="D106" s="3">
-        <v>23205809</v>
-      </c>
-      <c r="E106" s="6">
-        <v>13010</v>
-      </c>
-      <c r="F106" s="6">
-        <v>13010</v>
-      </c>
-      <c r="G106" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="H106" s="3">
-        <v>6</v>
-      </c>
-      <c r="I106" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="107" customHeight="1" spans="3:9">
-      <c r="C107" s="1">
-        <v>148</v>
-      </c>
-      <c r="D107" s="3">
-        <v>23205810</v>
-      </c>
-      <c r="E107" s="6">
-        <v>13010</v>
-      </c>
-      <c r="F107" s="6">
-        <v>13010</v>
-      </c>
-      <c r="G107" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="H107" s="3">
-        <v>6</v>
-      </c>
-      <c r="I107" s="2" t="s">
-        <v>33</v>
-      </c>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="102" customHeight="1" spans="4:6">
+      <c r="D102" s="3"/>
+      <c r="E102" s="6"/>
+      <c r="F102" s="6"/>
+    </row>
+    <row r="103" customHeight="1" spans="4:6">
+      <c r="D103" s="3"/>
+      <c r="E103" s="6"/>
+      <c r="F103" s="6"/>
+    </row>
+    <row r="104" customHeight="1" spans="4:6">
+      <c r="D104" s="3"/>
+      <c r="E104" s="6"/>
+      <c r="F104" s="6"/>
+    </row>
+    <row r="105" customHeight="1" spans="4:6">
+      <c r="D105" s="3"/>
+      <c r="E105" s="6"/>
+      <c r="F105" s="6"/>
+    </row>
+    <row r="106" customHeight="1" spans="4:6">
+      <c r="D106" s="3"/>
+      <c r="E106" s="6"/>
+      <c r="F106" s="6"/>
+    </row>
+    <row r="107" customHeight="1" spans="4:6">
+      <c r="D107" s="3"/>
+      <c r="E107" s="6"/>
+      <c r="F107" s="6"/>
+    </row>
+    <row r="108" customHeight="1" spans="4:6">
+      <c r="D108" s="3"/>
+      <c r="E108" s="6"/>
+      <c r="F108" s="6"/>
+    </row>
+    <row r="109" customHeight="1" spans="4:6">
+      <c r="D109" s="3"/>
+      <c r="E109" s="6"/>
+      <c r="F109" s="6"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Excel/GiftPackEquipConfig.xlsx
+++ b/Excel/GiftPackEquipConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -80,10 +80,10 @@
     <t>34,2011,2001,2002,2003,2005</t>
   </si>
   <si>
-    <t>35,35,2001,2002,2003,2006</t>
+    <t>7,7,2001,2006,2003,35</t>
   </si>
   <si>
-    <t>35,2011,2001,2002,2003,2006</t>
+    <t>35,35,2001,2006,2011,2003</t>
   </si>
   <si>
     <t>7,7,7,7,2001,2006</t>
@@ -2246,7 +2246,7 @@
         <v>15</v>
       </c>
       <c r="G52" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H52" s="3">
         <v>6</v>

--- a/Excel/GiftPackEquipConfig.xlsx
+++ b/Excel/GiftPackEquipConfig.xlsx
@@ -65,25 +65,25 @@
     <t>经验套</t>
   </si>
   <si>
-    <t>33,33,2001,2002,2003,2004</t>
+    <t>33,33,7,7,2001,2004</t>
   </si>
   <si>
     <t>攻击套</t>
   </si>
   <si>
-    <t>33,2011,2001,2002,2003,2004</t>
+    <t>35,35,2001,2006,2003,2011</t>
   </si>
   <si>
-    <t>34,34,2001,2002,2003,2005</t>
+    <t>33,33,2001,2004,2003,2011</t>
   </si>
   <si>
-    <t>34,2011,2001,2002,2003,2005</t>
+    <t>34,34,7,7,2001,2005</t>
   </si>
   <si>
-    <t>7,7,2001,2006,2003,35</t>
+    <t>34,34,2001,2005,2003,2011</t>
   </si>
   <si>
-    <t>35,35,2001,2006,2011,2003</t>
+    <t>35,35,7,7,2001,2006</t>
   </si>
   <si>
     <t>7,7,7,7,2001,2006</t>
@@ -769,7 +769,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -779,6 +779,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -1099,7 +1100,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I109"/>
+  <dimension ref="A1:I111"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
@@ -1206,7 +1207,7 @@
       <c r="F6" s="3">
         <v>10</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="G6" s="8" t="s">
         <v>10</v>
       </c>
       <c r="H6" s="3">
@@ -1229,7 +1230,7 @@
       <c r="F7" s="3">
         <v>10</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="G7" s="8" t="s">
         <v>10</v>
       </c>
       <c r="H7" s="3">
@@ -1252,7 +1253,7 @@
       <c r="F8" s="3">
         <v>10</v>
       </c>
-      <c r="G8" s="7" t="s">
+      <c r="G8" s="8" t="s">
         <v>10</v>
       </c>
       <c r="H8" s="3">
@@ -1275,7 +1276,7 @@
       <c r="F9" s="3">
         <v>10</v>
       </c>
-      <c r="G9" s="7" t="s">
+      <c r="G9" s="8" t="s">
         <v>10</v>
       </c>
       <c r="H9" s="3">
@@ -1298,7 +1299,7 @@
       <c r="F10" s="3">
         <v>13</v>
       </c>
-      <c r="G10" s="7" t="s">
+      <c r="G10" s="8" t="s">
         <v>10</v>
       </c>
       <c r="H10" s="3">
@@ -1321,7 +1322,7 @@
       <c r="F11" s="6">
         <v>10005</v>
       </c>
-      <c r="G11" s="7" t="s">
+      <c r="G11" s="8" t="s">
         <v>10</v>
       </c>
       <c r="H11" s="3">
@@ -1344,7 +1345,7 @@
       <c r="F12" s="6">
         <v>10006</v>
       </c>
-      <c r="G12" s="7" t="s">
+      <c r="G12" s="8" t="s">
         <v>10</v>
       </c>
       <c r="H12" s="3">
@@ -1367,7 +1368,7 @@
       <c r="F13" s="6">
         <v>10006</v>
       </c>
-      <c r="G13" s="7" t="s">
+      <c r="G13" s="8" t="s">
         <v>10</v>
       </c>
       <c r="H13" s="3">
@@ -1390,7 +1391,7 @@
       <c r="F14" s="6">
         <v>10021</v>
       </c>
-      <c r="G14" s="7" t="s">
+      <c r="G14" s="8" t="s">
         <v>10</v>
       </c>
       <c r="H14" s="3">
@@ -1413,7 +1414,7 @@
       <c r="F15" s="6">
         <v>10021</v>
       </c>
-      <c r="G15" s="7" t="s">
+      <c r="G15" s="8" t="s">
         <v>10</v>
       </c>
       <c r="H15" s="3">
@@ -1436,7 +1437,7 @@
       <c r="F16" s="6">
         <v>10022</v>
       </c>
-      <c r="G16" s="7" t="s">
+      <c r="G16" s="8" t="s">
         <v>10</v>
       </c>
       <c r="H16" s="3">
@@ -1459,7 +1460,7 @@
       <c r="F17" s="6">
         <v>10022</v>
       </c>
-      <c r="G17" s="7" t="s">
+      <c r="G17" s="8" t="s">
         <v>10</v>
       </c>
       <c r="H17" s="3">
@@ -1482,7 +1483,7 @@
       <c r="F18" s="6">
         <v>10017</v>
       </c>
-      <c r="G18" s="7" t="s">
+      <c r="G18" s="8" t="s">
         <v>10</v>
       </c>
       <c r="H18" s="3">
@@ -1505,7 +1506,7 @@
       <c r="F19" s="6">
         <v>10022</v>
       </c>
-      <c r="G19" s="7" t="s">
+      <c r="G19" s="8" t="s">
         <v>10</v>
       </c>
       <c r="H19" s="3">
@@ -1528,7 +1529,7 @@
       <c r="F20" s="6">
         <v>10018</v>
       </c>
-      <c r="G20" s="7" t="s">
+      <c r="G20" s="8" t="s">
         <v>10</v>
       </c>
       <c r="H20" s="3">
@@ -1551,7 +1552,7 @@
       <c r="F21" s="6">
         <v>10018</v>
       </c>
-      <c r="G21" s="7" t="s">
+      <c r="G21" s="8" t="s">
         <v>10</v>
       </c>
       <c r="H21" s="3">
@@ -1574,7 +1575,7 @@
       <c r="F22" s="3">
         <v>4</v>
       </c>
-      <c r="G22" s="7" t="s">
+      <c r="G22" s="8" t="s">
         <v>10</v>
       </c>
       <c r="H22" s="3">
@@ -1597,7 +1598,7 @@
       <c r="F23" s="3">
         <v>4</v>
       </c>
-      <c r="G23" s="7" t="s">
+      <c r="G23" s="8" t="s">
         <v>10</v>
       </c>
       <c r="H23" s="3">
@@ -1620,7 +1621,7 @@
       <c r="F24" s="3">
         <v>10037</v>
       </c>
-      <c r="G24" s="7" t="s">
+      <c r="G24" s="8" t="s">
         <v>10</v>
       </c>
       <c r="H24" s="3">
@@ -1643,7 +1644,7 @@
       <c r="F25" s="3">
         <v>10037</v>
       </c>
-      <c r="G25" s="7" t="s">
+      <c r="G25" s="8" t="s">
         <v>10</v>
       </c>
       <c r="H25" s="3">
@@ -1666,7 +1667,7 @@
       <c r="F26" s="3">
         <v>9</v>
       </c>
-      <c r="G26" s="7" t="s">
+      <c r="G26" s="8" t="s">
         <v>10</v>
       </c>
       <c r="H26" s="3">
@@ -1689,7 +1690,7 @@
       <c r="F27" s="3">
         <v>15</v>
       </c>
-      <c r="G27" s="7" t="s">
+      <c r="G27" s="8" t="s">
         <v>10</v>
       </c>
       <c r="H27" s="3">
@@ -1712,7 +1713,7 @@
       <c r="F28" s="3">
         <v>18</v>
       </c>
-      <c r="G28" s="7" t="s">
+      <c r="G28" s="8" t="s">
         <v>10</v>
       </c>
       <c r="H28" s="3">
@@ -1735,7 +1736,7 @@
       <c r="F29" s="3">
         <v>18</v>
       </c>
-      <c r="G29" s="7" t="s">
+      <c r="G29" s="8" t="s">
         <v>10</v>
       </c>
       <c r="H29" s="3">
@@ -1762,7 +1763,7 @@
       <c r="F31" s="3">
         <v>10</v>
       </c>
-      <c r="G31" s="7" t="s">
+      <c r="G31" s="8" t="s">
         <v>12</v>
       </c>
       <c r="H31" s="3">
@@ -1785,7 +1786,7 @@
       <c r="F32" s="3">
         <v>10</v>
       </c>
-      <c r="G32" s="7" t="s">
+      <c r="G32" s="8" t="s">
         <v>14</v>
       </c>
       <c r="H32" s="3">
@@ -1808,7 +1809,7 @@
       <c r="F33" s="3">
         <v>10</v>
       </c>
-      <c r="G33" s="7" t="s">
+      <c r="G33" s="8" t="s">
         <v>12</v>
       </c>
       <c r="H33" s="3">
@@ -1831,8 +1832,8 @@
       <c r="F34" s="3">
         <v>10</v>
       </c>
-      <c r="G34" s="7" t="s">
-        <v>14</v>
+      <c r="G34" s="8" t="s">
+        <v>15</v>
       </c>
       <c r="H34" s="3">
         <v>6</v>
@@ -1854,8 +1855,8 @@
       <c r="F35" s="3">
         <v>13</v>
       </c>
-      <c r="G35" s="7" t="s">
-        <v>14</v>
+      <c r="G35" s="8" t="s">
+        <v>15</v>
       </c>
       <c r="H35" s="3">
         <v>6</v>
@@ -1877,8 +1878,8 @@
       <c r="F36" s="6">
         <v>10005</v>
       </c>
-      <c r="G36" s="7" t="s">
-        <v>12</v>
+      <c r="G36" s="8" t="s">
+        <v>15</v>
       </c>
       <c r="H36" s="3">
         <v>6</v>
@@ -1900,8 +1901,8 @@
       <c r="F37" s="6">
         <v>10006</v>
       </c>
-      <c r="G37" s="7" t="s">
-        <v>14</v>
+      <c r="G37" s="8" t="s">
+        <v>15</v>
       </c>
       <c r="H37" s="3">
         <v>6</v>
@@ -1923,8 +1924,8 @@
       <c r="F38" s="6">
         <v>10006</v>
       </c>
-      <c r="G38" s="7" t="s">
-        <v>14</v>
+      <c r="G38" s="8" t="s">
+        <v>15</v>
       </c>
       <c r="H38" s="3">
         <v>6</v>
@@ -1933,43 +1934,25 @@
         <v>13</v>
       </c>
     </row>
-    <row r="39" customHeight="1" spans="3:9">
-      <c r="C39" s="1">
-        <v>33</v>
-      </c>
-      <c r="D39" s="3">
-        <v>22105801</v>
-      </c>
-      <c r="E39" s="3">
-        <v>10047</v>
-      </c>
-      <c r="F39" s="6">
-        <v>10021</v>
-      </c>
-      <c r="G39" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="H39" s="3">
-        <v>6</v>
-      </c>
-      <c r="I39" s="2" t="s">
-        <v>13</v>
-      </c>
+    <row r="39" customHeight="1" spans="4:6">
+      <c r="D39" s="3"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="6"/>
     </row>
     <row r="40" customHeight="1" spans="3:9">
       <c r="C40" s="1">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D40" s="3">
-        <v>22105802</v>
-      </c>
-      <c r="E40" s="3">
-        <v>10047</v>
+        <v>22105801</v>
+      </c>
+      <c r="E40" s="6">
+        <v>12</v>
       </c>
       <c r="F40" s="6">
-        <v>10021</v>
-      </c>
-      <c r="G40" s="7" t="s">
+        <v>10017</v>
+      </c>
+      <c r="G40" s="8" t="s">
         <v>16</v>
       </c>
       <c r="H40" s="3">
@@ -1981,19 +1964,19 @@
     </row>
     <row r="41" customHeight="1" spans="3:9">
       <c r="C41" s="1">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>22105803</v>
-      </c>
-      <c r="E41" s="3">
-        <v>3</v>
+        <v>22105802</v>
+      </c>
+      <c r="E41" s="6">
+        <v>12</v>
       </c>
       <c r="F41" s="6">
-        <v>10022</v>
-      </c>
-      <c r="G41" s="7" t="s">
-        <v>15</v>
+        <v>10017</v>
+      </c>
+      <c r="G41" s="8" t="s">
+        <v>17</v>
       </c>
       <c r="H41" s="3">
         <v>6</v>
@@ -2004,18 +1987,18 @@
     </row>
     <row r="42" customHeight="1" spans="3:9">
       <c r="C42" s="1">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>22105804</v>
-      </c>
-      <c r="E42" s="3">
-        <v>3</v>
+        <v>22105803</v>
+      </c>
+      <c r="E42" s="6">
+        <v>12</v>
       </c>
       <c r="F42" s="6">
-        <v>10022</v>
-      </c>
-      <c r="G42" s="7" t="s">
+        <v>10018</v>
+      </c>
+      <c r="G42" s="8" t="s">
         <v>16</v>
       </c>
       <c r="H42" s="3">
@@ -2027,19 +2010,19 @@
     </row>
     <row r="43" customHeight="1" spans="3:9">
       <c r="C43" s="1">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>22105805</v>
-      </c>
-      <c r="E43" s="3">
-        <v>8</v>
-      </c>
-      <c r="F43" s="6">
-        <v>10017</v>
-      </c>
-      <c r="G43" s="7" t="s">
-        <v>16</v>
+        <v>22105804</v>
+      </c>
+      <c r="E43" s="6">
+        <v>18</v>
+      </c>
+      <c r="F43" s="7">
+        <v>11</v>
+      </c>
+      <c r="G43" s="8" t="s">
+        <v>17</v>
       </c>
       <c r="H43" s="3">
         <v>6</v>
@@ -2050,19 +2033,19 @@
     </row>
     <row r="44" customHeight="1" spans="3:9">
       <c r="C44" s="1">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>22105807</v>
-      </c>
-      <c r="E44" s="3">
-        <v>3</v>
-      </c>
-      <c r="F44" s="6">
-        <v>10022</v>
-      </c>
-      <c r="G44" s="7" t="s">
-        <v>15</v>
+        <v>22105805</v>
+      </c>
+      <c r="E44" s="6">
+        <v>22</v>
+      </c>
+      <c r="F44" s="7">
+        <v>14</v>
+      </c>
+      <c r="G44" s="8" t="s">
+        <v>17</v>
       </c>
       <c r="H44" s="3">
         <v>6</v>
@@ -2073,19 +2056,19 @@
     </row>
     <row r="45" customHeight="1" spans="3:9">
       <c r="C45" s="1">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>22105809</v>
-      </c>
-      <c r="E45" s="3">
-        <v>12</v>
-      </c>
-      <c r="F45" s="6">
-        <v>10018</v>
-      </c>
-      <c r="G45" s="7" t="s">
-        <v>16</v>
+        <v>22105807</v>
+      </c>
+      <c r="E45" s="6">
+        <v>22</v>
+      </c>
+      <c r="F45" s="7">
+        <v>14</v>
+      </c>
+      <c r="G45" s="8" t="s">
+        <v>17</v>
       </c>
       <c r="H45" s="3">
         <v>6</v>
@@ -2096,19 +2079,19 @@
     </row>
     <row r="46" customHeight="1" spans="3:9">
       <c r="C46" s="1">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>22105810</v>
-      </c>
-      <c r="E46" s="3">
-        <v>12</v>
-      </c>
-      <c r="F46" s="6">
-        <v>10018</v>
-      </c>
-      <c r="G46" s="7" t="s">
-        <v>16</v>
+        <v>22105809</v>
+      </c>
+      <c r="E46" s="6">
+        <v>18</v>
+      </c>
+      <c r="F46" s="7">
+        <v>6</v>
+      </c>
+      <c r="G46" s="8" t="s">
+        <v>17</v>
       </c>
       <c r="H46" s="3">
         <v>6</v>
@@ -2119,18 +2102,18 @@
     </row>
     <row r="47" customHeight="1" spans="3:9">
       <c r="C47" s="1">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>23105801</v>
-      </c>
-      <c r="E47" s="3">
-        <v>20</v>
-      </c>
-      <c r="F47" s="3">
-        <v>4</v>
-      </c>
-      <c r="G47" s="7" t="s">
+        <v>22105810</v>
+      </c>
+      <c r="E47" s="6">
+        <v>18</v>
+      </c>
+      <c r="F47" s="7">
+        <v>6</v>
+      </c>
+      <c r="G47" s="8" t="s">
         <v>17</v>
       </c>
       <c r="H47" s="3">
@@ -2140,44 +2123,25 @@
         <v>13</v>
       </c>
     </row>
-    <row r="48" customHeight="1" spans="3:9">
-      <c r="C48" s="1">
-        <v>42</v>
-      </c>
-      <c r="D48" s="3">
-        <v>23105802</v>
-      </c>
-      <c r="E48" s="3">
-        <v>20</v>
-      </c>
-      <c r="F48" s="3">
-        <v>4</v>
-      </c>
-      <c r="G48" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="H48" s="3">
-        <v>6</v>
-      </c>
-      <c r="I48" s="2" t="s">
-        <v>13</v>
-      </c>
+    <row r="48" customHeight="1" spans="4:6">
+      <c r="D48" s="3"/>
+      <c r="F48" s="6"/>
     </row>
     <row r="49" customHeight="1" spans="3:9">
       <c r="C49" s="1">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D49" s="3">
-        <v>23105803</v>
+        <v>23105801</v>
       </c>
       <c r="E49" s="3">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F49" s="3">
-        <v>10037</v>
-      </c>
-      <c r="G49" s="7" t="s">
-        <v>17</v>
+        <v>4</v>
+      </c>
+      <c r="G49" s="8" t="s">
+        <v>18</v>
       </c>
       <c r="H49" s="3">
         <v>6</v>
@@ -2188,19 +2152,19 @@
     </row>
     <row r="50" customHeight="1" spans="3:9">
       <c r="C50" s="1">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D50" s="3">
-        <v>23105804</v>
+        <v>23105802</v>
       </c>
       <c r="E50" s="3">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F50" s="3">
-        <v>10037</v>
-      </c>
-      <c r="G50" s="7" t="s">
-        <v>18</v>
+        <v>4</v>
+      </c>
+      <c r="G50" s="8" t="s">
+        <v>14</v>
       </c>
       <c r="H50" s="3">
         <v>6</v>
@@ -2211,18 +2175,18 @@
     </row>
     <row r="51" customHeight="1" spans="3:9">
       <c r="C51" s="1">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D51" s="3">
-        <v>23105805</v>
+        <v>23105803</v>
       </c>
       <c r="E51" s="3">
-        <v>10064</v>
+        <v>16</v>
       </c>
       <c r="F51" s="3">
-        <v>9</v>
-      </c>
-      <c r="G51" s="7" t="s">
+        <v>10037</v>
+      </c>
+      <c r="G51" s="8" t="s">
         <v>18</v>
       </c>
       <c r="H51" s="3">
@@ -2234,19 +2198,19 @@
     </row>
     <row r="52" customHeight="1" spans="3:9">
       <c r="C52" s="1">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D52" s="3">
-        <v>23105807</v>
+        <v>23105804</v>
       </c>
       <c r="E52" s="3">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F52" s="3">
-        <v>15</v>
-      </c>
-      <c r="G52" s="7" t="s">
-        <v>18</v>
+        <v>10037</v>
+      </c>
+      <c r="G52" s="8" t="s">
+        <v>14</v>
       </c>
       <c r="H52" s="3">
         <v>6</v>
@@ -2257,19 +2221,19 @@
     </row>
     <row r="53" customHeight="1" spans="3:9">
       <c r="C53" s="1">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D53" s="3">
-        <v>23105809</v>
+        <v>23105805</v>
       </c>
       <c r="E53" s="3">
-        <v>28</v>
+        <v>10064</v>
       </c>
       <c r="F53" s="3">
-        <v>18</v>
-      </c>
-      <c r="G53" s="7" t="s">
-        <v>18</v>
+        <v>9</v>
+      </c>
+      <c r="G53" s="8" t="s">
+        <v>14</v>
       </c>
       <c r="H53" s="3">
         <v>6</v>
@@ -2280,19 +2244,19 @@
     </row>
     <row r="54" customHeight="1" spans="3:9">
       <c r="C54" s="1">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D54" s="3">
-        <v>23105810</v>
+        <v>23105807</v>
       </c>
       <c r="E54" s="3">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="F54" s="3">
-        <v>18</v>
-      </c>
-      <c r="G54" s="7" t="s">
-        <v>18</v>
+        <v>15</v>
+      </c>
+      <c r="G54" s="8" t="s">
+        <v>14</v>
       </c>
       <c r="H54" s="3">
         <v>6</v>
@@ -2303,110 +2267,110 @@
     </row>
     <row r="55" customHeight="1" spans="3:9">
       <c r="C55" s="1">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D55" s="3">
-        <v>23105801</v>
+        <v>23105809</v>
       </c>
       <c r="E55" s="3">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="F55" s="3">
-        <v>4</v>
-      </c>
-      <c r="G55" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
+      </c>
+      <c r="G55" s="8" t="s">
+        <v>14</v>
       </c>
       <c r="H55" s="3">
         <v>6</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="3:9">
       <c r="C56" s="1">
+        <v>48</v>
+      </c>
+      <c r="D56" s="3">
+        <v>23105810</v>
+      </c>
+      <c r="E56" s="3">
+        <v>28</v>
+      </c>
+      <c r="F56" s="3">
+        <v>18</v>
+      </c>
+      <c r="G56" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H56" s="3">
+        <v>6</v>
+      </c>
+      <c r="I56" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="57" customHeight="1" spans="3:9">
+      <c r="C57" s="1">
+        <v>49</v>
+      </c>
+      <c r="D57" s="3">
+        <v>23105801</v>
+      </c>
+      <c r="E57" s="3">
+        <v>20</v>
+      </c>
+      <c r="F57" s="3">
+        <v>4</v>
+      </c>
+      <c r="G57" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="H57" s="3">
+        <v>6</v>
+      </c>
+      <c r="I57" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="58" customHeight="1" spans="3:9">
+      <c r="C58" s="1">
         <v>50</v>
       </c>
-      <c r="D56" s="3">
+      <c r="D58" s="3">
         <v>23105803</v>
       </c>
-      <c r="E56" s="3">
+      <c r="E58" s="3">
         <v>20</v>
       </c>
-      <c r="F56" s="3">
+      <c r="F58" s="3">
         <v>4</v>
       </c>
-      <c r="G56" s="7" t="s">
+      <c r="G58" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="H56" s="3">
-        <v>6</v>
-      </c>
-      <c r="I56" s="2" t="s">
+      <c r="H58" s="3">
+        <v>6</v>
+      </c>
+      <c r="I58" s="2" t="s">
         <v>21</v>
-      </c>
-    </row>
-    <row r="59" customHeight="1" spans="3:9">
-      <c r="C59" s="1">
-        <v>101</v>
-      </c>
-      <c r="D59" s="3">
-        <v>21205801</v>
-      </c>
-      <c r="E59" s="6">
-        <v>11002</v>
-      </c>
-      <c r="F59" s="6">
-        <v>11002</v>
-      </c>
-      <c r="G59" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="H59" s="3">
-        <v>7</v>
-      </c>
-      <c r="I59" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="60" customHeight="1" spans="3:9">
-      <c r="C60" s="1">
-        <v>102</v>
-      </c>
-      <c r="D60" s="3">
-        <v>21205802</v>
-      </c>
-      <c r="E60" s="6">
-        <v>11002</v>
-      </c>
-      <c r="F60" s="6">
-        <v>11002</v>
-      </c>
-      <c r="G60" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="H60" s="3">
-        <v>7</v>
-      </c>
-      <c r="I60" s="2" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="3:9">
       <c r="C61" s="1">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D61" s="3">
-        <v>21205803</v>
+        <v>21205801</v>
       </c>
       <c r="E61" s="6">
-        <v>11005</v>
+        <v>11002</v>
       </c>
       <c r="F61" s="6">
-        <v>11005</v>
-      </c>
-      <c r="G61" s="7" t="s">
+        <v>11002</v>
+      </c>
+      <c r="G61" s="8" t="s">
         <v>22</v>
       </c>
       <c r="H61" s="3">
@@ -2418,18 +2382,18 @@
     </row>
     <row r="62" customHeight="1" spans="3:9">
       <c r="C62" s="1">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D62" s="3">
-        <v>21205804</v>
+        <v>21205802</v>
       </c>
       <c r="E62" s="6">
-        <v>11005</v>
+        <v>11002</v>
       </c>
       <c r="F62" s="6">
-        <v>11005</v>
-      </c>
-      <c r="G62" s="7" t="s">
+        <v>11002</v>
+      </c>
+      <c r="G62" s="8" t="s">
         <v>22</v>
       </c>
       <c r="H62" s="3">
@@ -2441,18 +2405,18 @@
     </row>
     <row r="63" customHeight="1" spans="3:9">
       <c r="C63" s="1">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D63" s="3">
-        <v>21205805</v>
+        <v>21205803</v>
       </c>
       <c r="E63" s="6">
-        <v>11006</v>
+        <v>11005</v>
       </c>
       <c r="F63" s="6">
-        <v>11006</v>
-      </c>
-      <c r="G63" s="7" t="s">
+        <v>11005</v>
+      </c>
+      <c r="G63" s="8" t="s">
         <v>22</v>
       </c>
       <c r="H63" s="3">
@@ -2464,18 +2428,18 @@
     </row>
     <row r="64" customHeight="1" spans="3:9">
       <c r="C64" s="1">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D64" s="3">
-        <v>21205807</v>
+        <v>21205804</v>
       </c>
       <c r="E64" s="6">
-        <v>11008</v>
+        <v>11005</v>
       </c>
       <c r="F64" s="6">
-        <v>11008</v>
-      </c>
-      <c r="G64" s="7" t="s">
+        <v>11005</v>
+      </c>
+      <c r="G64" s="8" t="s">
         <v>22</v>
       </c>
       <c r="H64" s="3">
@@ -2487,18 +2451,18 @@
     </row>
     <row r="65" customHeight="1" spans="3:9">
       <c r="C65" s="1">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D65" s="3">
-        <v>21205809</v>
+        <v>21205805</v>
       </c>
       <c r="E65" s="6">
-        <v>11010</v>
+        <v>11006</v>
       </c>
       <c r="F65" s="6">
-        <v>11010</v>
-      </c>
-      <c r="G65" s="7" t="s">
+        <v>11006</v>
+      </c>
+      <c r="G65" s="8" t="s">
         <v>22</v>
       </c>
       <c r="H65" s="3">
@@ -2510,18 +2474,18 @@
     </row>
     <row r="66" customHeight="1" spans="3:9">
       <c r="C66" s="1">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D66" s="3">
-        <v>21205810</v>
+        <v>21205807</v>
       </c>
       <c r="E66" s="6">
-        <v>11010</v>
+        <v>11008</v>
       </c>
       <c r="F66" s="6">
-        <v>11010</v>
-      </c>
-      <c r="G66" s="7" t="s">
+        <v>11008</v>
+      </c>
+      <c r="G66" s="8" t="s">
         <v>22</v>
       </c>
       <c r="H66" s="3">
@@ -2531,71 +2495,71 @@
         <v>23</v>
       </c>
     </row>
-    <row r="67" customHeight="1" spans="4:6">
-      <c r="D67" s="3"/>
-      <c r="E67" s="6"/>
-      <c r="F67" s="6"/>
+    <row r="67" customHeight="1" spans="3:9">
+      <c r="C67" s="1">
+        <v>107</v>
+      </c>
+      <c r="D67" s="3">
+        <v>21205809</v>
+      </c>
+      <c r="E67" s="6">
+        <v>11010</v>
+      </c>
+      <c r="F67" s="6">
+        <v>11010</v>
+      </c>
+      <c r="G67" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="H67" s="3">
+        <v>7</v>
+      </c>
+      <c r="I67" s="2" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="68" customHeight="1" spans="3:9">
       <c r="C68" s="1">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D68" s="3">
-        <v>22205801</v>
+        <v>21205810</v>
       </c>
       <c r="E68" s="6">
-        <v>12002</v>
+        <v>11010</v>
       </c>
       <c r="F68" s="6">
-        <v>12002</v>
-      </c>
-      <c r="G68" s="7" t="s">
-        <v>24</v>
+        <v>11010</v>
+      </c>
+      <c r="G68" s="8" t="s">
+        <v>22</v>
       </c>
       <c r="H68" s="3">
         <v>7</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="69" customHeight="1" spans="3:9">
-      <c r="C69" s="1">
-        <v>110</v>
-      </c>
-      <c r="D69" s="3">
-        <v>22205802</v>
-      </c>
-      <c r="E69" s="6">
-        <v>12002</v>
-      </c>
-      <c r="F69" s="6">
-        <v>12002</v>
-      </c>
-      <c r="G69" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="H69" s="3">
-        <v>7</v>
-      </c>
-      <c r="I69" s="2" t="s">
-        <v>25</v>
-      </c>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="69" customHeight="1" spans="4:6">
+      <c r="D69" s="3"/>
+      <c r="E69" s="6"/>
+      <c r="F69" s="6"/>
     </row>
     <row r="70" customHeight="1" spans="3:9">
       <c r="C70" s="1">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D70" s="3">
-        <v>22205803</v>
+        <v>22205801</v>
       </c>
       <c r="E70" s="6">
-        <v>12005</v>
+        <v>12002</v>
       </c>
       <c r="F70" s="6">
-        <v>12005</v>
-      </c>
-      <c r="G70" s="7" t="s">
+        <v>12002</v>
+      </c>
+      <c r="G70" s="8" t="s">
         <v>24</v>
       </c>
       <c r="H70" s="3">
@@ -2607,18 +2571,18 @@
     </row>
     <row r="71" customHeight="1" spans="3:9">
       <c r="C71" s="1">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D71" s="3">
-        <v>22205804</v>
+        <v>22205802</v>
       </c>
       <c r="E71" s="6">
-        <v>12005</v>
+        <v>12002</v>
       </c>
       <c r="F71" s="6">
-        <v>12005</v>
-      </c>
-      <c r="G71" s="7" t="s">
+        <v>12002</v>
+      </c>
+      <c r="G71" s="8" t="s">
         <v>24</v>
       </c>
       <c r="H71" s="3">
@@ -2630,18 +2594,18 @@
     </row>
     <row r="72" customHeight="1" spans="3:9">
       <c r="C72" s="1">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D72" s="3">
-        <v>22205805</v>
+        <v>22205803</v>
       </c>
       <c r="E72" s="6">
-        <v>12006</v>
+        <v>12005</v>
       </c>
       <c r="F72" s="6">
-        <v>12006</v>
-      </c>
-      <c r="G72" s="7" t="s">
+        <v>12005</v>
+      </c>
+      <c r="G72" s="8" t="s">
         <v>24</v>
       </c>
       <c r="H72" s="3">
@@ -2653,18 +2617,18 @@
     </row>
     <row r="73" customHeight="1" spans="3:9">
       <c r="C73" s="1">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D73" s="3">
-        <v>22205807</v>
+        <v>22205804</v>
       </c>
       <c r="E73" s="6">
-        <v>12008</v>
+        <v>12005</v>
       </c>
       <c r="F73" s="6">
-        <v>12008</v>
-      </c>
-      <c r="G73" s="7" t="s">
+        <v>12005</v>
+      </c>
+      <c r="G73" s="8" t="s">
         <v>24</v>
       </c>
       <c r="H73" s="3">
@@ -2676,18 +2640,18 @@
     </row>
     <row r="74" customHeight="1" spans="3:9">
       <c r="C74" s="1">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D74" s="3">
-        <v>22205809</v>
+        <v>22205805</v>
       </c>
       <c r="E74" s="6">
-        <v>12010</v>
+        <v>12006</v>
       </c>
       <c r="F74" s="6">
-        <v>12110</v>
-      </c>
-      <c r="G74" s="7" t="s">
+        <v>12006</v>
+      </c>
+      <c r="G74" s="8" t="s">
         <v>24</v>
       </c>
       <c r="H74" s="3">
@@ -2699,18 +2663,18 @@
     </row>
     <row r="75" customHeight="1" spans="3:9">
       <c r="C75" s="1">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D75" s="3">
-        <v>22205810</v>
+        <v>22205807</v>
       </c>
       <c r="E75" s="6">
-        <v>12010</v>
+        <v>12008</v>
       </c>
       <c r="F75" s="6">
-        <v>12110</v>
-      </c>
-      <c r="G75" s="7" t="s">
+        <v>12008</v>
+      </c>
+      <c r="G75" s="8" t="s">
         <v>24</v>
       </c>
       <c r="H75" s="3">
@@ -2720,71 +2684,71 @@
         <v>25</v>
       </c>
     </row>
-    <row r="76" customHeight="1" spans="4:6">
-      <c r="D76" s="3"/>
-      <c r="E76" s="6"/>
-      <c r="F76" s="6"/>
+    <row r="76" customHeight="1" spans="3:9">
+      <c r="C76" s="1">
+        <v>115</v>
+      </c>
+      <c r="D76" s="3">
+        <v>22205809</v>
+      </c>
+      <c r="E76" s="6">
+        <v>12010</v>
+      </c>
+      <c r="F76" s="6">
+        <v>12110</v>
+      </c>
+      <c r="G76" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="H76" s="3">
+        <v>7</v>
+      </c>
+      <c r="I76" s="2" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="77" customHeight="1" spans="3:9">
       <c r="C77" s="1">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D77" s="3">
-        <v>23205801</v>
+        <v>22205810</v>
       </c>
       <c r="E77" s="6">
-        <v>13002</v>
+        <v>12010</v>
       </c>
       <c r="F77" s="6">
-        <v>13002</v>
-      </c>
-      <c r="G77" s="7" t="s">
-        <v>26</v>
+        <v>12110</v>
+      </c>
+      <c r="G77" s="8" t="s">
+        <v>24</v>
       </c>
       <c r="H77" s="3">
         <v>7</v>
       </c>
       <c r="I77" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="78" customHeight="1" spans="3:9">
-      <c r="C78" s="1">
-        <v>118</v>
-      </c>
-      <c r="D78" s="3">
-        <v>23205802</v>
-      </c>
-      <c r="E78" s="6">
-        <v>13002</v>
-      </c>
-      <c r="F78" s="6">
-        <v>13002</v>
-      </c>
-      <c r="G78" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="H78" s="3">
-        <v>7</v>
-      </c>
-      <c r="I78" s="2" t="s">
-        <v>27</v>
-      </c>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="78" customHeight="1" spans="4:6">
+      <c r="D78" s="3"/>
+      <c r="E78" s="6"/>
+      <c r="F78" s="6"/>
     </row>
     <row r="79" customHeight="1" spans="3:9">
       <c r="C79" s="1">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D79" s="3">
-        <v>23205803</v>
+        <v>23205801</v>
       </c>
       <c r="E79" s="6">
-        <v>13005</v>
+        <v>13002</v>
       </c>
       <c r="F79" s="6">
-        <v>13005</v>
-      </c>
-      <c r="G79" s="7" t="s">
+        <v>13002</v>
+      </c>
+      <c r="G79" s="8" t="s">
         <v>26</v>
       </c>
       <c r="H79" s="3">
@@ -2796,18 +2760,18 @@
     </row>
     <row r="80" customHeight="1" spans="3:9">
       <c r="C80" s="1">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D80" s="3">
-        <v>23205804</v>
+        <v>23205802</v>
       </c>
       <c r="E80" s="6">
-        <v>13005</v>
+        <v>13002</v>
       </c>
       <c r="F80" s="6">
-        <v>13005</v>
-      </c>
-      <c r="G80" s="7" t="s">
+        <v>13002</v>
+      </c>
+      <c r="G80" s="8" t="s">
         <v>26</v>
       </c>
       <c r="H80" s="3">
@@ -2819,18 +2783,18 @@
     </row>
     <row r="81" customHeight="1" spans="3:9">
       <c r="C81" s="1">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D81" s="3">
-        <v>23205805</v>
+        <v>23205803</v>
       </c>
       <c r="E81" s="6">
-        <v>13008</v>
+        <v>13005</v>
       </c>
       <c r="F81" s="6">
-        <v>13008</v>
-      </c>
-      <c r="G81" s="7" t="s">
+        <v>13005</v>
+      </c>
+      <c r="G81" s="8" t="s">
         <v>26</v>
       </c>
       <c r="H81" s="3">
@@ -2842,18 +2806,18 @@
     </row>
     <row r="82" customHeight="1" spans="3:9">
       <c r="C82" s="1">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D82" s="3">
-        <v>23205807</v>
+        <v>23205804</v>
       </c>
       <c r="E82" s="6">
-        <v>13009</v>
+        <v>13005</v>
       </c>
       <c r="F82" s="6">
-        <v>13009</v>
-      </c>
-      <c r="G82" s="7" t="s">
+        <v>13005</v>
+      </c>
+      <c r="G82" s="8" t="s">
         <v>26</v>
       </c>
       <c r="H82" s="3">
@@ -2865,18 +2829,18 @@
     </row>
     <row r="83" customHeight="1" spans="3:9">
       <c r="C83" s="1">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D83" s="3">
-        <v>23205809</v>
+        <v>23205805</v>
       </c>
       <c r="E83" s="6">
-        <v>13010</v>
+        <v>13008</v>
       </c>
       <c r="F83" s="6">
-        <v>13010</v>
-      </c>
-      <c r="G83" s="7" t="s">
+        <v>13008</v>
+      </c>
+      <c r="G83" s="8" t="s">
         <v>26</v>
       </c>
       <c r="H83" s="3">
@@ -2888,18 +2852,18 @@
     </row>
     <row r="84" customHeight="1" spans="3:9">
       <c r="C84" s="1">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D84" s="3">
-        <v>23205810</v>
+        <v>23205807</v>
       </c>
       <c r="E84" s="6">
-        <v>13010</v>
+        <v>13009</v>
       </c>
       <c r="F84" s="6">
-        <v>13010</v>
-      </c>
-      <c r="G84" s="7" t="s">
+        <v>13009</v>
+      </c>
+      <c r="G84" s="8" t="s">
         <v>26</v>
       </c>
       <c r="H84" s="3">
@@ -2909,66 +2873,66 @@
         <v>27</v>
       </c>
     </row>
+    <row r="85" customHeight="1" spans="3:9">
+      <c r="C85" s="1">
+        <v>123</v>
+      </c>
+      <c r="D85" s="3">
+        <v>23205809</v>
+      </c>
+      <c r="E85" s="6">
+        <v>13010</v>
+      </c>
+      <c r="F85" s="6">
+        <v>13010</v>
+      </c>
+      <c r="G85" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="H85" s="3">
+        <v>7</v>
+      </c>
+      <c r="I85" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
     <row r="86" customHeight="1" spans="3:9">
       <c r="C86" s="1">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D86" s="3">
-        <v>21205801</v>
+        <v>23205810</v>
       </c>
       <c r="E86" s="6">
-        <v>11002</v>
+        <v>13010</v>
       </c>
       <c r="F86" s="6">
-        <v>11002</v>
-      </c>
-      <c r="G86" s="7" t="s">
-        <v>28</v>
+        <v>13010</v>
+      </c>
+      <c r="G86" s="8" t="s">
+        <v>26</v>
       </c>
       <c r="H86" s="3">
         <v>7</v>
       </c>
       <c r="I86" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="87" customHeight="1" spans="3:9">
-      <c r="C87" s="1">
-        <v>126</v>
-      </c>
-      <c r="D87" s="3">
-        <v>21205802</v>
-      </c>
-      <c r="E87" s="6">
-        <v>11002</v>
-      </c>
-      <c r="F87" s="6">
-        <v>11002</v>
-      </c>
-      <c r="G87" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="H87" s="3">
-        <v>7</v>
-      </c>
-      <c r="I87" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="88" customHeight="1" spans="3:9">
       <c r="C88" s="1">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D88" s="3">
-        <v>21205803</v>
+        <v>21205801</v>
       </c>
       <c r="E88" s="6">
-        <v>11005</v>
+        <v>11002</v>
       </c>
       <c r="F88" s="6">
-        <v>11005</v>
-      </c>
-      <c r="G88" s="7" t="s">
+        <v>11002</v>
+      </c>
+      <c r="G88" s="8" t="s">
         <v>28</v>
       </c>
       <c r="H88" s="3">
@@ -2980,18 +2944,18 @@
     </row>
     <row r="89" customHeight="1" spans="3:9">
       <c r="C89" s="1">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D89" s="3">
-        <v>21205804</v>
+        <v>21205802</v>
       </c>
       <c r="E89" s="6">
-        <v>11005</v>
+        <v>11002</v>
       </c>
       <c r="F89" s="6">
-        <v>11005</v>
-      </c>
-      <c r="G89" s="7" t="s">
+        <v>11002</v>
+      </c>
+      <c r="G89" s="8" t="s">
         <v>28</v>
       </c>
       <c r="H89" s="3">
@@ -3003,18 +2967,18 @@
     </row>
     <row r="90" customHeight="1" spans="3:9">
       <c r="C90" s="1">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D90" s="3">
-        <v>21205805</v>
+        <v>21205803</v>
       </c>
       <c r="E90" s="6">
-        <v>11006</v>
+        <v>11005</v>
       </c>
       <c r="F90" s="6">
-        <v>11006</v>
-      </c>
-      <c r="G90" s="7" t="s">
+        <v>11005</v>
+      </c>
+      <c r="G90" s="8" t="s">
         <v>28</v>
       </c>
       <c r="H90" s="3">
@@ -3026,18 +2990,18 @@
     </row>
     <row r="91" customHeight="1" spans="3:9">
       <c r="C91" s="1">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D91" s="3">
-        <v>21205807</v>
+        <v>21205804</v>
       </c>
       <c r="E91" s="6">
-        <v>11008</v>
+        <v>11005</v>
       </c>
       <c r="F91" s="6">
-        <v>11008</v>
-      </c>
-      <c r="G91" s="7" t="s">
+        <v>11005</v>
+      </c>
+      <c r="G91" s="8" t="s">
         <v>28</v>
       </c>
       <c r="H91" s="3">
@@ -3049,18 +3013,18 @@
     </row>
     <row r="92" customHeight="1" spans="3:9">
       <c r="C92" s="1">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D92" s="3">
-        <v>21205809</v>
+        <v>21205805</v>
       </c>
       <c r="E92" s="6">
-        <v>11010</v>
+        <v>11006</v>
       </c>
       <c r="F92" s="6">
-        <v>11010</v>
-      </c>
-      <c r="G92" s="7" t="s">
+        <v>11006</v>
+      </c>
+      <c r="G92" s="8" t="s">
         <v>28</v>
       </c>
       <c r="H92" s="3">
@@ -3072,18 +3036,18 @@
     </row>
     <row r="93" customHeight="1" spans="3:9">
       <c r="C93" s="1">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D93" s="3">
-        <v>21205810</v>
+        <v>21205807</v>
       </c>
       <c r="E93" s="6">
-        <v>11010</v>
+        <v>11008</v>
       </c>
       <c r="F93" s="6">
-        <v>11010</v>
-      </c>
-      <c r="G93" s="7" t="s">
+        <v>11008</v>
+      </c>
+      <c r="G93" s="8" t="s">
         <v>28</v>
       </c>
       <c r="H93" s="3">
@@ -3095,64 +3059,64 @@
     </row>
     <row r="94" customHeight="1" spans="3:9">
       <c r="C94" s="1">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D94" s="3">
-        <v>22205801</v>
+        <v>21205809</v>
       </c>
       <c r="E94" s="6">
-        <v>12002</v>
+        <v>11010</v>
       </c>
       <c r="F94" s="6">
-        <v>12002</v>
-      </c>
-      <c r="G94" s="7" t="s">
-        <v>30</v>
+        <v>11010</v>
+      </c>
+      <c r="G94" s="8" t="s">
+        <v>28</v>
       </c>
       <c r="H94" s="3">
         <v>7</v>
       </c>
       <c r="I94" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="95" customHeight="1" spans="3:9">
       <c r="C95" s="1">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D95" s="3">
-        <v>22205802</v>
+        <v>21205810</v>
       </c>
       <c r="E95" s="6">
-        <v>12002</v>
+        <v>11010</v>
       </c>
       <c r="F95" s="6">
-        <v>12002</v>
-      </c>
-      <c r="G95" s="7" t="s">
-        <v>30</v>
+        <v>11010</v>
+      </c>
+      <c r="G95" s="8" t="s">
+        <v>28</v>
       </c>
       <c r="H95" s="3">
         <v>7</v>
       </c>
       <c r="I95" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="96" customHeight="1" spans="3:9">
       <c r="C96" s="1">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D96" s="3">
-        <v>22205803</v>
+        <v>22205801</v>
       </c>
       <c r="E96" s="6">
-        <v>12005</v>
+        <v>12002</v>
       </c>
       <c r="F96" s="6">
-        <v>12005</v>
-      </c>
-      <c r="G96" s="7" t="s">
+        <v>12002</v>
+      </c>
+      <c r="G96" s="8" t="s">
         <v>30</v>
       </c>
       <c r="H96" s="3">
@@ -3164,18 +3128,18 @@
     </row>
     <row r="97" customHeight="1" spans="3:9">
       <c r="C97" s="1">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D97" s="3">
-        <v>22205804</v>
+        <v>22205802</v>
       </c>
       <c r="E97" s="6">
-        <v>12005</v>
+        <v>12002</v>
       </c>
       <c r="F97" s="6">
-        <v>12005</v>
-      </c>
-      <c r="G97" s="7" t="s">
+        <v>12002</v>
+      </c>
+      <c r="G97" s="8" t="s">
         <v>30</v>
       </c>
       <c r="H97" s="3">
@@ -3187,18 +3151,18 @@
     </row>
     <row r="98" customHeight="1" spans="3:9">
       <c r="C98" s="1">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D98" s="3">
-        <v>22205805</v>
+        <v>22205803</v>
       </c>
       <c r="E98" s="6">
-        <v>12006</v>
+        <v>12005</v>
       </c>
       <c r="F98" s="6">
-        <v>12006</v>
-      </c>
-      <c r="G98" s="7" t="s">
+        <v>12005</v>
+      </c>
+      <c r="G98" s="8" t="s">
         <v>30</v>
       </c>
       <c r="H98" s="3">
@@ -3210,18 +3174,18 @@
     </row>
     <row r="99" customHeight="1" spans="3:9">
       <c r="C99" s="1">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D99" s="3">
-        <v>22205807</v>
+        <v>22205804</v>
       </c>
       <c r="E99" s="6">
-        <v>12008</v>
+        <v>12005</v>
       </c>
       <c r="F99" s="6">
-        <v>12008</v>
-      </c>
-      <c r="G99" s="7" t="s">
+        <v>12005</v>
+      </c>
+      <c r="G99" s="8" t="s">
         <v>30</v>
       </c>
       <c r="H99" s="3">
@@ -3233,18 +3197,18 @@
     </row>
     <row r="100" customHeight="1" spans="3:9">
       <c r="C100" s="1">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D100" s="3">
-        <v>22205809</v>
+        <v>22205805</v>
       </c>
       <c r="E100" s="6">
-        <v>12010</v>
+        <v>12006</v>
       </c>
       <c r="F100" s="6">
-        <v>12110</v>
-      </c>
-      <c r="G100" s="7" t="s">
+        <v>12006</v>
+      </c>
+      <c r="G100" s="8" t="s">
         <v>30</v>
       </c>
       <c r="H100" s="3">
@@ -3256,18 +3220,18 @@
     </row>
     <row r="101" customHeight="1" spans="3:9">
       <c r="C101" s="1">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D101" s="3">
-        <v>22205810</v>
+        <v>22205807</v>
       </c>
       <c r="E101" s="6">
-        <v>12010</v>
+        <v>12008</v>
       </c>
       <c r="F101" s="6">
-        <v>12110</v>
-      </c>
-      <c r="G101" s="7" t="s">
+        <v>12008</v>
+      </c>
+      <c r="G101" s="8" t="s">
         <v>30</v>
       </c>
       <c r="H101" s="3">
@@ -3277,15 +3241,51 @@
         <v>31</v>
       </c>
     </row>
-    <row r="102" customHeight="1" spans="4:6">
-      <c r="D102" s="3"/>
-      <c r="E102" s="6"/>
-      <c r="F102" s="6"/>
-    </row>
-    <row r="103" customHeight="1" spans="4:6">
-      <c r="D103" s="3"/>
-      <c r="E103" s="6"/>
-      <c r="F103" s="6"/>
+    <row r="102" customHeight="1" spans="3:9">
+      <c r="C102" s="1">
+        <v>139</v>
+      </c>
+      <c r="D102" s="3">
+        <v>22205809</v>
+      </c>
+      <c r="E102" s="6">
+        <v>12010</v>
+      </c>
+      <c r="F102" s="6">
+        <v>12110</v>
+      </c>
+      <c r="G102" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="H102" s="3">
+        <v>7</v>
+      </c>
+      <c r="I102" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="103" customHeight="1" spans="3:9">
+      <c r="C103" s="1">
+        <v>140</v>
+      </c>
+      <c r="D103" s="3">
+        <v>22205810</v>
+      </c>
+      <c r="E103" s="6">
+        <v>12010</v>
+      </c>
+      <c r="F103" s="6">
+        <v>12110</v>
+      </c>
+      <c r="G103" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="H103" s="3">
+        <v>7</v>
+      </c>
+      <c r="I103" s="2" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="104" customHeight="1" spans="4:6">
       <c r="D104" s="3"/>
@@ -3316,6 +3316,16 @@
       <c r="D109" s="3"/>
       <c r="E109" s="6"/>
       <c r="F109" s="6"/>
+    </row>
+    <row r="110" customHeight="1" spans="4:6">
+      <c r="D110" s="3"/>
+      <c r="E110" s="6"/>
+      <c r="F110" s="6"/>
+    </row>
+    <row r="111" customHeight="1" spans="4:6">
+      <c r="D111" s="3"/>
+      <c r="E111" s="6"/>
+      <c r="F111" s="6"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Excel/GiftPackEquipConfig.xlsx
+++ b/Excel/GiftPackEquipConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -1385,11 +1385,11 @@
       <c r="D14" s="3">
         <v>22105801</v>
       </c>
-      <c r="E14" s="3">
-        <v>10047</v>
+      <c r="E14" s="6">
+        <v>12</v>
       </c>
       <c r="F14" s="6">
-        <v>10021</v>
+        <v>10017</v>
       </c>
       <c r="G14" s="8" t="s">
         <v>10</v>
@@ -1408,11 +1408,11 @@
       <c r="D15" s="3">
         <v>22105802</v>
       </c>
-      <c r="E15" s="3">
-        <v>10047</v>
+      <c r="E15" s="6">
+        <v>12</v>
       </c>
       <c r="F15" s="6">
-        <v>10021</v>
+        <v>10017</v>
       </c>
       <c r="G15" s="8" t="s">
         <v>10</v>
@@ -1431,11 +1431,11 @@
       <c r="D16" s="3">
         <v>22105803</v>
       </c>
-      <c r="E16" s="3">
-        <v>3</v>
+      <c r="E16" s="6">
+        <v>12</v>
       </c>
       <c r="F16" s="6">
-        <v>10022</v>
+        <v>10018</v>
       </c>
       <c r="G16" s="8" t="s">
         <v>10</v>
@@ -1454,11 +1454,11 @@
       <c r="D17" s="3">
         <v>22105804</v>
       </c>
-      <c r="E17" s="3">
-        <v>3</v>
-      </c>
-      <c r="F17" s="6">
-        <v>10022</v>
+      <c r="E17" s="6">
+        <v>18</v>
+      </c>
+      <c r="F17" s="7">
+        <v>11</v>
       </c>
       <c r="G17" s="8" t="s">
         <v>10</v>
@@ -1477,11 +1477,11 @@
       <c r="D18" s="3">
         <v>22105805</v>
       </c>
-      <c r="E18" s="3">
-        <v>8</v>
-      </c>
-      <c r="F18" s="6">
-        <v>10017</v>
+      <c r="E18" s="6">
+        <v>22</v>
+      </c>
+      <c r="F18" s="7">
+        <v>14</v>
       </c>
       <c r="G18" s="8" t="s">
         <v>10</v>
@@ -1500,11 +1500,11 @@
       <c r="D19" s="3">
         <v>22105807</v>
       </c>
-      <c r="E19" s="3">
-        <v>3</v>
-      </c>
-      <c r="F19" s="6">
-        <v>10022</v>
+      <c r="E19" s="6">
+        <v>22</v>
+      </c>
+      <c r="F19" s="7">
+        <v>14</v>
       </c>
       <c r="G19" s="8" t="s">
         <v>10</v>
@@ -1523,11 +1523,11 @@
       <c r="D20" s="3">
         <v>22105809</v>
       </c>
-      <c r="E20" s="3">
-        <v>12</v>
-      </c>
-      <c r="F20" s="6">
-        <v>10018</v>
+      <c r="E20" s="6">
+        <v>18</v>
+      </c>
+      <c r="F20" s="7">
+        <v>6</v>
       </c>
       <c r="G20" s="8" t="s">
         <v>10</v>
@@ -1546,11 +1546,11 @@
       <c r="D21" s="3">
         <v>22105810</v>
       </c>
-      <c r="E21" s="3">
-        <v>12</v>
-      </c>
-      <c r="F21" s="6">
-        <v>10018</v>
+      <c r="E21" s="6">
+        <v>18</v>
+      </c>
+      <c r="F21" s="7">
+        <v>6</v>
       </c>
       <c r="G21" s="8" t="s">
         <v>10</v>

--- a/Excel/GiftPackEquipConfig.xlsx
+++ b/Excel/GiftPackEquipConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="35">
   <si>
     <t>#</t>
   </si>
@@ -123,6 +123,15 @@
   </si>
   <si>
     <t>金色法师攻击套</t>
+  </si>
+  <si>
+    <t>战士暗金</t>
+  </si>
+  <si>
+    <t>法师暗金</t>
+  </si>
+  <si>
+    <t>道士暗金</t>
   </si>
 </sst>
 </file>
@@ -769,7 +778,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -780,6 +789,7 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -1100,7 +1110,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I111"/>
+  <dimension ref="A1:I130"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
@@ -1207,7 +1217,7 @@
       <c r="F6" s="3">
         <v>10</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="G6" s="9" t="s">
         <v>10</v>
       </c>
       <c r="H6" s="3">
@@ -1230,7 +1240,7 @@
       <c r="F7" s="3">
         <v>10</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="G7" s="9" t="s">
         <v>10</v>
       </c>
       <c r="H7" s="3">
@@ -1253,7 +1263,7 @@
       <c r="F8" s="3">
         <v>10</v>
       </c>
-      <c r="G8" s="8" t="s">
+      <c r="G8" s="9" t="s">
         <v>10</v>
       </c>
       <c r="H8" s="3">
@@ -1276,7 +1286,7 @@
       <c r="F9" s="3">
         <v>10</v>
       </c>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="9" t="s">
         <v>10</v>
       </c>
       <c r="H9" s="3">
@@ -1299,7 +1309,7 @@
       <c r="F10" s="3">
         <v>13</v>
       </c>
-      <c r="G10" s="8" t="s">
+      <c r="G10" s="9" t="s">
         <v>10</v>
       </c>
       <c r="H10" s="3">
@@ -1322,7 +1332,7 @@
       <c r="F11" s="6">
         <v>10005</v>
       </c>
-      <c r="G11" s="8" t="s">
+      <c r="G11" s="9" t="s">
         <v>10</v>
       </c>
       <c r="H11" s="3">
@@ -1345,7 +1355,7 @@
       <c r="F12" s="6">
         <v>10006</v>
       </c>
-      <c r="G12" s="8" t="s">
+      <c r="G12" s="9" t="s">
         <v>10</v>
       </c>
       <c r="H12" s="3">
@@ -1368,7 +1378,7 @@
       <c r="F13" s="6">
         <v>10006</v>
       </c>
-      <c r="G13" s="8" t="s">
+      <c r="G13" s="9" t="s">
         <v>10</v>
       </c>
       <c r="H13" s="3">
@@ -1391,7 +1401,7 @@
       <c r="F14" s="6">
         <v>10017</v>
       </c>
-      <c r="G14" s="8" t="s">
+      <c r="G14" s="9" t="s">
         <v>10</v>
       </c>
       <c r="H14" s="3">
@@ -1414,7 +1424,7 @@
       <c r="F15" s="6">
         <v>10017</v>
       </c>
-      <c r="G15" s="8" t="s">
+      <c r="G15" s="9" t="s">
         <v>10</v>
       </c>
       <c r="H15" s="3">
@@ -1437,7 +1447,7 @@
       <c r="F16" s="6">
         <v>10018</v>
       </c>
-      <c r="G16" s="8" t="s">
+      <c r="G16" s="9" t="s">
         <v>10</v>
       </c>
       <c r="H16" s="3">
@@ -1460,7 +1470,7 @@
       <c r="F17" s="7">
         <v>11</v>
       </c>
-      <c r="G17" s="8" t="s">
+      <c r="G17" s="9" t="s">
         <v>10</v>
       </c>
       <c r="H17" s="3">
@@ -1483,7 +1493,7 @@
       <c r="F18" s="7">
         <v>14</v>
       </c>
-      <c r="G18" s="8" t="s">
+      <c r="G18" s="9" t="s">
         <v>10</v>
       </c>
       <c r="H18" s="3">
@@ -1506,7 +1516,7 @@
       <c r="F19" s="7">
         <v>14</v>
       </c>
-      <c r="G19" s="8" t="s">
+      <c r="G19" s="9" t="s">
         <v>10</v>
       </c>
       <c r="H19" s="3">
@@ -1529,7 +1539,7 @@
       <c r="F20" s="7">
         <v>6</v>
       </c>
-      <c r="G20" s="8" t="s">
+      <c r="G20" s="9" t="s">
         <v>10</v>
       </c>
       <c r="H20" s="3">
@@ -1552,7 +1562,7 @@
       <c r="F21" s="7">
         <v>6</v>
       </c>
-      <c r="G21" s="8" t="s">
+      <c r="G21" s="9" t="s">
         <v>10</v>
       </c>
       <c r="H21" s="3">
@@ -1575,7 +1585,7 @@
       <c r="F22" s="3">
         <v>4</v>
       </c>
-      <c r="G22" s="8" t="s">
+      <c r="G22" s="9" t="s">
         <v>10</v>
       </c>
       <c r="H22" s="3">
@@ -1598,7 +1608,7 @@
       <c r="F23" s="3">
         <v>4</v>
       </c>
-      <c r="G23" s="8" t="s">
+      <c r="G23" s="9" t="s">
         <v>10</v>
       </c>
       <c r="H23" s="3">
@@ -1621,7 +1631,7 @@
       <c r="F24" s="3">
         <v>10037</v>
       </c>
-      <c r="G24" s="8" t="s">
+      <c r="G24" s="9" t="s">
         <v>10</v>
       </c>
       <c r="H24" s="3">
@@ -1644,7 +1654,7 @@
       <c r="F25" s="3">
         <v>10037</v>
       </c>
-      <c r="G25" s="8" t="s">
+      <c r="G25" s="9" t="s">
         <v>10</v>
       </c>
       <c r="H25" s="3">
@@ -1667,7 +1677,7 @@
       <c r="F26" s="3">
         <v>9</v>
       </c>
-      <c r="G26" s="8" t="s">
+      <c r="G26" s="9" t="s">
         <v>10</v>
       </c>
       <c r="H26" s="3">
@@ -1690,7 +1700,7 @@
       <c r="F27" s="3">
         <v>15</v>
       </c>
-      <c r="G27" s="8" t="s">
+      <c r="G27" s="9" t="s">
         <v>10</v>
       </c>
       <c r="H27" s="3">
@@ -1713,7 +1723,7 @@
       <c r="F28" s="3">
         <v>18</v>
       </c>
-      <c r="G28" s="8" t="s">
+      <c r="G28" s="9" t="s">
         <v>10</v>
       </c>
       <c r="H28" s="3">
@@ -1736,7 +1746,7 @@
       <c r="F29" s="3">
         <v>18</v>
       </c>
-      <c r="G29" s="8" t="s">
+      <c r="G29" s="9" t="s">
         <v>10</v>
       </c>
       <c r="H29" s="3">
@@ -1763,7 +1773,7 @@
       <c r="F31" s="3">
         <v>10</v>
       </c>
-      <c r="G31" s="8" t="s">
+      <c r="G31" s="9" t="s">
         <v>12</v>
       </c>
       <c r="H31" s="3">
@@ -1786,7 +1796,7 @@
       <c r="F32" s="3">
         <v>10</v>
       </c>
-      <c r="G32" s="8" t="s">
+      <c r="G32" s="9" t="s">
         <v>14</v>
       </c>
       <c r="H32" s="3">
@@ -1809,7 +1819,7 @@
       <c r="F33" s="3">
         <v>10</v>
       </c>
-      <c r="G33" s="8" t="s">
+      <c r="G33" s="9" t="s">
         <v>12</v>
       </c>
       <c r="H33" s="3">
@@ -1832,7 +1842,7 @@
       <c r="F34" s="3">
         <v>10</v>
       </c>
-      <c r="G34" s="8" t="s">
+      <c r="G34" s="9" t="s">
         <v>15</v>
       </c>
       <c r="H34" s="3">
@@ -1855,7 +1865,7 @@
       <c r="F35" s="3">
         <v>13</v>
       </c>
-      <c r="G35" s="8" t="s">
+      <c r="G35" s="9" t="s">
         <v>15</v>
       </c>
       <c r="H35" s="3">
@@ -1878,7 +1888,7 @@
       <c r="F36" s="6">
         <v>10005</v>
       </c>
-      <c r="G36" s="8" t="s">
+      <c r="G36" s="9" t="s">
         <v>15</v>
       </c>
       <c r="H36" s="3">
@@ -1901,7 +1911,7 @@
       <c r="F37" s="6">
         <v>10006</v>
       </c>
-      <c r="G37" s="8" t="s">
+      <c r="G37" s="9" t="s">
         <v>15</v>
       </c>
       <c r="H37" s="3">
@@ -1924,7 +1934,7 @@
       <c r="F38" s="6">
         <v>10006</v>
       </c>
-      <c r="G38" s="8" t="s">
+      <c r="G38" s="9" t="s">
         <v>15</v>
       </c>
       <c r="H38" s="3">
@@ -1952,7 +1962,7 @@
       <c r="F40" s="6">
         <v>10017</v>
       </c>
-      <c r="G40" s="8" t="s">
+      <c r="G40" s="9" t="s">
         <v>16</v>
       </c>
       <c r="H40" s="3">
@@ -1975,7 +1985,7 @@
       <c r="F41" s="6">
         <v>10017</v>
       </c>
-      <c r="G41" s="8" t="s">
+      <c r="G41" s="9" t="s">
         <v>17</v>
       </c>
       <c r="H41" s="3">
@@ -1998,7 +2008,7 @@
       <c r="F42" s="6">
         <v>10018</v>
       </c>
-      <c r="G42" s="8" t="s">
+      <c r="G42" s="9" t="s">
         <v>16</v>
       </c>
       <c r="H42" s="3">
@@ -2021,7 +2031,7 @@
       <c r="F43" s="7">
         <v>11</v>
       </c>
-      <c r="G43" s="8" t="s">
+      <c r="G43" s="9" t="s">
         <v>17</v>
       </c>
       <c r="H43" s="3">
@@ -2044,7 +2054,7 @@
       <c r="F44" s="7">
         <v>14</v>
       </c>
-      <c r="G44" s="8" t="s">
+      <c r="G44" s="9" t="s">
         <v>17</v>
       </c>
       <c r="H44" s="3">
@@ -2067,7 +2077,7 @@
       <c r="F45" s="7">
         <v>14</v>
       </c>
-      <c r="G45" s="8" t="s">
+      <c r="G45" s="9" t="s">
         <v>17</v>
       </c>
       <c r="H45" s="3">
@@ -2090,7 +2100,7 @@
       <c r="F46" s="7">
         <v>6</v>
       </c>
-      <c r="G46" s="8" t="s">
+      <c r="G46" s="9" t="s">
         <v>17</v>
       </c>
       <c r="H46" s="3">
@@ -2113,7 +2123,7 @@
       <c r="F47" s="7">
         <v>6</v>
       </c>
-      <c r="G47" s="8" t="s">
+      <c r="G47" s="9" t="s">
         <v>17</v>
       </c>
       <c r="H47" s="3">
@@ -2140,7 +2150,7 @@
       <c r="F49" s="3">
         <v>4</v>
       </c>
-      <c r="G49" s="8" t="s">
+      <c r="G49" s="9" t="s">
         <v>18</v>
       </c>
       <c r="H49" s="3">
@@ -2163,7 +2173,7 @@
       <c r="F50" s="3">
         <v>4</v>
       </c>
-      <c r="G50" s="8" t="s">
+      <c r="G50" s="9" t="s">
         <v>14</v>
       </c>
       <c r="H50" s="3">
@@ -2186,7 +2196,7 @@
       <c r="F51" s="3">
         <v>10037</v>
       </c>
-      <c r="G51" s="8" t="s">
+      <c r="G51" s="9" t="s">
         <v>18</v>
       </c>
       <c r="H51" s="3">
@@ -2209,7 +2219,7 @@
       <c r="F52" s="3">
         <v>10037</v>
       </c>
-      <c r="G52" s="8" t="s">
+      <c r="G52" s="9" t="s">
         <v>14</v>
       </c>
       <c r="H52" s="3">
@@ -2232,7 +2242,7 @@
       <c r="F53" s="3">
         <v>9</v>
       </c>
-      <c r="G53" s="8" t="s">
+      <c r="G53" s="9" t="s">
         <v>14</v>
       </c>
       <c r="H53" s="3">
@@ -2255,7 +2265,7 @@
       <c r="F54" s="3">
         <v>15</v>
       </c>
-      <c r="G54" s="8" t="s">
+      <c r="G54" s="9" t="s">
         <v>14</v>
       </c>
       <c r="H54" s="3">
@@ -2278,7 +2288,7 @@
       <c r="F55" s="3">
         <v>18</v>
       </c>
-      <c r="G55" s="8" t="s">
+      <c r="G55" s="9" t="s">
         <v>14</v>
       </c>
       <c r="H55" s="3">
@@ -2301,7 +2311,7 @@
       <c r="F56" s="3">
         <v>18</v>
       </c>
-      <c r="G56" s="8" t="s">
+      <c r="G56" s="9" t="s">
         <v>14</v>
       </c>
       <c r="H56" s="3">
@@ -2324,7 +2334,7 @@
       <c r="F57" s="3">
         <v>4</v>
       </c>
-      <c r="G57" s="8" t="s">
+      <c r="G57" s="9" t="s">
         <v>19</v>
       </c>
       <c r="H57" s="3">
@@ -2347,7 +2357,7 @@
       <c r="F58" s="3">
         <v>4</v>
       </c>
-      <c r="G58" s="8" t="s">
+      <c r="G58" s="9" t="s">
         <v>19</v>
       </c>
       <c r="H58" s="3">
@@ -2370,7 +2380,7 @@
       <c r="F61" s="6">
         <v>11002</v>
       </c>
-      <c r="G61" s="8" t="s">
+      <c r="G61" s="9" t="s">
         <v>22</v>
       </c>
       <c r="H61" s="3">
@@ -2393,7 +2403,7 @@
       <c r="F62" s="6">
         <v>11002</v>
       </c>
-      <c r="G62" s="8" t="s">
+      <c r="G62" s="9" t="s">
         <v>22</v>
       </c>
       <c r="H62" s="3">
@@ -2416,7 +2426,7 @@
       <c r="F63" s="6">
         <v>11005</v>
       </c>
-      <c r="G63" s="8" t="s">
+      <c r="G63" s="9" t="s">
         <v>22</v>
       </c>
       <c r="H63" s="3">
@@ -2439,7 +2449,7 @@
       <c r="F64" s="6">
         <v>11005</v>
       </c>
-      <c r="G64" s="8" t="s">
+      <c r="G64" s="9" t="s">
         <v>22</v>
       </c>
       <c r="H64" s="3">
@@ -2462,7 +2472,7 @@
       <c r="F65" s="6">
         <v>11006</v>
       </c>
-      <c r="G65" s="8" t="s">
+      <c r="G65" s="9" t="s">
         <v>22</v>
       </c>
       <c r="H65" s="3">
@@ -2485,7 +2495,7 @@
       <c r="F66" s="6">
         <v>11008</v>
       </c>
-      <c r="G66" s="8" t="s">
+      <c r="G66" s="9" t="s">
         <v>22</v>
       </c>
       <c r="H66" s="3">
@@ -2508,7 +2518,7 @@
       <c r="F67" s="6">
         <v>11010</v>
       </c>
-      <c r="G67" s="8" t="s">
+      <c r="G67" s="9" t="s">
         <v>22</v>
       </c>
       <c r="H67" s="3">
@@ -2531,7 +2541,7 @@
       <c r="F68" s="6">
         <v>11010</v>
       </c>
-      <c r="G68" s="8" t="s">
+      <c r="G68" s="9" t="s">
         <v>22</v>
       </c>
       <c r="H68" s="3">
@@ -2559,7 +2569,7 @@
       <c r="F70" s="6">
         <v>12002</v>
       </c>
-      <c r="G70" s="8" t="s">
+      <c r="G70" s="9" t="s">
         <v>24</v>
       </c>
       <c r="H70" s="3">
@@ -2582,7 +2592,7 @@
       <c r="F71" s="6">
         <v>12002</v>
       </c>
-      <c r="G71" s="8" t="s">
+      <c r="G71" s="9" t="s">
         <v>24</v>
       </c>
       <c r="H71" s="3">
@@ -2605,7 +2615,7 @@
       <c r="F72" s="6">
         <v>12005</v>
       </c>
-      <c r="G72" s="8" t="s">
+      <c r="G72" s="9" t="s">
         <v>24</v>
       </c>
       <c r="H72" s="3">
@@ -2628,7 +2638,7 @@
       <c r="F73" s="6">
         <v>12005</v>
       </c>
-      <c r="G73" s="8" t="s">
+      <c r="G73" s="9" t="s">
         <v>24</v>
       </c>
       <c r="H73" s="3">
@@ -2651,7 +2661,7 @@
       <c r="F74" s="6">
         <v>12006</v>
       </c>
-      <c r="G74" s="8" t="s">
+      <c r="G74" s="9" t="s">
         <v>24</v>
       </c>
       <c r="H74" s="3">
@@ -2674,7 +2684,7 @@
       <c r="F75" s="6">
         <v>12008</v>
       </c>
-      <c r="G75" s="8" t="s">
+      <c r="G75" s="9" t="s">
         <v>24</v>
       </c>
       <c r="H75" s="3">
@@ -2697,7 +2707,7 @@
       <c r="F76" s="6">
         <v>12110</v>
       </c>
-      <c r="G76" s="8" t="s">
+      <c r="G76" s="9" t="s">
         <v>24</v>
       </c>
       <c r="H76" s="3">
@@ -2720,7 +2730,7 @@
       <c r="F77" s="6">
         <v>12110</v>
       </c>
-      <c r="G77" s="8" t="s">
+      <c r="G77" s="9" t="s">
         <v>24</v>
       </c>
       <c r="H77" s="3">
@@ -2748,7 +2758,7 @@
       <c r="F79" s="6">
         <v>13002</v>
       </c>
-      <c r="G79" s="8" t="s">
+      <c r="G79" s="9" t="s">
         <v>26</v>
       </c>
       <c r="H79" s="3">
@@ -2771,7 +2781,7 @@
       <c r="F80" s="6">
         <v>13002</v>
       </c>
-      <c r="G80" s="8" t="s">
+      <c r="G80" s="9" t="s">
         <v>26</v>
       </c>
       <c r="H80" s="3">
@@ -2794,7 +2804,7 @@
       <c r="F81" s="6">
         <v>13005</v>
       </c>
-      <c r="G81" s="8" t="s">
+      <c r="G81" s="9" t="s">
         <v>26</v>
       </c>
       <c r="H81" s="3">
@@ -2817,7 +2827,7 @@
       <c r="F82" s="6">
         <v>13005</v>
       </c>
-      <c r="G82" s="8" t="s">
+      <c r="G82" s="9" t="s">
         <v>26</v>
       </c>
       <c r="H82" s="3">
@@ -2840,7 +2850,7 @@
       <c r="F83" s="6">
         <v>13008</v>
       </c>
-      <c r="G83" s="8" t="s">
+      <c r="G83" s="9" t="s">
         <v>26</v>
       </c>
       <c r="H83" s="3">
@@ -2863,7 +2873,7 @@
       <c r="F84" s="6">
         <v>13009</v>
       </c>
-      <c r="G84" s="8" t="s">
+      <c r="G84" s="9" t="s">
         <v>26</v>
       </c>
       <c r="H84" s="3">
@@ -2886,7 +2896,7 @@
       <c r="F85" s="6">
         <v>13010</v>
       </c>
-      <c r="G85" s="8" t="s">
+      <c r="G85" s="9" t="s">
         <v>26</v>
       </c>
       <c r="H85" s="3">
@@ -2909,7 +2919,7 @@
       <c r="F86" s="6">
         <v>13010</v>
       </c>
-      <c r="G86" s="8" t="s">
+      <c r="G86" s="9" t="s">
         <v>26</v>
       </c>
       <c r="H86" s="3">
@@ -2932,7 +2942,7 @@
       <c r="F88" s="6">
         <v>11002</v>
       </c>
-      <c r="G88" s="8" t="s">
+      <c r="G88" s="9" t="s">
         <v>28</v>
       </c>
       <c r="H88" s="3">
@@ -2955,7 +2965,7 @@
       <c r="F89" s="6">
         <v>11002</v>
       </c>
-      <c r="G89" s="8" t="s">
+      <c r="G89" s="9" t="s">
         <v>28</v>
       </c>
       <c r="H89" s="3">
@@ -2978,7 +2988,7 @@
       <c r="F90" s="6">
         <v>11005</v>
       </c>
-      <c r="G90" s="8" t="s">
+      <c r="G90" s="9" t="s">
         <v>28</v>
       </c>
       <c r="H90" s="3">
@@ -3001,7 +3011,7 @@
       <c r="F91" s="6">
         <v>11005</v>
       </c>
-      <c r="G91" s="8" t="s">
+      <c r="G91" s="9" t="s">
         <v>28</v>
       </c>
       <c r="H91" s="3">
@@ -3024,7 +3034,7 @@
       <c r="F92" s="6">
         <v>11006</v>
       </c>
-      <c r="G92" s="8" t="s">
+      <c r="G92" s="9" t="s">
         <v>28</v>
       </c>
       <c r="H92" s="3">
@@ -3047,7 +3057,7 @@
       <c r="F93" s="6">
         <v>11008</v>
       </c>
-      <c r="G93" s="8" t="s">
+      <c r="G93" s="9" t="s">
         <v>28</v>
       </c>
       <c r="H93" s="3">
@@ -3070,7 +3080,7 @@
       <c r="F94" s="6">
         <v>11010</v>
       </c>
-      <c r="G94" s="8" t="s">
+      <c r="G94" s="9" t="s">
         <v>28</v>
       </c>
       <c r="H94" s="3">
@@ -3093,7 +3103,7 @@
       <c r="F95" s="6">
         <v>11010</v>
       </c>
-      <c r="G95" s="8" t="s">
+      <c r="G95" s="9" t="s">
         <v>28</v>
       </c>
       <c r="H95" s="3">
@@ -3116,7 +3126,7 @@
       <c r="F96" s="6">
         <v>12002</v>
       </c>
-      <c r="G96" s="8" t="s">
+      <c r="G96" s="9" t="s">
         <v>30</v>
       </c>
       <c r="H96" s="3">
@@ -3139,7 +3149,7 @@
       <c r="F97" s="6">
         <v>12002</v>
       </c>
-      <c r="G97" s="8" t="s">
+      <c r="G97" s="9" t="s">
         <v>30</v>
       </c>
       <c r="H97" s="3">
@@ -3162,7 +3172,7 @@
       <c r="F98" s="6">
         <v>12005</v>
       </c>
-      <c r="G98" s="8" t="s">
+      <c r="G98" s="9" t="s">
         <v>30</v>
       </c>
       <c r="H98" s="3">
@@ -3185,7 +3195,7 @@
       <c r="F99" s="6">
         <v>12005</v>
       </c>
-      <c r="G99" s="8" t="s">
+      <c r="G99" s="9" t="s">
         <v>30</v>
       </c>
       <c r="H99" s="3">
@@ -3208,7 +3218,7 @@
       <c r="F100" s="6">
         <v>12006</v>
       </c>
-      <c r="G100" s="8" t="s">
+      <c r="G100" s="9" t="s">
         <v>30</v>
       </c>
       <c r="H100" s="3">
@@ -3231,7 +3241,7 @@
       <c r="F101" s="6">
         <v>12008</v>
       </c>
-      <c r="G101" s="8" t="s">
+      <c r="G101" s="9" t="s">
         <v>30</v>
       </c>
       <c r="H101" s="3">
@@ -3254,7 +3264,7 @@
       <c r="F102" s="6">
         <v>12110</v>
       </c>
-      <c r="G102" s="8" t="s">
+      <c r="G102" s="9" t="s">
         <v>30</v>
       </c>
       <c r="H102" s="3">
@@ -3277,7 +3287,7 @@
       <c r="F103" s="6">
         <v>12110</v>
       </c>
-      <c r="G103" s="8" t="s">
+      <c r="G103" s="9" t="s">
         <v>30</v>
       </c>
       <c r="H103" s="3">
@@ -3292,40 +3302,567 @@
       <c r="E104" s="6"/>
       <c r="F104" s="6"/>
     </row>
-    <row r="105" customHeight="1" spans="4:6">
-      <c r="D105" s="3"/>
-      <c r="E105" s="6"/>
-      <c r="F105" s="6"/>
-    </row>
-    <row r="106" customHeight="1" spans="4:6">
-      <c r="D106" s="3"/>
-      <c r="E106" s="6"/>
-      <c r="F106" s="6"/>
-    </row>
-    <row r="107" customHeight="1" spans="4:6">
-      <c r="D107" s="3"/>
-      <c r="E107" s="6"/>
-      <c r="F107" s="6"/>
-    </row>
-    <row r="108" customHeight="1" spans="4:6">
-      <c r="D108" s="3"/>
-      <c r="E108" s="6"/>
-      <c r="F108" s="6"/>
-    </row>
-    <row r="109" customHeight="1" spans="4:6">
-      <c r="D109" s="3"/>
-      <c r="E109" s="6"/>
-      <c r="F109" s="6"/>
-    </row>
-    <row r="110" customHeight="1" spans="4:6">
-      <c r="D110" s="3"/>
-      <c r="E110" s="6"/>
-      <c r="F110" s="6"/>
-    </row>
-    <row r="111" customHeight="1" spans="4:6">
-      <c r="D111" s="3"/>
-      <c r="E111" s="6"/>
-      <c r="F111" s="6"/>
+    <row r="105" customHeight="1" spans="3:9">
+      <c r="C105" s="1">
+        <v>151</v>
+      </c>
+      <c r="D105" s="3">
+        <v>21305801</v>
+      </c>
+      <c r="E105" s="6">
+        <v>21002</v>
+      </c>
+      <c r="F105" s="6">
+        <v>21002</v>
+      </c>
+      <c r="G105" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="H105" s="3">
+        <v>8</v>
+      </c>
+      <c r="I105" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="106" customHeight="1" spans="3:9">
+      <c r="C106" s="1">
+        <v>152</v>
+      </c>
+      <c r="D106" s="3">
+        <v>21305801</v>
+      </c>
+      <c r="E106" s="6">
+        <v>21002</v>
+      </c>
+      <c r="F106" s="6">
+        <v>21002</v>
+      </c>
+      <c r="G106" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="H106" s="3">
+        <v>8</v>
+      </c>
+      <c r="I106" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="107" customHeight="1" spans="3:9">
+      <c r="C107" s="1">
+        <v>153</v>
+      </c>
+      <c r="D107" s="3">
+        <v>21305801</v>
+      </c>
+      <c r="E107" s="6">
+        <v>21005</v>
+      </c>
+      <c r="F107" s="6">
+        <v>21005</v>
+      </c>
+      <c r="G107" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="H107" s="3">
+        <v>8</v>
+      </c>
+      <c r="I107" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="108" customHeight="1" spans="3:9">
+      <c r="C108" s="1">
+        <v>154</v>
+      </c>
+      <c r="D108" s="3">
+        <v>21305801</v>
+      </c>
+      <c r="E108" s="6">
+        <v>21005</v>
+      </c>
+      <c r="F108" s="6">
+        <v>21005</v>
+      </c>
+      <c r="G108" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="H108" s="3">
+        <v>8</v>
+      </c>
+      <c r="I108" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="109" customHeight="1" spans="3:9">
+      <c r="C109" s="1">
+        <v>155</v>
+      </c>
+      <c r="D109" s="3">
+        <v>21305801</v>
+      </c>
+      <c r="E109" s="6">
+        <v>21008</v>
+      </c>
+      <c r="F109" s="6">
+        <v>21008</v>
+      </c>
+      <c r="G109" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="H109" s="3">
+        <v>8</v>
+      </c>
+      <c r="I109" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="110" customHeight="1" spans="3:9">
+      <c r="C110" s="1">
+        <v>156</v>
+      </c>
+      <c r="D110" s="3">
+        <v>21305801</v>
+      </c>
+      <c r="E110" s="6">
+        <v>21010</v>
+      </c>
+      <c r="F110" s="6">
+        <v>21010</v>
+      </c>
+      <c r="G110" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="H110" s="3">
+        <v>8</v>
+      </c>
+      <c r="I110" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="111" customHeight="1" spans="3:9">
+      <c r="C111" s="1">
+        <v>157</v>
+      </c>
+      <c r="D111" s="3">
+        <v>21305801</v>
+      </c>
+      <c r="E111" s="6">
+        <v>21011</v>
+      </c>
+      <c r="F111" s="6">
+        <v>21011</v>
+      </c>
+      <c r="G111" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="H111" s="3">
+        <v>8</v>
+      </c>
+      <c r="I111" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="112" customHeight="1" spans="3:9">
+      <c r="C112" s="1">
+        <v>158</v>
+      </c>
+      <c r="D112" s="3">
+        <v>21305801</v>
+      </c>
+      <c r="E112" s="6">
+        <v>21011</v>
+      </c>
+      <c r="F112" s="6">
+        <v>21011</v>
+      </c>
+      <c r="G112" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="H112" s="3">
+        <v>8</v>
+      </c>
+      <c r="I112" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="113" customHeight="1" spans="4:6">
+      <c r="D113" s="3"/>
+      <c r="E113" s="6"/>
+      <c r="F113" s="6"/>
+    </row>
+    <row r="114" customHeight="1" spans="3:9">
+      <c r="C114" s="1">
+        <v>161</v>
+      </c>
+      <c r="D114" s="3">
+        <v>22305801</v>
+      </c>
+      <c r="E114" s="6">
+        <v>21002</v>
+      </c>
+      <c r="F114" s="6">
+        <v>21002</v>
+      </c>
+      <c r="G114" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H114" s="3">
+        <v>8</v>
+      </c>
+      <c r="I114" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="115" customHeight="1" spans="3:9">
+      <c r="C115" s="1">
+        <v>162</v>
+      </c>
+      <c r="D115" s="3">
+        <v>22305802</v>
+      </c>
+      <c r="E115" s="6">
+        <v>21002</v>
+      </c>
+      <c r="F115" s="6">
+        <v>21002</v>
+      </c>
+      <c r="G115" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H115" s="3">
+        <v>8</v>
+      </c>
+      <c r="I115" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="116" customHeight="1" spans="3:9">
+      <c r="C116" s="1">
+        <v>163</v>
+      </c>
+      <c r="D116" s="3">
+        <v>22305803</v>
+      </c>
+      <c r="E116" s="6">
+        <v>21005</v>
+      </c>
+      <c r="F116" s="6">
+        <v>21005</v>
+      </c>
+      <c r="G116" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H116" s="3">
+        <v>8</v>
+      </c>
+      <c r="I116" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="117" customHeight="1" spans="3:9">
+      <c r="C117" s="1">
+        <v>164</v>
+      </c>
+      <c r="D117" s="3">
+        <v>22305804</v>
+      </c>
+      <c r="E117" s="6">
+        <v>21005</v>
+      </c>
+      <c r="F117" s="6">
+        <v>21005</v>
+      </c>
+      <c r="G117" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H117" s="3">
+        <v>8</v>
+      </c>
+      <c r="I117" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="118" customHeight="1" spans="3:9">
+      <c r="C118" s="1">
+        <v>165</v>
+      </c>
+      <c r="D118" s="3">
+        <v>22305805</v>
+      </c>
+      <c r="E118" s="6">
+        <v>21008</v>
+      </c>
+      <c r="F118" s="6">
+        <v>21008</v>
+      </c>
+      <c r="G118" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H118" s="3">
+        <v>8</v>
+      </c>
+      <c r="I118" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="119" customHeight="1" spans="3:9">
+      <c r="C119" s="1">
+        <v>166</v>
+      </c>
+      <c r="D119" s="3">
+        <v>22305807</v>
+      </c>
+      <c r="E119" s="6">
+        <v>21010</v>
+      </c>
+      <c r="F119" s="6">
+        <v>21010</v>
+      </c>
+      <c r="G119" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H119" s="3">
+        <v>8</v>
+      </c>
+      <c r="I119" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="120" customHeight="1" spans="3:9">
+      <c r="C120" s="1">
+        <v>167</v>
+      </c>
+      <c r="D120" s="3">
+        <v>22305809</v>
+      </c>
+      <c r="E120" s="6">
+        <v>21011</v>
+      </c>
+      <c r="F120" s="6">
+        <v>21011</v>
+      </c>
+      <c r="G120" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H120" s="3">
+        <v>8</v>
+      </c>
+      <c r="I120" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="121" customHeight="1" spans="3:9">
+      <c r="C121" s="1">
+        <v>168</v>
+      </c>
+      <c r="D121" s="3">
+        <v>22305810</v>
+      </c>
+      <c r="E121" s="6">
+        <v>21011</v>
+      </c>
+      <c r="F121" s="6">
+        <v>21011</v>
+      </c>
+      <c r="G121" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H121" s="3">
+        <v>8</v>
+      </c>
+      <c r="I121" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="122" customHeight="1" spans="4:6">
+      <c r="D122" s="3"/>
+      <c r="E122" s="6"/>
+      <c r="F122" s="6"/>
+    </row>
+    <row r="123" customHeight="1" spans="3:9">
+      <c r="C123" s="1">
+        <v>171</v>
+      </c>
+      <c r="D123" s="3">
+        <v>23305801</v>
+      </c>
+      <c r="E123" s="6">
+        <v>21002</v>
+      </c>
+      <c r="F123" s="6">
+        <v>21002</v>
+      </c>
+      <c r="G123" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H123" s="3">
+        <v>8</v>
+      </c>
+      <c r="I123" s="8" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="124" customHeight="1" spans="3:9">
+      <c r="C124" s="1">
+        <v>172</v>
+      </c>
+      <c r="D124" s="3">
+        <v>23305802</v>
+      </c>
+      <c r="E124" s="6">
+        <v>21002</v>
+      </c>
+      <c r="F124" s="6">
+        <v>21002</v>
+      </c>
+      <c r="G124" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H124" s="3">
+        <v>8</v>
+      </c>
+      <c r="I124" s="8" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="125" customHeight="1" spans="3:9">
+      <c r="C125" s="1">
+        <v>173</v>
+      </c>
+      <c r="D125" s="3">
+        <v>23305803</v>
+      </c>
+      <c r="E125" s="6">
+        <v>21005</v>
+      </c>
+      <c r="F125" s="6">
+        <v>21005</v>
+      </c>
+      <c r="G125" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H125" s="3">
+        <v>8</v>
+      </c>
+      <c r="I125" s="8" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="126" customHeight="1" spans="3:9">
+      <c r="C126" s="1">
+        <v>174</v>
+      </c>
+      <c r="D126" s="3">
+        <v>23305804</v>
+      </c>
+      <c r="E126" s="6">
+        <v>21005</v>
+      </c>
+      <c r="F126" s="6">
+        <v>21005</v>
+      </c>
+      <c r="G126" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H126" s="3">
+        <v>8</v>
+      </c>
+      <c r="I126" s="8" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="127" customHeight="1" spans="3:9">
+      <c r="C127" s="1">
+        <v>175</v>
+      </c>
+      <c r="D127" s="3">
+        <v>23305805</v>
+      </c>
+      <c r="E127" s="6">
+        <v>21008</v>
+      </c>
+      <c r="F127" s="6">
+        <v>21008</v>
+      </c>
+      <c r="G127" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H127" s="3">
+        <v>8</v>
+      </c>
+      <c r="I127" s="8" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="128" customHeight="1" spans="3:9">
+      <c r="C128" s="1">
+        <v>176</v>
+      </c>
+      <c r="D128" s="3">
+        <v>23305807</v>
+      </c>
+      <c r="E128" s="6">
+        <v>21010</v>
+      </c>
+      <c r="F128" s="6">
+        <v>21010</v>
+      </c>
+      <c r="G128" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H128" s="3">
+        <v>8</v>
+      </c>
+      <c r="I128" s="8" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="129" customHeight="1" spans="3:9">
+      <c r="C129" s="1">
+        <v>177</v>
+      </c>
+      <c r="D129" s="3">
+        <v>23305809</v>
+      </c>
+      <c r="E129" s="6">
+        <v>21011</v>
+      </c>
+      <c r="F129" s="6">
+        <v>21011</v>
+      </c>
+      <c r="G129" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H129" s="3">
+        <v>8</v>
+      </c>
+      <c r="I129" s="8" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="130" customHeight="1" spans="3:9">
+      <c r="C130" s="1">
+        <v>178</v>
+      </c>
+      <c r="D130" s="3">
+        <v>23305810</v>
+      </c>
+      <c r="E130" s="6">
+        <v>21011</v>
+      </c>
+      <c r="F130" s="6">
+        <v>21011</v>
+      </c>
+      <c r="G130" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H130" s="3">
+        <v>8</v>
+      </c>
+      <c r="I130" s="8" t="s">
+        <v>34</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Excel/GiftPackEquipConfig.xlsx
+++ b/Excel/GiftPackEquipConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="38">
   <si>
     <t>#</t>
   </si>
@@ -125,10 +125,19 @@
     <t>金色法师攻击套</t>
   </si>
   <si>
+    <t>2001,2001,2010,2010,2005,2005,2005,2003</t>
+  </si>
+  <si>
     <t>战士暗金</t>
   </si>
   <si>
+    <t>2001,2001,2010,2010,2006,2006,2006,2003</t>
+  </si>
+  <si>
     <t>法师暗金</t>
+  </si>
+  <si>
+    <t>2001,2001,2010,2010,2007,2007,2007,2003</t>
   </si>
   <si>
     <t>道士暗金</t>
@@ -3316,13 +3325,13 @@
         <v>21002</v>
       </c>
       <c r="G105" s="9" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="H105" s="3">
         <v>8</v>
       </c>
       <c r="I105" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="106" customHeight="1" spans="3:9">
@@ -3339,13 +3348,13 @@
         <v>21002</v>
       </c>
       <c r="G106" s="9" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="H106" s="3">
         <v>8</v>
       </c>
       <c r="I106" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="107" customHeight="1" spans="3:9">
@@ -3362,13 +3371,13 @@
         <v>21005</v>
       </c>
       <c r="G107" s="9" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="H107" s="3">
         <v>8</v>
       </c>
       <c r="I107" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="108" customHeight="1" spans="3:9">
@@ -3385,13 +3394,13 @@
         <v>21005</v>
       </c>
       <c r="G108" s="9" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="H108" s="3">
         <v>8</v>
       </c>
       <c r="I108" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="109" customHeight="1" spans="3:9">
@@ -3408,13 +3417,13 @@
         <v>21008</v>
       </c>
       <c r="G109" s="9" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="H109" s="3">
         <v>8</v>
       </c>
       <c r="I109" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="110" customHeight="1" spans="3:9">
@@ -3431,13 +3440,13 @@
         <v>21010</v>
       </c>
       <c r="G110" s="9" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="H110" s="3">
         <v>8</v>
       </c>
       <c r="I110" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="111" customHeight="1" spans="3:9">
@@ -3454,13 +3463,13 @@
         <v>21011</v>
       </c>
       <c r="G111" s="9" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="H111" s="3">
         <v>8</v>
       </c>
       <c r="I111" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="112" customHeight="1" spans="3:9">
@@ -3477,13 +3486,13 @@
         <v>21011</v>
       </c>
       <c r="G112" s="9" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="H112" s="3">
         <v>8</v>
       </c>
       <c r="I112" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="113" customHeight="1" spans="4:6">
@@ -3505,13 +3514,13 @@
         <v>21002</v>
       </c>
       <c r="G114" s="9" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="H114" s="3">
         <v>8</v>
       </c>
       <c r="I114" s="8" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="115" customHeight="1" spans="3:9">
@@ -3528,13 +3537,13 @@
         <v>21002</v>
       </c>
       <c r="G115" s="9" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="H115" s="3">
         <v>8</v>
       </c>
       <c r="I115" s="8" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="116" customHeight="1" spans="3:9">
@@ -3551,13 +3560,13 @@
         <v>21005</v>
       </c>
       <c r="G116" s="9" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="H116" s="3">
         <v>8</v>
       </c>
       <c r="I116" s="8" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="117" customHeight="1" spans="3:9">
@@ -3574,13 +3583,13 @@
         <v>21005</v>
       </c>
       <c r="G117" s="9" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="H117" s="3">
         <v>8</v>
       </c>
       <c r="I117" s="8" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="118" customHeight="1" spans="3:9">
@@ -3597,13 +3606,13 @@
         <v>21008</v>
       </c>
       <c r="G118" s="9" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="H118" s="3">
         <v>8</v>
       </c>
       <c r="I118" s="8" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="119" customHeight="1" spans="3:9">
@@ -3620,13 +3629,13 @@
         <v>21010</v>
       </c>
       <c r="G119" s="9" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="H119" s="3">
         <v>8</v>
       </c>
       <c r="I119" s="8" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="120" customHeight="1" spans="3:9">
@@ -3643,13 +3652,13 @@
         <v>21011</v>
       </c>
       <c r="G120" s="9" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="H120" s="3">
         <v>8</v>
       </c>
       <c r="I120" s="8" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="121" customHeight="1" spans="3:9">
@@ -3666,13 +3675,13 @@
         <v>21011</v>
       </c>
       <c r="G121" s="9" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="H121" s="3">
         <v>8</v>
       </c>
       <c r="I121" s="8" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="122" customHeight="1" spans="4:6">
@@ -3694,13 +3703,13 @@
         <v>21002</v>
       </c>
       <c r="G123" s="9" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="H123" s="3">
         <v>8</v>
       </c>
       <c r="I123" s="8" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="124" customHeight="1" spans="3:9">
@@ -3717,13 +3726,13 @@
         <v>21002</v>
       </c>
       <c r="G124" s="9" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="H124" s="3">
         <v>8</v>
       </c>
       <c r="I124" s="8" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="125" customHeight="1" spans="3:9">
@@ -3740,13 +3749,13 @@
         <v>21005</v>
       </c>
       <c r="G125" s="9" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="H125" s="3">
         <v>8</v>
       </c>
       <c r="I125" s="8" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="126" customHeight="1" spans="3:9">
@@ -3763,13 +3772,13 @@
         <v>21005</v>
       </c>
       <c r="G126" s="9" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="H126" s="3">
         <v>8</v>
       </c>
       <c r="I126" s="8" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="127" customHeight="1" spans="3:9">
@@ -3786,13 +3795,13 @@
         <v>21008</v>
       </c>
       <c r="G127" s="9" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="H127" s="3">
         <v>8</v>
       </c>
       <c r="I127" s="8" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="128" customHeight="1" spans="3:9">
@@ -3809,13 +3818,13 @@
         <v>21010</v>
       </c>
       <c r="G128" s="9" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="H128" s="3">
         <v>8</v>
       </c>
       <c r="I128" s="8" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="129" customHeight="1" spans="3:9">
@@ -3832,13 +3841,13 @@
         <v>21011</v>
       </c>
       <c r="G129" s="9" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="H129" s="3">
         <v>8</v>
       </c>
       <c r="I129" s="8" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="130" customHeight="1" spans="3:9">
@@ -3855,13 +3864,13 @@
         <v>21011</v>
       </c>
       <c r="G130" s="9" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="H130" s="3">
         <v>8</v>
       </c>
       <c r="I130" s="8" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/GiftPackEquipConfig.xlsx
+++ b/Excel/GiftPackEquipConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27952" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -125,19 +125,19 @@
     <t>金色法师攻击套</t>
   </si>
   <si>
-    <t>2001,2001,2010,2010,2005,2005,2005,2003</t>
+    <t>2001,2001,2010,2010,2004,2004,2004,2003</t>
   </si>
   <si>
     <t>战士暗金</t>
   </si>
   <si>
-    <t>2001,2001,2010,2010,2006,2006,2006,2003</t>
+    <t>2001,2001,2010,2010,2005,2005,2005,2003</t>
   </si>
   <si>
     <t>法师暗金</t>
   </si>
   <si>
-    <t>2001,2001,2010,2010,2007,2007,2007,2003</t>
+    <t>2001,2001,2010,2010,2006,2006,2006,2003</t>
   </si>
   <si>
     <t>道士暗金</t>
@@ -1122,13 +1122,13 @@
   <dimension ref="A1:I130"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
+    <col min="1" max="1" width="6.87610619469027" style="2" customWidth="1"/>
     <col min="2" max="2" width="9" style="2"/>
-    <col min="3" max="4" width="9.875" style="1" customWidth="1"/>
-    <col min="5" max="6" width="12.25" style="3" customWidth="1"/>
-    <col min="7" max="7" width="31.25" style="3" customWidth="1"/>
-    <col min="8" max="8" width="12.25" style="3" customWidth="1"/>
-    <col min="9" max="9" width="13.75" style="2" customWidth="1"/>
+    <col min="3" max="4" width="9.87610619469027" style="1" customWidth="1"/>
+    <col min="5" max="6" width="12.2477876106195" style="3" customWidth="1"/>
+    <col min="7" max="7" width="34.8495575221239" style="3" customWidth="1"/>
+    <col min="8" max="8" width="12.2477876106195" style="3" customWidth="1"/>
+    <col min="9" max="9" width="13.7522123893805" style="2" customWidth="1"/>
     <col min="10" max="16368" width="9" style="2"/>
     <col min="16369" max="16384" width="9" style="3"/>
   </cols>

--- a/Excel/GiftPackEquipConfig.xlsx
+++ b/Excel/GiftPackEquipConfig.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27952" windowHeight="12255"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="39">
   <si>
     <t>#</t>
   </si>
@@ -48,6 +48,9 @@
   </si>
   <si>
     <t>Quality</t>
+  </si>
+  <si>
+    <t>Cycle</t>
   </si>
   <si>
     <t>Id</t>
@@ -1119,35 +1122,35 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I130"/>
+  <dimension ref="A1:J130"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="6.87610619469027" style="2" customWidth="1"/>
+    <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
     <col min="2" max="2" width="9" style="2"/>
-    <col min="3" max="4" width="9.87610619469027" style="1" customWidth="1"/>
-    <col min="5" max="6" width="12.2477876106195" style="3" customWidth="1"/>
-    <col min="7" max="7" width="34.8495575221239" style="3" customWidth="1"/>
-    <col min="8" max="8" width="12.2477876106195" style="3" customWidth="1"/>
-    <col min="9" max="9" width="13.7522123893805" style="2" customWidth="1"/>
-    <col min="10" max="16368" width="9" style="2"/>
-    <col min="16369" max="16384" width="9" style="3"/>
+    <col min="3" max="4" width="9.875" style="1" customWidth="1"/>
+    <col min="5" max="6" width="12.25" style="3" customWidth="1"/>
+    <col min="7" max="7" width="34.85" style="3" customWidth="1"/>
+    <col min="8" max="9" width="12.25" style="3" customWidth="1"/>
+    <col min="10" max="10" width="13.75" style="2" customWidth="1"/>
+    <col min="11" max="16369" width="9" style="2"/>
+    <col min="16370" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:9">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:9">
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:8">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:9">
       <c r="A3" s="2"/>
       <c r="B3" s="4"/>
       <c r="C3" s="5" t="s">
@@ -1168,12 +1171,15 @@
       <c r="H3" s="5" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:8">
+      <c r="I3" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:9">
       <c r="A4" s="2"/>
       <c r="B4" s="4"/>
       <c r="C4" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>2</v>
@@ -1190,30 +1196,36 @@
       <c r="H4" s="5" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:8">
+      <c r="I4" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:9">
       <c r="A5" s="2"/>
       <c r="B5" s="4"/>
       <c r="C5" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G5" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H5" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="H5" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" customHeight="1" spans="3:9">
+      <c r="I5" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" customHeight="1" spans="3:10">
       <c r="C6" s="1">
         <v>1</v>
       </c>
@@ -1227,16 +1239,19 @@
         <v>10</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H6" s="3">
         <v>6</v>
       </c>
-      <c r="I6" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" customHeight="1" spans="3:9">
+      <c r="I6" s="3">
+        <v>2</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="3:10">
       <c r="C7" s="1">
         <v>2</v>
       </c>
@@ -1250,16 +1265,19 @@
         <v>10</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H7" s="3">
         <v>6</v>
       </c>
-      <c r="I7" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" customHeight="1" spans="3:9">
+      <c r="I7" s="3">
+        <v>2</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="3:10">
       <c r="C8" s="1">
         <v>3</v>
       </c>
@@ -1273,16 +1291,19 @@
         <v>10</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H8" s="3">
         <v>6</v>
       </c>
-      <c r="I8" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" customHeight="1" spans="3:9">
+      <c r="I8" s="3">
+        <v>2</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="3:10">
       <c r="C9" s="1">
         <v>4</v>
       </c>
@@ -1296,16 +1317,19 @@
         <v>10</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H9" s="3">
         <v>6</v>
       </c>
-      <c r="I9" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" customHeight="1" spans="3:9">
+      <c r="I9" s="3">
+        <v>2</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" customHeight="1" spans="3:10">
       <c r="C10" s="1">
         <v>5</v>
       </c>
@@ -1319,16 +1343,19 @@
         <v>13</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H10" s="3">
         <v>6</v>
       </c>
-      <c r="I10" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" customHeight="1" spans="3:9">
+      <c r="I10" s="3">
+        <v>2</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" spans="3:10">
       <c r="C11" s="1">
         <v>6</v>
       </c>
@@ -1342,16 +1369,19 @@
         <v>10005</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H11" s="3">
         <v>6</v>
       </c>
-      <c r="I11" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" customHeight="1" spans="3:9">
+      <c r="I11" s="3">
+        <v>2</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="3:10">
       <c r="C12" s="1">
         <v>7</v>
       </c>
@@ -1365,16 +1395,19 @@
         <v>10006</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H12" s="3">
         <v>6</v>
       </c>
-      <c r="I12" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" customHeight="1" spans="3:9">
+      <c r="I12" s="3">
+        <v>2</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="3:10">
       <c r="C13" s="1">
         <v>8</v>
       </c>
@@ -1388,16 +1421,19 @@
         <v>10006</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H13" s="3">
         <v>6</v>
       </c>
-      <c r="I13" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" customHeight="1" spans="3:9">
+      <c r="I13" s="3">
+        <v>2</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="3:10">
       <c r="C14" s="1">
         <v>9</v>
       </c>
@@ -1411,16 +1447,19 @@
         <v>10017</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H14" s="3">
         <v>6</v>
       </c>
-      <c r="I14" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="15" customHeight="1" spans="3:9">
+      <c r="I14" s="3">
+        <v>2</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="3:10">
       <c r="C15" s="1">
         <v>10</v>
       </c>
@@ -1434,16 +1473,19 @@
         <v>10017</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H15" s="3">
         <v>6</v>
       </c>
-      <c r="I15" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="16" customHeight="1" spans="3:9">
+      <c r="I15" s="3">
+        <v>2</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="3:10">
       <c r="C16" s="1">
         <v>11</v>
       </c>
@@ -1457,16 +1499,19 @@
         <v>10018</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H16" s="3">
         <v>6</v>
       </c>
-      <c r="I16" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="17" customHeight="1" spans="3:9">
+      <c r="I16" s="3">
+        <v>2</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="3:10">
       <c r="C17" s="1">
         <v>12</v>
       </c>
@@ -1480,16 +1525,19 @@
         <v>11</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H17" s="3">
         <v>6</v>
       </c>
-      <c r="I17" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="18" customHeight="1" spans="3:9">
+      <c r="I17" s="3">
+        <v>2</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="3:10">
       <c r="C18" s="1">
         <v>13</v>
       </c>
@@ -1503,16 +1551,19 @@
         <v>14</v>
       </c>
       <c r="G18" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H18" s="3">
         <v>6</v>
       </c>
-      <c r="I18" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="19" customHeight="1" spans="3:9">
+      <c r="I18" s="3">
+        <v>2</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" customHeight="1" spans="3:10">
       <c r="C19" s="1">
         <v>14</v>
       </c>
@@ -1526,16 +1577,19 @@
         <v>14</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H19" s="3">
         <v>6</v>
       </c>
-      <c r="I19" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="20" customHeight="1" spans="3:9">
+      <c r="I19" s="3">
+        <v>2</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="3:10">
       <c r="C20" s="1">
         <v>15</v>
       </c>
@@ -1549,16 +1603,19 @@
         <v>6</v>
       </c>
       <c r="G20" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H20" s="3">
         <v>6</v>
       </c>
-      <c r="I20" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="21" customHeight="1" spans="3:9">
+      <c r="I20" s="3">
+        <v>2</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" spans="3:10">
       <c r="C21" s="1">
         <v>16</v>
       </c>
@@ -1572,16 +1629,19 @@
         <v>6</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H21" s="3">
         <v>6</v>
       </c>
-      <c r="I21" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="22" customHeight="1" spans="3:9">
+      <c r="I21" s="3">
+        <v>2</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" customHeight="1" spans="3:10">
       <c r="C22" s="1">
         <v>17</v>
       </c>
@@ -1595,16 +1655,19 @@
         <v>4</v>
       </c>
       <c r="G22" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H22" s="3">
         <v>6</v>
       </c>
-      <c r="I22" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="23" customHeight="1" spans="3:9">
+      <c r="I22" s="3">
+        <v>2</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="23" customHeight="1" spans="3:10">
       <c r="C23" s="1">
         <v>18</v>
       </c>
@@ -1618,16 +1681,19 @@
         <v>4</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H23" s="3">
         <v>6</v>
       </c>
-      <c r="I23" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="24" customHeight="1" spans="3:9">
+      <c r="I23" s="3">
+        <v>2</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24" customHeight="1" spans="3:10">
       <c r="C24" s="1">
         <v>19</v>
       </c>
@@ -1641,16 +1707,19 @@
         <v>10037</v>
       </c>
       <c r="G24" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H24" s="3">
         <v>6</v>
       </c>
-      <c r="I24" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="25" customHeight="1" spans="3:9">
+      <c r="I24" s="3">
+        <v>2</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" customHeight="1" spans="3:10">
       <c r="C25" s="1">
         <v>20</v>
       </c>
@@ -1664,16 +1733,19 @@
         <v>10037</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H25" s="3">
         <v>6</v>
       </c>
-      <c r="I25" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="26" customHeight="1" spans="3:9">
+      <c r="I25" s="3">
+        <v>2</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26" customHeight="1" spans="3:10">
       <c r="C26" s="1">
         <v>21</v>
       </c>
@@ -1687,16 +1759,19 @@
         <v>9</v>
       </c>
       <c r="G26" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H26" s="3">
         <v>6</v>
       </c>
-      <c r="I26" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="27" customHeight="1" spans="3:9">
+      <c r="I26" s="3">
+        <v>2</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" customHeight="1" spans="3:10">
       <c r="C27" s="1">
         <v>22</v>
       </c>
@@ -1710,16 +1785,19 @@
         <v>15</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H27" s="3">
         <v>6</v>
       </c>
-      <c r="I27" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="28" customHeight="1" spans="3:9">
+      <c r="I27" s="3">
+        <v>2</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28" customHeight="1" spans="3:10">
       <c r="C28" s="1">
         <v>23</v>
       </c>
@@ -1733,16 +1811,19 @@
         <v>18</v>
       </c>
       <c r="G28" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H28" s="3">
         <v>6</v>
       </c>
-      <c r="I28" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="29" customHeight="1" spans="3:9">
+      <c r="I28" s="3">
+        <v>2</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="29" customHeight="1" spans="3:10">
       <c r="C29" s="1">
         <v>24</v>
       </c>
@@ -1756,20 +1837,24 @@
         <v>18</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H29" s="3">
         <v>6</v>
       </c>
-      <c r="I29" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="30" customHeight="1" spans="6:8">
+      <c r="I29" s="3">
+        <v>2</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30" customHeight="1" spans="6:9">
       <c r="F30" s="6"/>
       <c r="H30" s="6"/>
-    </row>
-    <row r="31" customHeight="1" spans="3:9">
+      <c r="I30" s="6"/>
+    </row>
+    <row r="31" customHeight="1" spans="3:10">
       <c r="C31" s="1">
         <v>25</v>
       </c>
@@ -1783,16 +1868,19 @@
         <v>10</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H31" s="3">
         <v>6</v>
       </c>
-      <c r="I31" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="32" customHeight="1" spans="3:9">
+      <c r="I31" s="3">
+        <v>2</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="32" customHeight="1" spans="3:10">
       <c r="C32" s="1">
         <v>26</v>
       </c>
@@ -1806,16 +1894,19 @@
         <v>10</v>
       </c>
       <c r="G32" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H32" s="3">
+        <v>6</v>
+      </c>
+      <c r="I32" s="3">
+        <v>2</v>
+      </c>
+      <c r="J32" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="H32" s="3">
-        <v>6</v>
-      </c>
-      <c r="I32" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="33" customHeight="1" spans="3:9">
+    </row>
+    <row r="33" customHeight="1" spans="3:10">
       <c r="C33" s="1">
         <v>27</v>
       </c>
@@ -1829,16 +1920,19 @@
         <v>10</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H33" s="3">
         <v>6</v>
       </c>
-      <c r="I33" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="34" customHeight="1" spans="3:9">
+      <c r="I33" s="3">
+        <v>2</v>
+      </c>
+      <c r="J33" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="34" customHeight="1" spans="3:10">
       <c r="C34" s="1">
         <v>28</v>
       </c>
@@ -1852,16 +1946,19 @@
         <v>10</v>
       </c>
       <c r="G34" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H34" s="3">
         <v>6</v>
       </c>
-      <c r="I34" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="35" customHeight="1" spans="3:9">
+      <c r="I34" s="3">
+        <v>2</v>
+      </c>
+      <c r="J34" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="35" customHeight="1" spans="3:10">
       <c r="C35" s="1">
         <v>29</v>
       </c>
@@ -1875,16 +1972,19 @@
         <v>13</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H35" s="3">
         <v>6</v>
       </c>
-      <c r="I35" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="36" customHeight="1" spans="3:9">
+      <c r="I35" s="3">
+        <v>2</v>
+      </c>
+      <c r="J35" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="36" customHeight="1" spans="3:10">
       <c r="C36" s="1">
         <v>30</v>
       </c>
@@ -1898,16 +1998,19 @@
         <v>10005</v>
       </c>
       <c r="G36" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H36" s="3">
         <v>6</v>
       </c>
-      <c r="I36" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="37" customHeight="1" spans="3:9">
+      <c r="I36" s="3">
+        <v>2</v>
+      </c>
+      <c r="J36" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="37" customHeight="1" spans="3:10">
       <c r="C37" s="1">
         <v>31</v>
       </c>
@@ -1921,16 +2024,19 @@
         <v>10006</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H37" s="3">
         <v>6</v>
       </c>
-      <c r="I37" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="38" customHeight="1" spans="3:9">
+      <c r="I37" s="3">
+        <v>2</v>
+      </c>
+      <c r="J37" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="38" customHeight="1" spans="3:10">
       <c r="C38" s="1">
         <v>32</v>
       </c>
@@ -1944,13 +2050,16 @@
         <v>10006</v>
       </c>
       <c r="G38" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H38" s="3">
         <v>6</v>
       </c>
-      <c r="I38" s="2" t="s">
-        <v>13</v>
+      <c r="I38" s="3">
+        <v>2</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="4:6">
@@ -1958,7 +2067,7 @@
       <c r="E39" s="6"/>
       <c r="F39" s="6"/>
     </row>
-    <row r="40" customHeight="1" spans="3:9">
+    <row r="40" customHeight="1" spans="3:10">
       <c r="C40" s="1">
         <v>33</v>
       </c>
@@ -1972,16 +2081,19 @@
         <v>10017</v>
       </c>
       <c r="G40" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H40" s="3">
         <v>6</v>
       </c>
-      <c r="I40" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="41" customHeight="1" spans="3:9">
+      <c r="I40" s="3">
+        <v>2</v>
+      </c>
+      <c r="J40" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="41" customHeight="1" spans="3:10">
       <c r="C41" s="1">
         <v>34</v>
       </c>
@@ -1995,16 +2107,19 @@
         <v>10017</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H41" s="3">
         <v>6</v>
       </c>
-      <c r="I41" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="42" customHeight="1" spans="3:9">
+      <c r="I41" s="3">
+        <v>2</v>
+      </c>
+      <c r="J41" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="42" customHeight="1" spans="3:10">
       <c r="C42" s="1">
         <v>35</v>
       </c>
@@ -2018,16 +2133,19 @@
         <v>10018</v>
       </c>
       <c r="G42" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H42" s="3">
         <v>6</v>
       </c>
-      <c r="I42" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="43" customHeight="1" spans="3:9">
+      <c r="I42" s="3">
+        <v>2</v>
+      </c>
+      <c r="J42" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="43" customHeight="1" spans="3:10">
       <c r="C43" s="1">
         <v>36</v>
       </c>
@@ -2041,16 +2159,19 @@
         <v>11</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H43" s="3">
         <v>6</v>
       </c>
-      <c r="I43" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="44" customHeight="1" spans="3:9">
+      <c r="I43" s="3">
+        <v>2</v>
+      </c>
+      <c r="J43" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="44" customHeight="1" spans="3:10">
       <c r="C44" s="1">
         <v>37</v>
       </c>
@@ -2064,16 +2185,19 @@
         <v>14</v>
       </c>
       <c r="G44" s="9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H44" s="3">
         <v>6</v>
       </c>
-      <c r="I44" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="45" customHeight="1" spans="3:9">
+      <c r="I44" s="3">
+        <v>2</v>
+      </c>
+      <c r="J44" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="45" customHeight="1" spans="3:10">
       <c r="C45" s="1">
         <v>38</v>
       </c>
@@ -2087,16 +2211,19 @@
         <v>14</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H45" s="3">
         <v>6</v>
       </c>
-      <c r="I45" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="46" customHeight="1" spans="3:9">
+      <c r="I45" s="3">
+        <v>2</v>
+      </c>
+      <c r="J45" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="46" customHeight="1" spans="3:10">
       <c r="C46" s="1">
         <v>39</v>
       </c>
@@ -2110,16 +2237,19 @@
         <v>6</v>
       </c>
       <c r="G46" s="9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H46" s="3">
         <v>6</v>
       </c>
-      <c r="I46" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="47" customHeight="1" spans="3:9">
+      <c r="I46" s="3">
+        <v>2</v>
+      </c>
+      <c r="J46" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="47" customHeight="1" spans="3:10">
       <c r="C47" s="1">
         <v>40</v>
       </c>
@@ -2133,20 +2263,23 @@
         <v>6</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H47" s="3">
         <v>6</v>
       </c>
-      <c r="I47" s="2" t="s">
-        <v>13</v>
+      <c r="I47" s="3">
+        <v>2</v>
+      </c>
+      <c r="J47" s="2" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="48" customHeight="1" spans="4:6">
       <c r="D48" s="3"/>
       <c r="F48" s="6"/>
     </row>
-    <row r="49" customHeight="1" spans="3:9">
+    <row r="49" customHeight="1" spans="3:10">
       <c r="C49" s="1">
         <v>41</v>
       </c>
@@ -2160,16 +2293,19 @@
         <v>4</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H49" s="3">
         <v>6</v>
       </c>
-      <c r="I49" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="50" customHeight="1" spans="3:9">
+      <c r="I49" s="3">
+        <v>2</v>
+      </c>
+      <c r="J49" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="50" customHeight="1" spans="3:10">
       <c r="C50" s="1">
         <v>42</v>
       </c>
@@ -2183,16 +2319,19 @@
         <v>4</v>
       </c>
       <c r="G50" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H50" s="3">
+        <v>6</v>
+      </c>
+      <c r="I50" s="3">
+        <v>2</v>
+      </c>
+      <c r="J50" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="H50" s="3">
-        <v>6</v>
-      </c>
-      <c r="I50" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="51" customHeight="1" spans="3:9">
+    </row>
+    <row r="51" customHeight="1" spans="3:10">
       <c r="C51" s="1">
         <v>43</v>
       </c>
@@ -2206,16 +2345,19 @@
         <v>10037</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H51" s="3">
         <v>6</v>
       </c>
-      <c r="I51" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="52" customHeight="1" spans="3:9">
+      <c r="I51" s="3">
+        <v>2</v>
+      </c>
+      <c r="J51" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="52" customHeight="1" spans="3:10">
       <c r="C52" s="1">
         <v>44</v>
       </c>
@@ -2229,16 +2371,19 @@
         <v>10037</v>
       </c>
       <c r="G52" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H52" s="3">
+        <v>6</v>
+      </c>
+      <c r="I52" s="3">
+        <v>2</v>
+      </c>
+      <c r="J52" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="H52" s="3">
-        <v>6</v>
-      </c>
-      <c r="I52" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="53" customHeight="1" spans="3:9">
+    </row>
+    <row r="53" customHeight="1" spans="3:10">
       <c r="C53" s="1">
         <v>45</v>
       </c>
@@ -2252,16 +2397,19 @@
         <v>9</v>
       </c>
       <c r="G53" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H53" s="3">
+        <v>6</v>
+      </c>
+      <c r="I53" s="3">
+        <v>2</v>
+      </c>
+      <c r="J53" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="H53" s="3">
-        <v>6</v>
-      </c>
-      <c r="I53" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="54" customHeight="1" spans="3:9">
+    </row>
+    <row r="54" customHeight="1" spans="3:10">
       <c r="C54" s="1">
         <v>46</v>
       </c>
@@ -2275,16 +2423,19 @@
         <v>15</v>
       </c>
       <c r="G54" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H54" s="3">
+        <v>6</v>
+      </c>
+      <c r="I54" s="3">
+        <v>2</v>
+      </c>
+      <c r="J54" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="H54" s="3">
-        <v>6</v>
-      </c>
-      <c r="I54" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="55" customHeight="1" spans="3:9">
+    </row>
+    <row r="55" customHeight="1" spans="3:10">
       <c r="C55" s="1">
         <v>47</v>
       </c>
@@ -2298,16 +2449,19 @@
         <v>18</v>
       </c>
       <c r="G55" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H55" s="3">
+        <v>6</v>
+      </c>
+      <c r="I55" s="3">
+        <v>2</v>
+      </c>
+      <c r="J55" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="H55" s="3">
-        <v>6</v>
-      </c>
-      <c r="I55" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="56" customHeight="1" spans="3:9">
+    </row>
+    <row r="56" customHeight="1" spans="3:10">
       <c r="C56" s="1">
         <v>48</v>
       </c>
@@ -2321,16 +2475,19 @@
         <v>18</v>
       </c>
       <c r="G56" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H56" s="3">
+        <v>6</v>
+      </c>
+      <c r="I56" s="3">
+        <v>2</v>
+      </c>
+      <c r="J56" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="H56" s="3">
-        <v>6</v>
-      </c>
-      <c r="I56" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="57" customHeight="1" spans="3:9">
+    </row>
+    <row r="57" customHeight="1" spans="3:10">
       <c r="C57" s="1">
         <v>49</v>
       </c>
@@ -2344,16 +2501,19 @@
         <v>4</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H57" s="3">
         <v>6</v>
       </c>
-      <c r="I57" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="58" customHeight="1" spans="3:9">
+      <c r="I57" s="3">
+        <v>2</v>
+      </c>
+      <c r="J57" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="58" customHeight="1" spans="3:10">
       <c r="C58" s="1">
         <v>50</v>
       </c>
@@ -2367,16 +2527,19 @@
         <v>4</v>
       </c>
       <c r="G58" s="9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H58" s="3">
         <v>6</v>
       </c>
-      <c r="I58" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="61" customHeight="1" spans="3:9">
+      <c r="I58" s="3">
+        <v>2</v>
+      </c>
+      <c r="J58" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="61" customHeight="1" spans="3:10">
       <c r="C61" s="1">
         <v>101</v>
       </c>
@@ -2390,16 +2553,19 @@
         <v>11002</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H61" s="3">
         <v>7</v>
       </c>
-      <c r="I61" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="62" customHeight="1" spans="3:9">
+      <c r="I61" s="3">
+        <v>3</v>
+      </c>
+      <c r="J61" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="62" customHeight="1" spans="3:10">
       <c r="C62" s="1">
         <v>102</v>
       </c>
@@ -2413,16 +2579,19 @@
         <v>11002</v>
       </c>
       <c r="G62" s="9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H62" s="3">
         <v>7</v>
       </c>
-      <c r="I62" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="63" customHeight="1" spans="3:9">
+      <c r="I62" s="3">
+        <v>3</v>
+      </c>
+      <c r="J62" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="63" customHeight="1" spans="3:10">
       <c r="C63" s="1">
         <v>103</v>
       </c>
@@ -2436,16 +2605,19 @@
         <v>11005</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H63" s="3">
         <v>7</v>
       </c>
-      <c r="I63" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="64" customHeight="1" spans="3:9">
+      <c r="I63" s="3">
+        <v>3</v>
+      </c>
+      <c r="J63" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="64" customHeight="1" spans="3:10">
       <c r="C64" s="1">
         <v>104</v>
       </c>
@@ -2459,16 +2631,19 @@
         <v>11005</v>
       </c>
       <c r="G64" s="9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H64" s="3">
         <v>7</v>
       </c>
-      <c r="I64" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="65" customHeight="1" spans="3:9">
+      <c r="I64" s="3">
+        <v>3</v>
+      </c>
+      <c r="J64" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="65" customHeight="1" spans="3:10">
       <c r="C65" s="1">
         <v>105</v>
       </c>
@@ -2482,16 +2657,19 @@
         <v>11006</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H65" s="3">
         <v>7</v>
       </c>
-      <c r="I65" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="66" customHeight="1" spans="3:9">
+      <c r="I65" s="3">
+        <v>3</v>
+      </c>
+      <c r="J65" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="66" customHeight="1" spans="3:10">
       <c r="C66" s="1">
         <v>106</v>
       </c>
@@ -2505,16 +2683,19 @@
         <v>11008</v>
       </c>
       <c r="G66" s="9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H66" s="3">
         <v>7</v>
       </c>
-      <c r="I66" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="67" customHeight="1" spans="3:9">
+      <c r="I66" s="3">
+        <v>3</v>
+      </c>
+      <c r="J66" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="67" customHeight="1" spans="3:10">
       <c r="C67" s="1">
         <v>107</v>
       </c>
@@ -2528,16 +2709,19 @@
         <v>11010</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H67" s="3">
         <v>7</v>
       </c>
-      <c r="I67" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="68" customHeight="1" spans="3:9">
+      <c r="I67" s="3">
+        <v>3</v>
+      </c>
+      <c r="J67" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="68" customHeight="1" spans="3:10">
       <c r="C68" s="1">
         <v>108</v>
       </c>
@@ -2551,13 +2735,16 @@
         <v>11010</v>
       </c>
       <c r="G68" s="9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H68" s="3">
         <v>7</v>
       </c>
-      <c r="I68" s="2" t="s">
-        <v>23</v>
+      <c r="I68" s="3">
+        <v>3</v>
+      </c>
+      <c r="J68" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="69" customHeight="1" spans="4:6">
@@ -2565,7 +2752,7 @@
       <c r="E69" s="6"/>
       <c r="F69" s="6"/>
     </row>
-    <row r="70" customHeight="1" spans="3:9">
+    <row r="70" customHeight="1" spans="3:10">
       <c r="C70" s="1">
         <v>109</v>
       </c>
@@ -2579,16 +2766,19 @@
         <v>12002</v>
       </c>
       <c r="G70" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H70" s="3">
         <v>7</v>
       </c>
-      <c r="I70" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="71" customHeight="1" spans="3:9">
+      <c r="I70" s="3">
+        <v>3</v>
+      </c>
+      <c r="J70" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="71" customHeight="1" spans="3:10">
       <c r="C71" s="1">
         <v>110</v>
       </c>
@@ -2602,16 +2792,19 @@
         <v>12002</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H71" s="3">
         <v>7</v>
       </c>
-      <c r="I71" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="72" customHeight="1" spans="3:9">
+      <c r="I71" s="3">
+        <v>3</v>
+      </c>
+      <c r="J71" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="72" customHeight="1" spans="3:10">
       <c r="C72" s="1">
         <v>111</v>
       </c>
@@ -2625,16 +2818,19 @@
         <v>12005</v>
       </c>
       <c r="G72" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H72" s="3">
         <v>7</v>
       </c>
-      <c r="I72" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="73" customHeight="1" spans="3:9">
+      <c r="I72" s="3">
+        <v>3</v>
+      </c>
+      <c r="J72" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="73" customHeight="1" spans="3:10">
       <c r="C73" s="1">
         <v>112</v>
       </c>
@@ -2648,16 +2844,19 @@
         <v>12005</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H73" s="3">
         <v>7</v>
       </c>
-      <c r="I73" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="74" customHeight="1" spans="3:9">
+      <c r="I73" s="3">
+        <v>3</v>
+      </c>
+      <c r="J73" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="74" customHeight="1" spans="3:10">
       <c r="C74" s="1">
         <v>113</v>
       </c>
@@ -2671,16 +2870,19 @@
         <v>12006</v>
       </c>
       <c r="G74" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H74" s="3">
         <v>7</v>
       </c>
-      <c r="I74" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="75" customHeight="1" spans="3:9">
+      <c r="I74" s="3">
+        <v>3</v>
+      </c>
+      <c r="J74" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="75" customHeight="1" spans="3:10">
       <c r="C75" s="1">
         <v>114</v>
       </c>
@@ -2694,16 +2896,19 @@
         <v>12008</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H75" s="3">
         <v>7</v>
       </c>
-      <c r="I75" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="76" customHeight="1" spans="3:9">
+      <c r="I75" s="3">
+        <v>3</v>
+      </c>
+      <c r="J75" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="76" customHeight="1" spans="3:10">
       <c r="C76" s="1">
         <v>115</v>
       </c>
@@ -2717,16 +2922,19 @@
         <v>12110</v>
       </c>
       <c r="G76" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H76" s="3">
         <v>7</v>
       </c>
-      <c r="I76" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="77" customHeight="1" spans="3:9">
+      <c r="I76" s="3">
+        <v>3</v>
+      </c>
+      <c r="J76" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="77" customHeight="1" spans="3:10">
       <c r="C77" s="1">
         <v>116</v>
       </c>
@@ -2740,13 +2948,16 @@
         <v>12110</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H77" s="3">
         <v>7</v>
       </c>
-      <c r="I77" s="2" t="s">
-        <v>25</v>
+      <c r="I77" s="3">
+        <v>3</v>
+      </c>
+      <c r="J77" s="2" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="78" customHeight="1" spans="4:6">
@@ -2754,7 +2965,7 @@
       <c r="E78" s="6"/>
       <c r="F78" s="6"/>
     </row>
-    <row r="79" customHeight="1" spans="3:9">
+    <row r="79" customHeight="1" spans="3:10">
       <c r="C79" s="1">
         <v>117</v>
       </c>
@@ -2768,16 +2979,19 @@
         <v>13002</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H79" s="3">
         <v>7</v>
       </c>
-      <c r="I79" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="80" customHeight="1" spans="3:9">
+      <c r="I79" s="3">
+        <v>3</v>
+      </c>
+      <c r="J79" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="80" customHeight="1" spans="3:10">
       <c r="C80" s="1">
         <v>118</v>
       </c>
@@ -2791,16 +3005,19 @@
         <v>13002</v>
       </c>
       <c r="G80" s="9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H80" s="3">
         <v>7</v>
       </c>
-      <c r="I80" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="81" customHeight="1" spans="3:9">
+      <c r="I80" s="3">
+        <v>3</v>
+      </c>
+      <c r="J80" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="81" customHeight="1" spans="3:10">
       <c r="C81" s="1">
         <v>119</v>
       </c>
@@ -2814,16 +3031,19 @@
         <v>13005</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H81" s="3">
         <v>7</v>
       </c>
-      <c r="I81" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="82" customHeight="1" spans="3:9">
+      <c r="I81" s="3">
+        <v>3</v>
+      </c>
+      <c r="J81" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="82" customHeight="1" spans="3:10">
       <c r="C82" s="1">
         <v>120</v>
       </c>
@@ -2837,16 +3057,19 @@
         <v>13005</v>
       </c>
       <c r="G82" s="9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H82" s="3">
         <v>7</v>
       </c>
-      <c r="I82" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="83" customHeight="1" spans="3:9">
+      <c r="I82" s="3">
+        <v>3</v>
+      </c>
+      <c r="J82" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="83" customHeight="1" spans="3:10">
       <c r="C83" s="1">
         <v>121</v>
       </c>
@@ -2860,16 +3083,19 @@
         <v>13008</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H83" s="3">
         <v>7</v>
       </c>
-      <c r="I83" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="84" customHeight="1" spans="3:9">
+      <c r="I83" s="3">
+        <v>3</v>
+      </c>
+      <c r="J83" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="84" customHeight="1" spans="3:10">
       <c r="C84" s="1">
         <v>122</v>
       </c>
@@ -2883,16 +3109,19 @@
         <v>13009</v>
       </c>
       <c r="G84" s="9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H84" s="3">
         <v>7</v>
       </c>
-      <c r="I84" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="85" customHeight="1" spans="3:9">
+      <c r="I84" s="3">
+        <v>3</v>
+      </c>
+      <c r="J84" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="85" customHeight="1" spans="3:10">
       <c r="C85" s="1">
         <v>123</v>
       </c>
@@ -2906,16 +3135,19 @@
         <v>13010</v>
       </c>
       <c r="G85" s="9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H85" s="3">
         <v>7</v>
       </c>
-      <c r="I85" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="86" customHeight="1" spans="3:9">
+      <c r="I85" s="3">
+        <v>3</v>
+      </c>
+      <c r="J85" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="86" customHeight="1" spans="3:10">
       <c r="C86" s="1">
         <v>124</v>
       </c>
@@ -2929,16 +3161,19 @@
         <v>13010</v>
       </c>
       <c r="G86" s="9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H86" s="3">
         <v>7</v>
       </c>
-      <c r="I86" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="88" customHeight="1" spans="3:9">
+      <c r="I86" s="3">
+        <v>3</v>
+      </c>
+      <c r="J86" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="88" customHeight="1" spans="3:10">
       <c r="C88" s="1">
         <v>125</v>
       </c>
@@ -2952,16 +3187,19 @@
         <v>11002</v>
       </c>
       <c r="G88" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H88" s="3">
         <v>7</v>
       </c>
-      <c r="I88" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="89" customHeight="1" spans="3:9">
+      <c r="I88" s="3">
+        <v>3</v>
+      </c>
+      <c r="J88" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="89" customHeight="1" spans="3:10">
       <c r="C89" s="1">
         <v>126</v>
       </c>
@@ -2975,16 +3213,19 @@
         <v>11002</v>
       </c>
       <c r="G89" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H89" s="3">
         <v>7</v>
       </c>
-      <c r="I89" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="90" customHeight="1" spans="3:9">
+      <c r="I89" s="3">
+        <v>3</v>
+      </c>
+      <c r="J89" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="90" customHeight="1" spans="3:10">
       <c r="C90" s="1">
         <v>127</v>
       </c>
@@ -2998,16 +3239,19 @@
         <v>11005</v>
       </c>
       <c r="G90" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H90" s="3">
         <v>7</v>
       </c>
-      <c r="I90" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="91" customHeight="1" spans="3:9">
+      <c r="I90" s="3">
+        <v>3</v>
+      </c>
+      <c r="J90" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="91" customHeight="1" spans="3:10">
       <c r="C91" s="1">
         <v>128</v>
       </c>
@@ -3021,16 +3265,19 @@
         <v>11005</v>
       </c>
       <c r="G91" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H91" s="3">
         <v>7</v>
       </c>
-      <c r="I91" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="92" customHeight="1" spans="3:9">
+      <c r="I91" s="3">
+        <v>3</v>
+      </c>
+      <c r="J91" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="92" customHeight="1" spans="3:10">
       <c r="C92" s="1">
         <v>129</v>
       </c>
@@ -3044,16 +3291,19 @@
         <v>11006</v>
       </c>
       <c r="G92" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H92" s="3">
         <v>7</v>
       </c>
-      <c r="I92" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="93" customHeight="1" spans="3:9">
+      <c r="I92" s="3">
+        <v>3</v>
+      </c>
+      <c r="J92" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="93" customHeight="1" spans="3:10">
       <c r="C93" s="1">
         <v>130</v>
       </c>
@@ -3067,16 +3317,19 @@
         <v>11008</v>
       </c>
       <c r="G93" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H93" s="3">
         <v>7</v>
       </c>
-      <c r="I93" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="94" customHeight="1" spans="3:9">
+      <c r="I93" s="3">
+        <v>3</v>
+      </c>
+      <c r="J93" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="94" customHeight="1" spans="3:10">
       <c r="C94" s="1">
         <v>131</v>
       </c>
@@ -3090,16 +3343,19 @@
         <v>11010</v>
       </c>
       <c r="G94" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H94" s="3">
         <v>7</v>
       </c>
-      <c r="I94" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="95" customHeight="1" spans="3:9">
+      <c r="I94" s="3">
+        <v>3</v>
+      </c>
+      <c r="J94" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="95" customHeight="1" spans="3:10">
       <c r="C95" s="1">
         <v>132</v>
       </c>
@@ -3113,16 +3369,19 @@
         <v>11010</v>
       </c>
       <c r="G95" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H95" s="3">
         <v>7</v>
       </c>
-      <c r="I95" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="96" customHeight="1" spans="3:9">
+      <c r="I95" s="3">
+        <v>3</v>
+      </c>
+      <c r="J95" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="96" customHeight="1" spans="3:10">
       <c r="C96" s="1">
         <v>133</v>
       </c>
@@ -3136,16 +3395,19 @@
         <v>12002</v>
       </c>
       <c r="G96" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H96" s="3">
         <v>7</v>
       </c>
-      <c r="I96" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="97" customHeight="1" spans="3:9">
+      <c r="I96" s="3">
+        <v>3</v>
+      </c>
+      <c r="J96" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="97" customHeight="1" spans="3:10">
       <c r="C97" s="1">
         <v>134</v>
       </c>
@@ -3159,16 +3421,19 @@
         <v>12002</v>
       </c>
       <c r="G97" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H97" s="3">
         <v>7</v>
       </c>
-      <c r="I97" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="98" customHeight="1" spans="3:9">
+      <c r="I97" s="3">
+        <v>3</v>
+      </c>
+      <c r="J97" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="98" customHeight="1" spans="3:10">
       <c r="C98" s="1">
         <v>135</v>
       </c>
@@ -3182,16 +3447,19 @@
         <v>12005</v>
       </c>
       <c r="G98" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H98" s="3">
         <v>7</v>
       </c>
-      <c r="I98" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="99" customHeight="1" spans="3:9">
+      <c r="I98" s="3">
+        <v>3</v>
+      </c>
+      <c r="J98" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="99" customHeight="1" spans="3:10">
       <c r="C99" s="1">
         <v>136</v>
       </c>
@@ -3205,16 +3473,19 @@
         <v>12005</v>
       </c>
       <c r="G99" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H99" s="3">
         <v>7</v>
       </c>
-      <c r="I99" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="100" customHeight="1" spans="3:9">
+      <c r="I99" s="3">
+        <v>3</v>
+      </c>
+      <c r="J99" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="100" customHeight="1" spans="3:10">
       <c r="C100" s="1">
         <v>137</v>
       </c>
@@ -3228,16 +3499,19 @@
         <v>12006</v>
       </c>
       <c r="G100" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H100" s="3">
         <v>7</v>
       </c>
-      <c r="I100" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="101" customHeight="1" spans="3:9">
+      <c r="I100" s="3">
+        <v>3</v>
+      </c>
+      <c r="J100" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="101" customHeight="1" spans="3:10">
       <c r="C101" s="1">
         <v>138</v>
       </c>
@@ -3251,16 +3525,19 @@
         <v>12008</v>
       </c>
       <c r="G101" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H101" s="3">
         <v>7</v>
       </c>
-      <c r="I101" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="102" customHeight="1" spans="3:9">
+      <c r="I101" s="3">
+        <v>3</v>
+      </c>
+      <c r="J101" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="102" customHeight="1" spans="3:10">
       <c r="C102" s="1">
         <v>139</v>
       </c>
@@ -3274,16 +3551,19 @@
         <v>12110</v>
       </c>
       <c r="G102" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H102" s="3">
         <v>7</v>
       </c>
-      <c r="I102" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="103" customHeight="1" spans="3:9">
+      <c r="I102" s="3">
+        <v>3</v>
+      </c>
+      <c r="J102" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="103" customHeight="1" spans="3:10">
       <c r="C103" s="1">
         <v>140</v>
       </c>
@@ -3297,13 +3577,16 @@
         <v>12110</v>
       </c>
       <c r="G103" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H103" s="3">
         <v>7</v>
       </c>
-      <c r="I103" s="2" t="s">
-        <v>31</v>
+      <c r="I103" s="3">
+        <v>3</v>
+      </c>
+      <c r="J103" s="2" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="104" customHeight="1" spans="4:6">
@@ -3311,7 +3594,7 @@
       <c r="E104" s="6"/>
       <c r="F104" s="6"/>
     </row>
-    <row r="105" customHeight="1" spans="3:9">
+    <row r="105" customHeight="1" spans="3:10">
       <c r="C105" s="1">
         <v>151</v>
       </c>
@@ -3325,16 +3608,19 @@
         <v>21002</v>
       </c>
       <c r="G105" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H105" s="3">
         <v>8</v>
       </c>
-      <c r="I105" s="8" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="106" customHeight="1" spans="3:9">
+      <c r="I105" s="3">
+        <v>4</v>
+      </c>
+      <c r="J105" s="8" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="106" customHeight="1" spans="3:10">
       <c r="C106" s="1">
         <v>152</v>
       </c>
@@ -3348,16 +3634,19 @@
         <v>21002</v>
       </c>
       <c r="G106" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H106" s="3">
         <v>8</v>
       </c>
-      <c r="I106" s="8" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="107" customHeight="1" spans="3:9">
+      <c r="I106" s="3">
+        <v>4</v>
+      </c>
+      <c r="J106" s="8" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="107" customHeight="1" spans="3:10">
       <c r="C107" s="1">
         <v>153</v>
       </c>
@@ -3371,16 +3660,19 @@
         <v>21005</v>
       </c>
       <c r="G107" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H107" s="3">
         <v>8</v>
       </c>
-      <c r="I107" s="8" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="108" customHeight="1" spans="3:9">
+      <c r="I107" s="3">
+        <v>4</v>
+      </c>
+      <c r="J107" s="8" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="108" customHeight="1" spans="3:10">
       <c r="C108" s="1">
         <v>154</v>
       </c>
@@ -3394,16 +3686,19 @@
         <v>21005</v>
       </c>
       <c r="G108" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H108" s="3">
         <v>8</v>
       </c>
-      <c r="I108" s="8" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="109" customHeight="1" spans="3:9">
+      <c r="I108" s="3">
+        <v>4</v>
+      </c>
+      <c r="J108" s="8" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="109" customHeight="1" spans="3:10">
       <c r="C109" s="1">
         <v>155</v>
       </c>
@@ -3417,16 +3712,19 @@
         <v>21008</v>
       </c>
       <c r="G109" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H109" s="3">
         <v>8</v>
       </c>
-      <c r="I109" s="8" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="110" customHeight="1" spans="3:9">
+      <c r="I109" s="3">
+        <v>4</v>
+      </c>
+      <c r="J109" s="8" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="110" customHeight="1" spans="3:10">
       <c r="C110" s="1">
         <v>156</v>
       </c>
@@ -3440,16 +3738,19 @@
         <v>21010</v>
       </c>
       <c r="G110" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H110" s="3">
         <v>8</v>
       </c>
-      <c r="I110" s="8" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="111" customHeight="1" spans="3:9">
+      <c r="I110" s="3">
+        <v>4</v>
+      </c>
+      <c r="J110" s="8" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="111" customHeight="1" spans="3:10">
       <c r="C111" s="1">
         <v>157</v>
       </c>
@@ -3463,16 +3764,19 @@
         <v>21011</v>
       </c>
       <c r="G111" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H111" s="3">
         <v>8</v>
       </c>
-      <c r="I111" s="8" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="112" customHeight="1" spans="3:9">
+      <c r="I111" s="3">
+        <v>4</v>
+      </c>
+      <c r="J111" s="8" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="112" customHeight="1" spans="3:10">
       <c r="C112" s="1">
         <v>158</v>
       </c>
@@ -3486,13 +3790,16 @@
         <v>21011</v>
       </c>
       <c r="G112" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H112" s="3">
         <v>8</v>
       </c>
-      <c r="I112" s="8" t="s">
-        <v>33</v>
+      <c r="I112" s="3">
+        <v>4</v>
+      </c>
+      <c r="J112" s="8" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="113" customHeight="1" spans="4:6">
@@ -3500,7 +3807,7 @@
       <c r="E113" s="6"/>
       <c r="F113" s="6"/>
     </row>
-    <row r="114" customHeight="1" spans="3:9">
+    <row r="114" customHeight="1" spans="3:10">
       <c r="C114" s="1">
         <v>161</v>
       </c>
@@ -3514,16 +3821,19 @@
         <v>21002</v>
       </c>
       <c r="G114" s="9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H114" s="3">
         <v>8</v>
       </c>
-      <c r="I114" s="8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="115" customHeight="1" spans="3:9">
+      <c r="I114" s="3">
+        <v>4</v>
+      </c>
+      <c r="J114" s="8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="115" customHeight="1" spans="3:10">
       <c r="C115" s="1">
         <v>162</v>
       </c>
@@ -3537,16 +3847,19 @@
         <v>21002</v>
       </c>
       <c r="G115" s="9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H115" s="3">
         <v>8</v>
       </c>
-      <c r="I115" s="8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="116" customHeight="1" spans="3:9">
+      <c r="I115" s="3">
+        <v>4</v>
+      </c>
+      <c r="J115" s="8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="116" customHeight="1" spans="3:10">
       <c r="C116" s="1">
         <v>163</v>
       </c>
@@ -3560,16 +3873,19 @@
         <v>21005</v>
       </c>
       <c r="G116" s="9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H116" s="3">
         <v>8</v>
       </c>
-      <c r="I116" s="8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="117" customHeight="1" spans="3:9">
+      <c r="I116" s="3">
+        <v>4</v>
+      </c>
+      <c r="J116" s="8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="117" customHeight="1" spans="3:10">
       <c r="C117" s="1">
         <v>164</v>
       </c>
@@ -3583,16 +3899,19 @@
         <v>21005</v>
       </c>
       <c r="G117" s="9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H117" s="3">
         <v>8</v>
       </c>
-      <c r="I117" s="8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="118" customHeight="1" spans="3:9">
+      <c r="I117" s="3">
+        <v>4</v>
+      </c>
+      <c r="J117" s="8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="118" customHeight="1" spans="3:10">
       <c r="C118" s="1">
         <v>165</v>
       </c>
@@ -3606,16 +3925,19 @@
         <v>21008</v>
       </c>
       <c r="G118" s="9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H118" s="3">
         <v>8</v>
       </c>
-      <c r="I118" s="8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="119" customHeight="1" spans="3:9">
+      <c r="I118" s="3">
+        <v>4</v>
+      </c>
+      <c r="J118" s="8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="119" customHeight="1" spans="3:10">
       <c r="C119" s="1">
         <v>166</v>
       </c>
@@ -3629,16 +3951,19 @@
         <v>21010</v>
       </c>
       <c r="G119" s="9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H119" s="3">
         <v>8</v>
       </c>
-      <c r="I119" s="8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="120" customHeight="1" spans="3:9">
+      <c r="I119" s="3">
+        <v>4</v>
+      </c>
+      <c r="J119" s="8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="120" customHeight="1" spans="3:10">
       <c r="C120" s="1">
         <v>167</v>
       </c>
@@ -3652,16 +3977,19 @@
         <v>21011</v>
       </c>
       <c r="G120" s="9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H120" s="3">
         <v>8</v>
       </c>
-      <c r="I120" s="8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="121" customHeight="1" spans="3:9">
+      <c r="I120" s="3">
+        <v>4</v>
+      </c>
+      <c r="J120" s="8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="121" customHeight="1" spans="3:10">
       <c r="C121" s="1">
         <v>168</v>
       </c>
@@ -3675,13 +4003,16 @@
         <v>21011</v>
       </c>
       <c r="G121" s="9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H121" s="3">
         <v>8</v>
       </c>
-      <c r="I121" s="8" t="s">
-        <v>35</v>
+      <c r="I121" s="3">
+        <v>4</v>
+      </c>
+      <c r="J121" s="8" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="122" customHeight="1" spans="4:6">
@@ -3689,7 +4020,7 @@
       <c r="E122" s="6"/>
       <c r="F122" s="6"/>
     </row>
-    <row r="123" customHeight="1" spans="3:9">
+    <row r="123" customHeight="1" spans="3:10">
       <c r="C123" s="1">
         <v>171</v>
       </c>
@@ -3703,16 +4034,19 @@
         <v>21002</v>
       </c>
       <c r="G123" s="9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H123" s="3">
         <v>8</v>
       </c>
-      <c r="I123" s="8" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="124" customHeight="1" spans="3:9">
+      <c r="I123" s="3">
+        <v>4</v>
+      </c>
+      <c r="J123" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="124" customHeight="1" spans="3:10">
       <c r="C124" s="1">
         <v>172</v>
       </c>
@@ -3726,16 +4060,19 @@
         <v>21002</v>
       </c>
       <c r="G124" s="9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H124" s="3">
         <v>8</v>
       </c>
-      <c r="I124" s="8" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="125" customHeight="1" spans="3:9">
+      <c r="I124" s="3">
+        <v>4</v>
+      </c>
+      <c r="J124" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="125" customHeight="1" spans="3:10">
       <c r="C125" s="1">
         <v>173</v>
       </c>
@@ -3749,16 +4086,19 @@
         <v>21005</v>
       </c>
       <c r="G125" s="9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H125" s="3">
         <v>8</v>
       </c>
-      <c r="I125" s="8" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="126" customHeight="1" spans="3:9">
+      <c r="I125" s="3">
+        <v>4</v>
+      </c>
+      <c r="J125" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="126" customHeight="1" spans="3:10">
       <c r="C126" s="1">
         <v>174</v>
       </c>
@@ -3772,16 +4112,19 @@
         <v>21005</v>
       </c>
       <c r="G126" s="9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H126" s="3">
         <v>8</v>
       </c>
-      <c r="I126" s="8" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="127" customHeight="1" spans="3:9">
+      <c r="I126" s="3">
+        <v>4</v>
+      </c>
+      <c r="J126" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="127" customHeight="1" spans="3:10">
       <c r="C127" s="1">
         <v>175</v>
       </c>
@@ -3795,16 +4138,19 @@
         <v>21008</v>
       </c>
       <c r="G127" s="9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H127" s="3">
         <v>8</v>
       </c>
-      <c r="I127" s="8" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="128" customHeight="1" spans="3:9">
+      <c r="I127" s="3">
+        <v>4</v>
+      </c>
+      <c r="J127" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="128" customHeight="1" spans="3:10">
       <c r="C128" s="1">
         <v>176</v>
       </c>
@@ -3818,16 +4164,19 @@
         <v>21010</v>
       </c>
       <c r="G128" s="9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H128" s="3">
         <v>8</v>
       </c>
-      <c r="I128" s="8" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="129" customHeight="1" spans="3:9">
+      <c r="I128" s="3">
+        <v>4</v>
+      </c>
+      <c r="J128" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="129" customHeight="1" spans="3:10">
       <c r="C129" s="1">
         <v>177</v>
       </c>
@@ -3841,16 +4190,19 @@
         <v>21011</v>
       </c>
       <c r="G129" s="9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H129" s="3">
         <v>8</v>
       </c>
-      <c r="I129" s="8" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="130" customHeight="1" spans="3:9">
+      <c r="I129" s="3">
+        <v>4</v>
+      </c>
+      <c r="J129" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="130" customHeight="1" spans="3:10">
       <c r="C130" s="1">
         <v>178</v>
       </c>
@@ -3864,13 +4216,16 @@
         <v>21011</v>
       </c>
       <c r="G130" s="9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H130" s="3">
         <v>8</v>
       </c>
-      <c r="I130" s="8" t="s">
-        <v>37</v>
+      <c r="I130" s="3">
+        <v>4</v>
+      </c>
+      <c r="J130" s="8" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/GiftPackEquipConfig.xlsx
+++ b/Excel/GiftPackEquipConfig.xlsx
@@ -3625,7 +3625,7 @@
         <v>152</v>
       </c>
       <c r="D106" s="3">
-        <v>21305801</v>
+        <v>21305802</v>
       </c>
       <c r="E106" s="6">
         <v>21002</v>
@@ -3651,7 +3651,7 @@
         <v>153</v>
       </c>
       <c r="D107" s="3">
-        <v>21305801</v>
+        <v>21305803</v>
       </c>
       <c r="E107" s="6">
         <v>21005</v>
@@ -3677,7 +3677,7 @@
         <v>154</v>
       </c>
       <c r="D108" s="3">
-        <v>21305801</v>
+        <v>21305804</v>
       </c>
       <c r="E108" s="6">
         <v>21005</v>
@@ -3703,7 +3703,7 @@
         <v>155</v>
       </c>
       <c r="D109" s="3">
-        <v>21305801</v>
+        <v>21305805</v>
       </c>
       <c r="E109" s="6">
         <v>21008</v>
@@ -3729,7 +3729,7 @@
         <v>156</v>
       </c>
       <c r="D110" s="3">
-        <v>21305801</v>
+        <v>21305807</v>
       </c>
       <c r="E110" s="6">
         <v>21010</v>
@@ -3755,7 +3755,7 @@
         <v>157</v>
       </c>
       <c r="D111" s="3">
-        <v>21305801</v>
+        <v>21305809</v>
       </c>
       <c r="E111" s="6">
         <v>21011</v>
@@ -3781,7 +3781,7 @@
         <v>158</v>
       </c>
       <c r="D112" s="3">
-        <v>21305801</v>
+        <v>21305810</v>
       </c>
       <c r="E112" s="6">
         <v>21011</v>

--- a/Excel/GiftPackEquipConfig.xlsx
+++ b/Excel/GiftPackEquipConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="45">
   <si>
     <t>#</t>
   </si>
@@ -144,6 +144,24 @@
   </si>
   <si>
     <t>道士暗金</t>
+  </si>
+  <si>
+    <t>2001,2001,2010,2010,2004,2004,2004,55,54</t>
+  </si>
+  <si>
+    <t>战士</t>
+  </si>
+  <si>
+    <t>2001,2001,2004,2010,2005,2005,2005,55,54</t>
+  </si>
+  <si>
+    <t>法师</t>
+  </si>
+  <si>
+    <t>2001,2001,2010,2010,2006,2006,2006,55,54</t>
+  </si>
+  <si>
+    <t>道士</t>
   </si>
 </sst>
 </file>
@@ -1122,7 +1140,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J130"/>
+  <dimension ref="A1:J157"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
@@ -4228,6 +4246,640 @@
         <v>38</v>
       </c>
     </row>
+    <row r="132" customHeight="1" spans="3:10">
+      <c r="C132" s="1">
+        <v>181</v>
+      </c>
+      <c r="D132" s="3">
+        <v>21405801</v>
+      </c>
+      <c r="E132" s="6">
+        <v>31112</v>
+      </c>
+      <c r="F132" s="6">
+        <v>31012</v>
+      </c>
+      <c r="G132" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="H132" s="3">
+        <v>9</v>
+      </c>
+      <c r="I132" s="3">
+        <v>5</v>
+      </c>
+      <c r="J132" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="133" customHeight="1" spans="3:10">
+      <c r="C133" s="1">
+        <v>182</v>
+      </c>
+      <c r="D133" s="3">
+        <v>21405802</v>
+      </c>
+      <c r="E133" s="6">
+        <v>31112</v>
+      </c>
+      <c r="F133" s="6">
+        <v>31012</v>
+      </c>
+      <c r="G133" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="H133" s="3">
+        <v>9</v>
+      </c>
+      <c r="I133" s="3">
+        <v>5</v>
+      </c>
+      <c r="J133" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="134" customHeight="1" spans="3:10">
+      <c r="C134" s="1">
+        <v>183</v>
+      </c>
+      <c r="D134" s="3">
+        <v>21405803</v>
+      </c>
+      <c r="E134" s="6">
+        <v>31212</v>
+      </c>
+      <c r="F134" s="6">
+        <v>31112</v>
+      </c>
+      <c r="G134" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="H134" s="3">
+        <v>9</v>
+      </c>
+      <c r="I134" s="3">
+        <v>5</v>
+      </c>
+      <c r="J134" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="135" customHeight="1" spans="3:10">
+      <c r="C135" s="1">
+        <v>184</v>
+      </c>
+      <c r="D135" s="3">
+        <v>21405804</v>
+      </c>
+      <c r="E135" s="6">
+        <v>31212</v>
+      </c>
+      <c r="F135" s="6">
+        <v>31112</v>
+      </c>
+      <c r="G135" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="H135" s="3">
+        <v>9</v>
+      </c>
+      <c r="I135" s="3">
+        <v>5</v>
+      </c>
+      <c r="J135" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="136" customHeight="1" spans="3:10">
+      <c r="C136" s="1">
+        <v>185</v>
+      </c>
+      <c r="D136" s="3">
+        <v>21405805</v>
+      </c>
+      <c r="E136" s="6">
+        <v>31012</v>
+      </c>
+      <c r="F136" s="6">
+        <v>31212</v>
+      </c>
+      <c r="G136" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="H136" s="3">
+        <v>9</v>
+      </c>
+      <c r="I136" s="3">
+        <v>5</v>
+      </c>
+      <c r="J136" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="137" customHeight="1" spans="3:10">
+      <c r="C137" s="1">
+        <v>186</v>
+      </c>
+      <c r="D137" s="3">
+        <v>21405807</v>
+      </c>
+      <c r="E137" s="6">
+        <v>31012</v>
+      </c>
+      <c r="F137" s="6">
+        <v>31312</v>
+      </c>
+      <c r="G137" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="H137" s="3">
+        <v>9</v>
+      </c>
+      <c r="I137" s="3">
+        <v>5</v>
+      </c>
+      <c r="J137" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="138" customHeight="1" spans="3:10">
+      <c r="C138" s="1">
+        <v>187</v>
+      </c>
+      <c r="D138" s="3">
+        <v>21405809</v>
+      </c>
+      <c r="E138" s="6">
+        <v>31002</v>
+      </c>
+      <c r="F138" s="6">
+        <v>31002</v>
+      </c>
+      <c r="G138" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="H138" s="3">
+        <v>9</v>
+      </c>
+      <c r="I138" s="3">
+        <v>5</v>
+      </c>
+      <c r="J138" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="139" customHeight="1" spans="3:10">
+      <c r="C139" s="1">
+        <v>188</v>
+      </c>
+      <c r="D139" s="3">
+        <v>21405810</v>
+      </c>
+      <c r="E139" s="6">
+        <v>31002</v>
+      </c>
+      <c r="F139" s="6">
+        <v>31002</v>
+      </c>
+      <c r="G139" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="H139" s="3">
+        <v>9</v>
+      </c>
+      <c r="I139" s="3">
+        <v>5</v>
+      </c>
+      <c r="J139" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="140" customHeight="1" spans="4:6">
+      <c r="D140" s="3"/>
+      <c r="E140" s="6"/>
+      <c r="F140" s="6"/>
+    </row>
+    <row r="141" customHeight="1" spans="3:10">
+      <c r="C141" s="1">
+        <v>191</v>
+      </c>
+      <c r="D141" s="3">
+        <v>22405801</v>
+      </c>
+      <c r="E141" s="6">
+        <v>32002</v>
+      </c>
+      <c r="F141" s="6">
+        <v>32102</v>
+      </c>
+      <c r="G141" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="H141" s="3">
+        <v>9</v>
+      </c>
+      <c r="I141" s="3">
+        <v>5</v>
+      </c>
+      <c r="J141" s="8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="142" customHeight="1" spans="3:10">
+      <c r="C142" s="1">
+        <v>192</v>
+      </c>
+      <c r="D142" s="3">
+        <v>22405802</v>
+      </c>
+      <c r="E142" s="6">
+        <v>32002</v>
+      </c>
+      <c r="F142" s="6">
+        <v>32102</v>
+      </c>
+      <c r="G142" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="H142" s="3">
+        <v>9</v>
+      </c>
+      <c r="I142" s="3">
+        <v>5</v>
+      </c>
+      <c r="J142" s="8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="143" customHeight="1" spans="3:10">
+      <c r="C143" s="1">
+        <v>193</v>
+      </c>
+      <c r="D143" s="3">
+        <v>22405803</v>
+      </c>
+      <c r="E143" s="6">
+        <v>32002</v>
+      </c>
+      <c r="F143" s="6">
+        <v>32202</v>
+      </c>
+      <c r="G143" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="H143" s="3">
+        <v>9</v>
+      </c>
+      <c r="I143" s="3">
+        <v>5</v>
+      </c>
+      <c r="J143" s="8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="144" customHeight="1" spans="3:10">
+      <c r="C144" s="1">
+        <v>194</v>
+      </c>
+      <c r="D144" s="3">
+        <v>22405804</v>
+      </c>
+      <c r="E144" s="6">
+        <v>32002</v>
+      </c>
+      <c r="F144" s="6">
+        <v>32202</v>
+      </c>
+      <c r="G144" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="H144" s="3">
+        <v>9</v>
+      </c>
+      <c r="I144" s="3">
+        <v>5</v>
+      </c>
+      <c r="J144" s="8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="145" customHeight="1" spans="3:10">
+      <c r="C145" s="1">
+        <v>195</v>
+      </c>
+      <c r="D145" s="3">
+        <v>22405805</v>
+      </c>
+      <c r="E145" s="6">
+        <v>32007</v>
+      </c>
+      <c r="F145" s="6">
+        <v>32107</v>
+      </c>
+      <c r="G145" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="H145" s="3">
+        <v>9</v>
+      </c>
+      <c r="I145" s="3">
+        <v>5</v>
+      </c>
+      <c r="J145" s="8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="146" customHeight="1" spans="3:10">
+      <c r="C146" s="1">
+        <v>196</v>
+      </c>
+      <c r="D146" s="3">
+        <v>22405807</v>
+      </c>
+      <c r="E146" s="6">
+        <v>32008</v>
+      </c>
+      <c r="F146" s="6">
+        <v>32108</v>
+      </c>
+      <c r="G146" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="H146" s="3">
+        <v>9</v>
+      </c>
+      <c r="I146" s="3">
+        <v>5</v>
+      </c>
+      <c r="J146" s="8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="147" customHeight="1" spans="3:10">
+      <c r="C147" s="1">
+        <v>197</v>
+      </c>
+      <c r="D147" s="3">
+        <v>22405809</v>
+      </c>
+      <c r="E147" s="6">
+        <v>32010</v>
+      </c>
+      <c r="F147" s="6">
+        <v>32110</v>
+      </c>
+      <c r="G147" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="H147" s="3">
+        <v>9</v>
+      </c>
+      <c r="I147" s="3">
+        <v>5</v>
+      </c>
+      <c r="J147" s="8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="148" customHeight="1" spans="3:10">
+      <c r="C148" s="1">
+        <v>198</v>
+      </c>
+      <c r="D148" s="3">
+        <v>22405810</v>
+      </c>
+      <c r="E148" s="6">
+        <v>32010</v>
+      </c>
+      <c r="F148" s="6">
+        <v>32110</v>
+      </c>
+      <c r="G148" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="H148" s="3">
+        <v>9</v>
+      </c>
+      <c r="I148" s="3">
+        <v>5</v>
+      </c>
+      <c r="J148" s="8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="149" customHeight="1" spans="4:6">
+      <c r="D149" s="3"/>
+      <c r="E149" s="6"/>
+      <c r="F149" s="6"/>
+    </row>
+    <row r="150" customHeight="1" spans="3:10">
+      <c r="C150" s="1">
+        <v>201</v>
+      </c>
+      <c r="D150" s="3">
+        <v>23405801</v>
+      </c>
+      <c r="E150" s="6">
+        <v>33012</v>
+      </c>
+      <c r="F150" s="6">
+        <v>33012</v>
+      </c>
+      <c r="G150" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="H150" s="3">
+        <v>9</v>
+      </c>
+      <c r="I150" s="3">
+        <v>5</v>
+      </c>
+      <c r="J150" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="151" customHeight="1" spans="3:10">
+      <c r="C151" s="1">
+        <v>202</v>
+      </c>
+      <c r="D151" s="3">
+        <v>23405802</v>
+      </c>
+      <c r="E151" s="6">
+        <v>33012</v>
+      </c>
+      <c r="F151" s="6">
+        <v>33012</v>
+      </c>
+      <c r="G151" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="H151" s="3">
+        <v>9</v>
+      </c>
+      <c r="I151" s="3">
+        <v>5</v>
+      </c>
+      <c r="J151" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="152" customHeight="1" spans="3:10">
+      <c r="C152" s="1">
+        <v>203</v>
+      </c>
+      <c r="D152" s="3">
+        <v>23405803</v>
+      </c>
+      <c r="E152" s="6">
+        <v>33212</v>
+      </c>
+      <c r="F152" s="6">
+        <v>33012</v>
+      </c>
+      <c r="G152" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="H152" s="3">
+        <v>9</v>
+      </c>
+      <c r="I152" s="3">
+        <v>5</v>
+      </c>
+      <c r="J152" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="153" customHeight="1" spans="3:10">
+      <c r="C153" s="1">
+        <v>204</v>
+      </c>
+      <c r="D153" s="3">
+        <v>23405804</v>
+      </c>
+      <c r="E153" s="6">
+        <v>33212</v>
+      </c>
+      <c r="F153" s="6">
+        <v>33012</v>
+      </c>
+      <c r="G153" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="H153" s="3">
+        <v>9</v>
+      </c>
+      <c r="I153" s="3">
+        <v>5</v>
+      </c>
+      <c r="J153" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="154" customHeight="1" spans="3:10">
+      <c r="C154" s="1">
+        <v>205</v>
+      </c>
+      <c r="D154" s="3">
+        <v>23405805</v>
+      </c>
+      <c r="E154" s="6">
+        <v>33312</v>
+      </c>
+      <c r="F154" s="6">
+        <v>33212</v>
+      </c>
+      <c r="G154" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="H154" s="3">
+        <v>9</v>
+      </c>
+      <c r="I154" s="3">
+        <v>5</v>
+      </c>
+      <c r="J154" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="155" customHeight="1" spans="3:10">
+      <c r="C155" s="1">
+        <v>206</v>
+      </c>
+      <c r="D155" s="3">
+        <v>23405807</v>
+      </c>
+      <c r="E155" s="6">
+        <v>33008</v>
+      </c>
+      <c r="F155" s="6">
+        <v>33208</v>
+      </c>
+      <c r="G155" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="H155" s="3">
+        <v>9</v>
+      </c>
+      <c r="I155" s="3">
+        <v>5</v>
+      </c>
+      <c r="J155" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="156" customHeight="1" spans="3:10">
+      <c r="C156" s="1">
+        <v>207</v>
+      </c>
+      <c r="D156" s="3">
+        <v>23405809</v>
+      </c>
+      <c r="E156" s="6">
+        <v>33010</v>
+      </c>
+      <c r="F156" s="6">
+        <v>33010</v>
+      </c>
+      <c r="G156" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="H156" s="3">
+        <v>9</v>
+      </c>
+      <c r="I156" s="3">
+        <v>5</v>
+      </c>
+      <c r="J156" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="157" customHeight="1" spans="3:10">
+      <c r="C157" s="1">
+        <v>208</v>
+      </c>
+      <c r="D157" s="3">
+        <v>23405810</v>
+      </c>
+      <c r="E157" s="6">
+        <v>33010</v>
+      </c>
+      <c r="F157" s="6">
+        <v>33010</v>
+      </c>
+      <c r="G157" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="H157" s="3">
+        <v>9</v>
+      </c>
+      <c r="I157" s="3">
+        <v>5</v>
+      </c>
+      <c r="J157" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:D5" errorStyle="warning">

--- a/Excel/GiftPackEquipConfig.xlsx
+++ b/Excel/GiftPackEquipConfig.xlsx
@@ -1168,7 +1168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:9">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A3" s="2"/>
       <c r="B3" s="4"/>
       <c r="C3" s="5" t="s">
@@ -1193,7 +1193,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:9">
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A4" s="2"/>
       <c r="B4" s="4"/>
       <c r="C4" s="5" t="s">
@@ -1218,7 +1218,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:9">
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A5" s="2"/>
       <c r="B5" s="4"/>
       <c r="C5" s="5" t="s">
@@ -1243,7 +1243,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" customHeight="1" spans="3:10">
+    <row r="6" customHeight="1" spans="1:10">
       <c r="C6" s="1">
         <v>1</v>
       </c>
@@ -1269,7 +1269,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="3:10">
+    <row r="7" customHeight="1" spans="1:10">
       <c r="C7" s="1">
         <v>2</v>
       </c>
@@ -1295,7 +1295,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" customHeight="1" spans="3:10">
+    <row r="8" customHeight="1" spans="1:10">
       <c r="C8" s="1">
         <v>3</v>
       </c>
@@ -1321,7 +1321,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" customHeight="1" spans="3:10">
+    <row r="9" customHeight="1" spans="1:10">
       <c r="C9" s="1">
         <v>4</v>
       </c>
@@ -1347,7 +1347,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" customHeight="1" spans="3:10">
+    <row r="10" customHeight="1" spans="1:10">
       <c r="C10" s="1">
         <v>5</v>
       </c>
@@ -1373,7 +1373,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" customHeight="1" spans="3:10">
+    <row r="11" customHeight="1" spans="1:10">
       <c r="C11" s="1">
         <v>6</v>
       </c>
@@ -1399,7 +1399,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" customHeight="1" spans="3:10">
+    <row r="12" customHeight="1" spans="1:10">
       <c r="C12" s="1">
         <v>7</v>
       </c>
@@ -1425,7 +1425,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" customHeight="1" spans="3:10">
+    <row r="13" customHeight="1" spans="1:10">
       <c r="C13" s="1">
         <v>8</v>
       </c>
@@ -1451,7 +1451,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" customHeight="1" spans="3:10">
+    <row r="14" customHeight="1" spans="1:10">
       <c r="C14" s="1">
         <v>9</v>
       </c>
@@ -1477,7 +1477,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" customHeight="1" spans="3:10">
+    <row r="15" customHeight="1" spans="1:10">
       <c r="C15" s="1">
         <v>10</v>
       </c>
@@ -1503,7 +1503,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" customHeight="1" spans="3:10">
+    <row r="16" customHeight="1" spans="1:10">
       <c r="C16" s="1">
         <v>11</v>
       </c>
@@ -1669,8 +1669,8 @@
       <c r="E22" s="3">
         <v>20</v>
       </c>
-      <c r="F22" s="3">
-        <v>4</v>
+      <c r="F22" s="7">
+        <v>19</v>
       </c>
       <c r="G22" s="9" t="s">
         <v>11</v>
@@ -1695,8 +1695,8 @@
       <c r="E23" s="3">
         <v>20</v>
       </c>
-      <c r="F23" s="3">
-        <v>4</v>
+      <c r="F23" s="7">
+        <v>19</v>
       </c>
       <c r="G23" s="9" t="s">
         <v>11</v>
@@ -1867,7 +1867,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="30" customHeight="1" spans="6:9">
+    <row r="30" customHeight="1" spans="3:10">
       <c r="F30" s="6"/>
       <c r="H30" s="6"/>
       <c r="I30" s="6"/>
@@ -2080,7 +2080,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="39" customHeight="1" spans="4:6">
+    <row r="39" customHeight="1" spans="3:10">
       <c r="D39" s="3"/>
       <c r="E39" s="6"/>
       <c r="F39" s="6"/>
@@ -2293,7 +2293,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="48" customHeight="1" spans="4:6">
+    <row r="48" customHeight="1" spans="3:10">
       <c r="D48" s="3"/>
       <c r="F48" s="6"/>
     </row>
@@ -2765,7 +2765,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="69" customHeight="1" spans="4:6">
+    <row r="69" customHeight="1" spans="3:10">
       <c r="D69" s="3"/>
       <c r="E69" s="6"/>
       <c r="F69" s="6"/>
@@ -2978,7 +2978,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="78" customHeight="1" spans="4:6">
+    <row r="78" customHeight="1" spans="3:10">
       <c r="D78" s="3"/>
       <c r="E78" s="6"/>
       <c r="F78" s="6"/>
@@ -3607,7 +3607,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="104" customHeight="1" spans="4:6">
+    <row r="104" customHeight="1" spans="3:10">
       <c r="D104" s="3"/>
       <c r="E104" s="6"/>
       <c r="F104" s="6"/>
@@ -3820,7 +3820,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="113" customHeight="1" spans="4:6">
+    <row r="113" customHeight="1" spans="3:10">
       <c r="D113" s="3"/>
       <c r="E113" s="6"/>
       <c r="F113" s="6"/>
@@ -4033,7 +4033,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="122" customHeight="1" spans="4:6">
+    <row r="122" customHeight="1" spans="3:10">
       <c r="D122" s="3"/>
       <c r="E122" s="6"/>
       <c r="F122" s="6"/>
@@ -4454,7 +4454,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="140" customHeight="1" spans="4:6">
+    <row r="140" customHeight="1" spans="3:10">
       <c r="D140" s="3"/>
       <c r="E140" s="6"/>
       <c r="F140" s="6"/>
@@ -4667,7 +4667,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="149" customHeight="1" spans="4:6">
+    <row r="149" customHeight="1" spans="3:10">
       <c r="D149" s="3"/>
       <c r="E149" s="6"/>
       <c r="F149" s="6"/>

--- a/Excel/GiftPackEquipConfig.xlsx
+++ b/Excel/GiftPackEquipConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="48">
   <si>
     <t>#</t>
   </si>
@@ -162,6 +162,15 @@
   </si>
   <si>
     <t>道士</t>
+  </si>
+  <si>
+    <t>2001,2001,2004,2004,2004,2010,2010,2013,2013,2003</t>
+  </si>
+  <si>
+    <t>2001,2001,2005,2005,2005,2010,2010,2013,2013,2003</t>
+  </si>
+  <si>
+    <t>2001,2001,2006,2006,2006,2010,2010,2013,2013,2003</t>
   </si>
 </sst>
 </file>
@@ -1140,7 +1149,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J157"/>
+  <dimension ref="A1:J184"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
@@ -2297,7 +2306,7 @@
       <c r="D48" s="3"/>
       <c r="F48" s="6"/>
     </row>
-    <row r="49" customHeight="1" spans="3:10">
+    <row r="49" customHeight="1" spans="1:10">
       <c r="C49" s="1">
         <v>41</v>
       </c>
@@ -2323,7 +2332,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="50" customHeight="1" spans="3:10">
+    <row r="50" customHeight="1" spans="1:10">
       <c r="C50" s="1">
         <v>42</v>
       </c>
@@ -2349,7 +2358,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="51" customHeight="1" spans="3:10">
+    <row r="51" customHeight="1" spans="1:10">
       <c r="C51" s="1">
         <v>43</v>
       </c>
@@ -2375,7 +2384,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="52" customHeight="1" spans="3:10">
+    <row r="52" customHeight="1" spans="1:10">
       <c r="C52" s="1">
         <v>44</v>
       </c>
@@ -2401,7 +2410,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="53" customHeight="1" spans="3:10">
+    <row r="53" customHeight="1" spans="1:10">
       <c r="C53" s="1">
         <v>45</v>
       </c>
@@ -2427,7 +2436,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="54" customHeight="1" spans="3:10">
+    <row r="54" customHeight="1" spans="1:10">
       <c r="C54" s="1">
         <v>46</v>
       </c>
@@ -2453,7 +2462,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="55" customHeight="1" spans="3:10">
+    <row r="55" customHeight="1" spans="1:10">
       <c r="C55" s="1">
         <v>47</v>
       </c>
@@ -2479,7 +2488,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="56" customHeight="1" spans="3:10">
+    <row r="56" customHeight="1" spans="1:10">
       <c r="C56" s="1">
         <v>48</v>
       </c>
@@ -2505,7 +2514,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="57" customHeight="1" spans="3:10">
+    <row r="57" customHeight="1" spans="1:10">
       <c r="C57" s="1">
         <v>49</v>
       </c>
@@ -2531,7 +2540,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="58" customHeight="1" spans="3:10">
+    <row r="58" customHeight="1" spans="1:10">
       <c r="C58" s="1">
         <v>50</v>
       </c>
@@ -2557,7 +2566,13 @@
         <v>22</v>
       </c>
     </row>
-    <row r="61" customHeight="1" spans="3:10">
+    <row r="61" customHeight="1" spans="1:10">
+      <c r="A61" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C61" s="1">
         <v>101</v>
       </c>
@@ -2583,7 +2598,13 @@
         <v>24</v>
       </c>
     </row>
-    <row r="62" customHeight="1" spans="3:10">
+    <row r="62" customHeight="1" spans="1:10">
+      <c r="A62" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C62" s="1">
         <v>102</v>
       </c>
@@ -2609,7 +2630,13 @@
         <v>24</v>
       </c>
     </row>
-    <row r="63" customHeight="1" spans="3:10">
+    <row r="63" customHeight="1" spans="1:10">
+      <c r="A63" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C63" s="1">
         <v>103</v>
       </c>
@@ -2635,7 +2662,13 @@
         <v>24</v>
       </c>
     </row>
-    <row r="64" customHeight="1" spans="3:10">
+    <row r="64" customHeight="1" spans="1:10">
+      <c r="A64" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C64" s="1">
         <v>104</v>
       </c>
@@ -2661,7 +2694,13 @@
         <v>24</v>
       </c>
     </row>
-    <row r="65" customHeight="1" spans="3:10">
+    <row r="65" customHeight="1" spans="1:10">
+      <c r="A65" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C65" s="1">
         <v>105</v>
       </c>
@@ -2687,7 +2726,13 @@
         <v>24</v>
       </c>
     </row>
-    <row r="66" customHeight="1" spans="3:10">
+    <row r="66" customHeight="1" spans="1:10">
+      <c r="A66" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C66" s="1">
         <v>106</v>
       </c>
@@ -2713,7 +2758,13 @@
         <v>24</v>
       </c>
     </row>
-    <row r="67" customHeight="1" spans="3:10">
+    <row r="67" customHeight="1" spans="1:10">
+      <c r="A67" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C67" s="1">
         <v>107</v>
       </c>
@@ -2739,7 +2790,13 @@
         <v>24</v>
       </c>
     </row>
-    <row r="68" customHeight="1" spans="3:10">
+    <row r="68" customHeight="1" spans="1:10">
+      <c r="A68" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C68" s="1">
         <v>108</v>
       </c>
@@ -2765,12 +2822,24 @@
         <v>24</v>
       </c>
     </row>
-    <row r="69" customHeight="1" spans="3:10">
+    <row r="69" customHeight="1" spans="1:10">
+      <c r="A69" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="D69" s="3"/>
       <c r="E69" s="6"/>
       <c r="F69" s="6"/>
     </row>
-    <row r="70" customHeight="1" spans="3:10">
+    <row r="70" customHeight="1" spans="1:10">
+      <c r="A70" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C70" s="1">
         <v>109</v>
       </c>
@@ -2796,7 +2865,13 @@
         <v>26</v>
       </c>
     </row>
-    <row r="71" customHeight="1" spans="3:10">
+    <row r="71" customHeight="1" spans="1:10">
+      <c r="A71" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C71" s="1">
         <v>110</v>
       </c>
@@ -2822,7 +2897,13 @@
         <v>26</v>
       </c>
     </row>
-    <row r="72" customHeight="1" spans="3:10">
+    <row r="72" customHeight="1" spans="1:10">
+      <c r="A72" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C72" s="1">
         <v>111</v>
       </c>
@@ -2848,7 +2929,13 @@
         <v>26</v>
       </c>
     </row>
-    <row r="73" customHeight="1" spans="3:10">
+    <row r="73" customHeight="1" spans="1:10">
+      <c r="A73" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C73" s="1">
         <v>112</v>
       </c>
@@ -2874,7 +2961,13 @@
         <v>26</v>
       </c>
     </row>
-    <row r="74" customHeight="1" spans="3:10">
+    <row r="74" customHeight="1" spans="1:10">
+      <c r="A74" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C74" s="1">
         <v>113</v>
       </c>
@@ -2900,7 +2993,13 @@
         <v>26</v>
       </c>
     </row>
-    <row r="75" customHeight="1" spans="3:10">
+    <row r="75" customHeight="1" spans="1:10">
+      <c r="A75" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C75" s="1">
         <v>114</v>
       </c>
@@ -2926,7 +3025,13 @@
         <v>26</v>
       </c>
     </row>
-    <row r="76" customHeight="1" spans="3:10">
+    <row r="76" customHeight="1" spans="1:10">
+      <c r="A76" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C76" s="1">
         <v>115</v>
       </c>
@@ -2952,7 +3057,13 @@
         <v>26</v>
       </c>
     </row>
-    <row r="77" customHeight="1" spans="3:10">
+    <row r="77" customHeight="1" spans="1:10">
+      <c r="A77" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C77" s="1">
         <v>116</v>
       </c>
@@ -2978,12 +3089,24 @@
         <v>26</v>
       </c>
     </row>
-    <row r="78" customHeight="1" spans="3:10">
+    <row r="78" customHeight="1" spans="1:10">
+      <c r="A78" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="D78" s="3"/>
       <c r="E78" s="6"/>
       <c r="F78" s="6"/>
     </row>
-    <row r="79" customHeight="1" spans="3:10">
+    <row r="79" customHeight="1" spans="1:10">
+      <c r="A79" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C79" s="1">
         <v>117</v>
       </c>
@@ -3009,7 +3132,13 @@
         <v>28</v>
       </c>
     </row>
-    <row r="80" customHeight="1" spans="3:10">
+    <row r="80" customHeight="1" spans="1:10">
+      <c r="A80" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C80" s="1">
         <v>118</v>
       </c>
@@ -3035,7 +3164,13 @@
         <v>28</v>
       </c>
     </row>
-    <row r="81" customHeight="1" spans="3:10">
+    <row r="81" customHeight="1" spans="1:10">
+      <c r="A81" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C81" s="1">
         <v>119</v>
       </c>
@@ -3061,7 +3196,13 @@
         <v>28</v>
       </c>
     </row>
-    <row r="82" customHeight="1" spans="3:10">
+    <row r="82" customHeight="1" spans="1:10">
+      <c r="A82" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C82" s="1">
         <v>120</v>
       </c>
@@ -3087,7 +3228,13 @@
         <v>28</v>
       </c>
     </row>
-    <row r="83" customHeight="1" spans="3:10">
+    <row r="83" customHeight="1" spans="1:10">
+      <c r="A83" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C83" s="1">
         <v>121</v>
       </c>
@@ -3113,7 +3260,13 @@
         <v>28</v>
       </c>
     </row>
-    <row r="84" customHeight="1" spans="3:10">
+    <row r="84" customHeight="1" spans="1:10">
+      <c r="A84" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C84" s="1">
         <v>122</v>
       </c>
@@ -3139,7 +3292,13 @@
         <v>28</v>
       </c>
     </row>
-    <row r="85" customHeight="1" spans="3:10">
+    <row r="85" customHeight="1" spans="1:10">
+      <c r="A85" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C85" s="1">
         <v>123</v>
       </c>
@@ -3165,7 +3324,13 @@
         <v>28</v>
       </c>
     </row>
-    <row r="86" customHeight="1" spans="3:10">
+    <row r="86" customHeight="1" spans="1:10">
+      <c r="A86" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C86" s="1">
         <v>124</v>
       </c>
@@ -3191,7 +3356,21 @@
         <v>28</v>
       </c>
     </row>
-    <row r="88" customHeight="1" spans="3:10">
+    <row r="87" customHeight="1" spans="1:10">
+      <c r="A87" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" customHeight="1" spans="1:10">
+      <c r="A88" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C88" s="1">
         <v>125</v>
       </c>
@@ -3217,7 +3396,13 @@
         <v>30</v>
       </c>
     </row>
-    <row r="89" customHeight="1" spans="3:10">
+    <row r="89" customHeight="1" spans="1:10">
+      <c r="A89" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C89" s="1">
         <v>126</v>
       </c>
@@ -3243,7 +3428,13 @@
         <v>30</v>
       </c>
     </row>
-    <row r="90" customHeight="1" spans="3:10">
+    <row r="90" customHeight="1" spans="1:10">
+      <c r="A90" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C90" s="1">
         <v>127</v>
       </c>
@@ -3269,7 +3460,13 @@
         <v>30</v>
       </c>
     </row>
-    <row r="91" customHeight="1" spans="3:10">
+    <row r="91" customHeight="1" spans="1:10">
+      <c r="A91" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C91" s="1">
         <v>128</v>
       </c>
@@ -3295,7 +3492,13 @@
         <v>30</v>
       </c>
     </row>
-    <row r="92" customHeight="1" spans="3:10">
+    <row r="92" customHeight="1" spans="1:10">
+      <c r="A92" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C92" s="1">
         <v>129</v>
       </c>
@@ -3321,7 +3524,13 @@
         <v>30</v>
       </c>
     </row>
-    <row r="93" customHeight="1" spans="3:10">
+    <row r="93" customHeight="1" spans="1:10">
+      <c r="A93" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C93" s="1">
         <v>130</v>
       </c>
@@ -3347,7 +3556,13 @@
         <v>30</v>
       </c>
     </row>
-    <row r="94" customHeight="1" spans="3:10">
+    <row r="94" customHeight="1" spans="1:10">
+      <c r="A94" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C94" s="1">
         <v>131</v>
       </c>
@@ -3373,7 +3588,13 @@
         <v>30</v>
       </c>
     </row>
-    <row r="95" customHeight="1" spans="3:10">
+    <row r="95" customHeight="1" spans="1:10">
+      <c r="A95" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C95" s="1">
         <v>132</v>
       </c>
@@ -3399,7 +3620,13 @@
         <v>30</v>
       </c>
     </row>
-    <row r="96" customHeight="1" spans="3:10">
+    <row r="96" customHeight="1" spans="1:10">
+      <c r="A96" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C96" s="1">
         <v>133</v>
       </c>
@@ -3425,7 +3652,13 @@
         <v>32</v>
       </c>
     </row>
-    <row r="97" customHeight="1" spans="3:10">
+    <row r="97" customHeight="1" spans="1:10">
+      <c r="A97" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C97" s="1">
         <v>134</v>
       </c>
@@ -3451,7 +3684,13 @@
         <v>32</v>
       </c>
     </row>
-    <row r="98" customHeight="1" spans="3:10">
+    <row r="98" customHeight="1" spans="1:10">
+      <c r="A98" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C98" s="1">
         <v>135</v>
       </c>
@@ -3477,7 +3716,13 @@
         <v>32</v>
       </c>
     </row>
-    <row r="99" customHeight="1" spans="3:10">
+    <row r="99" customHeight="1" spans="1:10">
+      <c r="A99" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C99" s="1">
         <v>136</v>
       </c>
@@ -3503,7 +3748,13 @@
         <v>32</v>
       </c>
     </row>
-    <row r="100" customHeight="1" spans="3:10">
+    <row r="100" customHeight="1" spans="1:10">
+      <c r="A100" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C100" s="1">
         <v>137</v>
       </c>
@@ -3529,7 +3780,13 @@
         <v>32</v>
       </c>
     </row>
-    <row r="101" customHeight="1" spans="3:10">
+    <row r="101" customHeight="1" spans="1:10">
+      <c r="A101" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C101" s="1">
         <v>138</v>
       </c>
@@ -3555,7 +3812,13 @@
         <v>32</v>
       </c>
     </row>
-    <row r="102" customHeight="1" spans="3:10">
+    <row r="102" customHeight="1" spans="1:10">
+      <c r="A102" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C102" s="1">
         <v>139</v>
       </c>
@@ -3581,7 +3844,13 @@
         <v>32</v>
       </c>
     </row>
-    <row r="103" customHeight="1" spans="3:10">
+    <row r="103" customHeight="1" spans="1:10">
+      <c r="A103" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C103" s="1">
         <v>140</v>
       </c>
@@ -3607,12 +3876,24 @@
         <v>32</v>
       </c>
     </row>
-    <row r="104" customHeight="1" spans="3:10">
+    <row r="104" customHeight="1" spans="1:10">
+      <c r="A104" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="D104" s="3"/>
       <c r="E104" s="6"/>
       <c r="F104" s="6"/>
     </row>
-    <row r="105" customHeight="1" spans="3:10">
+    <row r="105" customHeight="1" spans="1:10">
+      <c r="A105" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C105" s="1">
         <v>151</v>
       </c>
@@ -3638,7 +3919,13 @@
         <v>34</v>
       </c>
     </row>
-    <row r="106" customHeight="1" spans="3:10">
+    <row r="106" customHeight="1" spans="1:10">
+      <c r="A106" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C106" s="1">
         <v>152</v>
       </c>
@@ -3664,7 +3951,13 @@
         <v>34</v>
       </c>
     </row>
-    <row r="107" customHeight="1" spans="3:10">
+    <row r="107" customHeight="1" spans="1:10">
+      <c r="A107" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C107" s="1">
         <v>153</v>
       </c>
@@ -3690,7 +3983,13 @@
         <v>34</v>
       </c>
     </row>
-    <row r="108" customHeight="1" spans="3:10">
+    <row r="108" customHeight="1" spans="1:10">
+      <c r="A108" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C108" s="1">
         <v>154</v>
       </c>
@@ -3716,7 +4015,13 @@
         <v>34</v>
       </c>
     </row>
-    <row r="109" customHeight="1" spans="3:10">
+    <row r="109" customHeight="1" spans="1:10">
+      <c r="A109" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C109" s="1">
         <v>155</v>
       </c>
@@ -3742,7 +4047,13 @@
         <v>34</v>
       </c>
     </row>
-    <row r="110" customHeight="1" spans="3:10">
+    <row r="110" customHeight="1" spans="1:10">
+      <c r="A110" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C110" s="1">
         <v>156</v>
       </c>
@@ -3768,7 +4079,13 @@
         <v>34</v>
       </c>
     </row>
-    <row r="111" customHeight="1" spans="3:10">
+    <row r="111" customHeight="1" spans="1:10">
+      <c r="A111" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C111" s="1">
         <v>157</v>
       </c>
@@ -3794,7 +4111,13 @@
         <v>34</v>
       </c>
     </row>
-    <row r="112" customHeight="1" spans="3:10">
+    <row r="112" customHeight="1" spans="1:10">
+      <c r="A112" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C112" s="1">
         <v>158</v>
       </c>
@@ -3820,12 +4143,24 @@
         <v>34</v>
       </c>
     </row>
-    <row r="113" customHeight="1" spans="3:10">
+    <row r="113" customHeight="1" spans="1:10">
+      <c r="A113" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="D113" s="3"/>
       <c r="E113" s="6"/>
       <c r="F113" s="6"/>
     </row>
-    <row r="114" customHeight="1" spans="3:10">
+    <row r="114" customHeight="1" spans="1:10">
+      <c r="A114" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C114" s="1">
         <v>161</v>
       </c>
@@ -3851,7 +4186,13 @@
         <v>36</v>
       </c>
     </row>
-    <row r="115" customHeight="1" spans="3:10">
+    <row r="115" customHeight="1" spans="1:10">
+      <c r="A115" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C115" s="1">
         <v>162</v>
       </c>
@@ -3877,7 +4218,13 @@
         <v>36</v>
       </c>
     </row>
-    <row r="116" customHeight="1" spans="3:10">
+    <row r="116" customHeight="1" spans="1:10">
+      <c r="A116" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C116" s="1">
         <v>163</v>
       </c>
@@ -3903,7 +4250,13 @@
         <v>36</v>
       </c>
     </row>
-    <row r="117" customHeight="1" spans="3:10">
+    <row r="117" customHeight="1" spans="1:10">
+      <c r="A117" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C117" s="1">
         <v>164</v>
       </c>
@@ -3929,7 +4282,13 @@
         <v>36</v>
       </c>
     </row>
-    <row r="118" customHeight="1" spans="3:10">
+    <row r="118" customHeight="1" spans="1:10">
+      <c r="A118" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C118" s="1">
         <v>165</v>
       </c>
@@ -3955,7 +4314,13 @@
         <v>36</v>
       </c>
     </row>
-    <row r="119" customHeight="1" spans="3:10">
+    <row r="119" customHeight="1" spans="1:10">
+      <c r="A119" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C119" s="1">
         <v>166</v>
       </c>
@@ -3981,7 +4346,13 @@
         <v>36</v>
       </c>
     </row>
-    <row r="120" customHeight="1" spans="3:10">
+    <row r="120" customHeight="1" spans="1:10">
+      <c r="A120" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C120" s="1">
         <v>167</v>
       </c>
@@ -4007,7 +4378,13 @@
         <v>36</v>
       </c>
     </row>
-    <row r="121" customHeight="1" spans="3:10">
+    <row r="121" customHeight="1" spans="1:10">
+      <c r="A121" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C121" s="1">
         <v>168</v>
       </c>
@@ -4033,12 +4410,24 @@
         <v>36</v>
       </c>
     </row>
-    <row r="122" customHeight="1" spans="3:10">
+    <row r="122" customHeight="1" spans="1:10">
+      <c r="A122" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="D122" s="3"/>
       <c r="E122" s="6"/>
       <c r="F122" s="6"/>
     </row>
-    <row r="123" customHeight="1" spans="3:10">
+    <row r="123" customHeight="1" spans="1:10">
+      <c r="A123" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B123" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C123" s="1">
         <v>171</v>
       </c>
@@ -4064,7 +4453,13 @@
         <v>38</v>
       </c>
     </row>
-    <row r="124" customHeight="1" spans="3:10">
+    <row r="124" customHeight="1" spans="1:10">
+      <c r="A124" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B124" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C124" s="1">
         <v>172</v>
       </c>
@@ -4090,7 +4485,13 @@
         <v>38</v>
       </c>
     </row>
-    <row r="125" customHeight="1" spans="3:10">
+    <row r="125" customHeight="1" spans="1:10">
+      <c r="A125" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C125" s="1">
         <v>173</v>
       </c>
@@ -4116,7 +4517,13 @@
         <v>38</v>
       </c>
     </row>
-    <row r="126" customHeight="1" spans="3:10">
+    <row r="126" customHeight="1" spans="1:10">
+      <c r="A126" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C126" s="1">
         <v>174</v>
       </c>
@@ -4142,7 +4549,13 @@
         <v>38</v>
       </c>
     </row>
-    <row r="127" customHeight="1" spans="3:10">
+    <row r="127" customHeight="1" spans="1:10">
+      <c r="A127" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B127" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C127" s="1">
         <v>175</v>
       </c>
@@ -4168,7 +4581,13 @@
         <v>38</v>
       </c>
     </row>
-    <row r="128" customHeight="1" spans="3:10">
+    <row r="128" customHeight="1" spans="1:10">
+      <c r="A128" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B128" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C128" s="1">
         <v>176</v>
       </c>
@@ -4194,7 +4613,13 @@
         <v>38</v>
       </c>
     </row>
-    <row r="129" customHeight="1" spans="3:10">
+    <row r="129" customHeight="1" spans="1:10">
+      <c r="A129" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B129" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C129" s="1">
         <v>177</v>
       </c>
@@ -4220,7 +4645,13 @@
         <v>38</v>
       </c>
     </row>
-    <row r="130" customHeight="1" spans="3:10">
+    <row r="130" customHeight="1" spans="1:10">
+      <c r="A130" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B130" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C130" s="1">
         <v>178</v>
       </c>
@@ -4246,7 +4677,21 @@
         <v>38</v>
       </c>
     </row>
-    <row r="132" customHeight="1" spans="3:10">
+    <row r="131" customHeight="1" spans="1:10">
+      <c r="A131" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B131" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" customHeight="1" spans="1:10">
+      <c r="A132" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B132" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C132" s="1">
         <v>181</v>
       </c>
@@ -4272,7 +4717,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="133" customHeight="1" spans="3:10">
+    <row r="133" customHeight="1" spans="1:10">
+      <c r="A133" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B133" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C133" s="1">
         <v>182</v>
       </c>
@@ -4298,7 +4749,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="134" customHeight="1" spans="3:10">
+    <row r="134" customHeight="1" spans="1:10">
+      <c r="A134" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C134" s="1">
         <v>183</v>
       </c>
@@ -4324,7 +4781,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="135" customHeight="1" spans="3:10">
+    <row r="135" customHeight="1" spans="1:10">
+      <c r="A135" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B135" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C135" s="1">
         <v>184</v>
       </c>
@@ -4350,7 +4813,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="136" customHeight="1" spans="3:10">
+    <row r="136" customHeight="1" spans="1:10">
+      <c r="A136" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B136" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C136" s="1">
         <v>185</v>
       </c>
@@ -4376,7 +4845,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="137" customHeight="1" spans="3:10">
+    <row r="137" customHeight="1" spans="1:10">
+      <c r="A137" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B137" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C137" s="1">
         <v>186</v>
       </c>
@@ -4402,7 +4877,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="138" customHeight="1" spans="3:10">
+    <row r="138" customHeight="1" spans="1:10">
+      <c r="A138" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B138" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C138" s="1">
         <v>187</v>
       </c>
@@ -4428,7 +4909,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="139" customHeight="1" spans="3:10">
+    <row r="139" customHeight="1" spans="1:10">
+      <c r="A139" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B139" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C139" s="1">
         <v>188</v>
       </c>
@@ -4454,12 +4941,24 @@
         <v>40</v>
       </c>
     </row>
-    <row r="140" customHeight="1" spans="3:10">
+    <row r="140" customHeight="1" spans="1:10">
+      <c r="A140" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B140" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="D140" s="3"/>
       <c r="E140" s="6"/>
       <c r="F140" s="6"/>
     </row>
-    <row r="141" customHeight="1" spans="3:10">
+    <row r="141" customHeight="1" spans="1:10">
+      <c r="A141" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B141" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C141" s="1">
         <v>191</v>
       </c>
@@ -4485,7 +4984,13 @@
         <v>42</v>
       </c>
     </row>
-    <row r="142" customHeight="1" spans="3:10">
+    <row r="142" customHeight="1" spans="1:10">
+      <c r="A142" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B142" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C142" s="1">
         <v>192</v>
       </c>
@@ -4511,7 +5016,13 @@
         <v>42</v>
       </c>
     </row>
-    <row r="143" customHeight="1" spans="3:10">
+    <row r="143" customHeight="1" spans="1:10">
+      <c r="A143" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B143" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C143" s="1">
         <v>193</v>
       </c>
@@ -4537,7 +5048,13 @@
         <v>42</v>
       </c>
     </row>
-    <row r="144" customHeight="1" spans="3:10">
+    <row r="144" customHeight="1" spans="1:10">
+      <c r="A144" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B144" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C144" s="1">
         <v>194</v>
       </c>
@@ -4563,7 +5080,13 @@
         <v>42</v>
       </c>
     </row>
-    <row r="145" customHeight="1" spans="3:10">
+    <row r="145" customHeight="1" spans="1:10">
+      <c r="A145" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B145" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C145" s="1">
         <v>195</v>
       </c>
@@ -4589,7 +5112,13 @@
         <v>42</v>
       </c>
     </row>
-    <row r="146" customHeight="1" spans="3:10">
+    <row r="146" customHeight="1" spans="1:10">
+      <c r="A146" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B146" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C146" s="1">
         <v>196</v>
       </c>
@@ -4615,7 +5144,13 @@
         <v>42</v>
       </c>
     </row>
-    <row r="147" customHeight="1" spans="3:10">
+    <row r="147" customHeight="1" spans="1:10">
+      <c r="A147" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B147" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C147" s="1">
         <v>197</v>
       </c>
@@ -4641,7 +5176,13 @@
         <v>42</v>
       </c>
     </row>
-    <row r="148" customHeight="1" spans="3:10">
+    <row r="148" customHeight="1" spans="1:10">
+      <c r="A148" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B148" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C148" s="1">
         <v>198</v>
       </c>
@@ -4667,12 +5208,24 @@
         <v>42</v>
       </c>
     </row>
-    <row r="149" customHeight="1" spans="3:10">
+    <row r="149" customHeight="1" spans="1:10">
+      <c r="A149" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B149" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="D149" s="3"/>
       <c r="E149" s="6"/>
       <c r="F149" s="6"/>
     </row>
-    <row r="150" customHeight="1" spans="3:10">
+    <row r="150" customHeight="1" spans="1:10">
+      <c r="A150" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B150" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C150" s="1">
         <v>201</v>
       </c>
@@ -4698,7 +5251,13 @@
         <v>44</v>
       </c>
     </row>
-    <row r="151" customHeight="1" spans="3:10">
+    <row r="151" customHeight="1" spans="1:10">
+      <c r="A151" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B151" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C151" s="1">
         <v>202</v>
       </c>
@@ -4724,7 +5283,13 @@
         <v>44</v>
       </c>
     </row>
-    <row r="152" customHeight="1" spans="3:10">
+    <row r="152" customHeight="1" spans="1:10">
+      <c r="A152" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B152" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C152" s="1">
         <v>203</v>
       </c>
@@ -4750,7 +5315,13 @@
         <v>44</v>
       </c>
     </row>
-    <row r="153" customHeight="1" spans="3:10">
+    <row r="153" customHeight="1" spans="1:10">
+      <c r="A153" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B153" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C153" s="1">
         <v>204</v>
       </c>
@@ -4776,7 +5347,13 @@
         <v>44</v>
       </c>
     </row>
-    <row r="154" customHeight="1" spans="3:10">
+    <row r="154" customHeight="1" spans="1:10">
+      <c r="A154" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B154" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C154" s="1">
         <v>205</v>
       </c>
@@ -4802,7 +5379,13 @@
         <v>44</v>
       </c>
     </row>
-    <row r="155" customHeight="1" spans="3:10">
+    <row r="155" customHeight="1" spans="1:10">
+      <c r="A155" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B155" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C155" s="1">
         <v>206</v>
       </c>
@@ -4828,7 +5411,13 @@
         <v>44</v>
       </c>
     </row>
-    <row r="156" customHeight="1" spans="3:10">
+    <row r="156" customHeight="1" spans="1:10">
+      <c r="A156" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B156" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C156" s="1">
         <v>207</v>
       </c>
@@ -4854,7 +5443,13 @@
         <v>44</v>
       </c>
     </row>
-    <row r="157" customHeight="1" spans="3:10">
+    <row r="157" customHeight="1" spans="1:10">
+      <c r="A157" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B157" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C157" s="1">
         <v>208</v>
       </c>
@@ -4877,6 +5472,640 @@
         <v>5</v>
       </c>
       <c r="J157" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="159" customHeight="1" spans="1:10">
+      <c r="C159" s="1">
+        <v>211</v>
+      </c>
+      <c r="D159" s="3">
+        <v>21505801</v>
+      </c>
+      <c r="E159" s="6">
+        <v>41002</v>
+      </c>
+      <c r="F159" s="6">
+        <v>41002</v>
+      </c>
+      <c r="G159" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="H159" s="3">
+        <v>9</v>
+      </c>
+      <c r="I159" s="3">
+        <v>5</v>
+      </c>
+      <c r="J159" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="160" customHeight="1" spans="1:10">
+      <c r="C160" s="1">
+        <v>212</v>
+      </c>
+      <c r="D160" s="3">
+        <v>21505802</v>
+      </c>
+      <c r="E160" s="6">
+        <v>41002</v>
+      </c>
+      <c r="F160" s="6">
+        <v>41002</v>
+      </c>
+      <c r="G160" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="H160" s="3">
+        <v>9</v>
+      </c>
+      <c r="I160" s="3">
+        <v>5</v>
+      </c>
+      <c r="J160" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="161" customHeight="1" spans="3:10">
+      <c r="C161" s="1">
+        <v>213</v>
+      </c>
+      <c r="D161" s="3">
+        <v>21505803</v>
+      </c>
+      <c r="E161" s="6">
+        <v>41008</v>
+      </c>
+      <c r="F161" s="6">
+        <v>41008</v>
+      </c>
+      <c r="G161" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="H161" s="3">
+        <v>9</v>
+      </c>
+      <c r="I161" s="3">
+        <v>5</v>
+      </c>
+      <c r="J161" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="162" customHeight="1" spans="3:10">
+      <c r="C162" s="1">
+        <v>214</v>
+      </c>
+      <c r="D162" s="3">
+        <v>21505804</v>
+      </c>
+      <c r="E162" s="6">
+        <v>41008</v>
+      </c>
+      <c r="F162" s="6">
+        <v>41008</v>
+      </c>
+      <c r="G162" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="H162" s="3">
+        <v>9</v>
+      </c>
+      <c r="I162" s="3">
+        <v>5</v>
+      </c>
+      <c r="J162" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="163" customHeight="1" spans="3:10">
+      <c r="C163" s="1">
+        <v>215</v>
+      </c>
+      <c r="D163" s="3">
+        <v>21505805</v>
+      </c>
+      <c r="E163" s="6">
+        <v>41010</v>
+      </c>
+      <c r="F163" s="6">
+        <v>41010</v>
+      </c>
+      <c r="G163" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="H163" s="3">
+        <v>9</v>
+      </c>
+      <c r="I163" s="3">
+        <v>5</v>
+      </c>
+      <c r="J163" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="164" customHeight="1" spans="3:10">
+      <c r="C164" s="1">
+        <v>216</v>
+      </c>
+      <c r="D164" s="3">
+        <v>21505807</v>
+      </c>
+      <c r="E164" s="6">
+        <v>41011</v>
+      </c>
+      <c r="F164" s="6">
+        <v>41011</v>
+      </c>
+      <c r="G164" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="H164" s="3">
+        <v>9</v>
+      </c>
+      <c r="I164" s="3">
+        <v>5</v>
+      </c>
+      <c r="J164" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="165" customHeight="1" spans="3:10">
+      <c r="C165" s="1">
+        <v>217</v>
+      </c>
+      <c r="D165" s="3">
+        <v>21505809</v>
+      </c>
+      <c r="E165" s="6">
+        <v>41012</v>
+      </c>
+      <c r="F165" s="6">
+        <v>41012</v>
+      </c>
+      <c r="G165" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="H165" s="3">
+        <v>9</v>
+      </c>
+      <c r="I165" s="3">
+        <v>5</v>
+      </c>
+      <c r="J165" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="166" customHeight="1" spans="3:10">
+      <c r="C166" s="1">
+        <v>218</v>
+      </c>
+      <c r="D166" s="3">
+        <v>21505810</v>
+      </c>
+      <c r="E166" s="6">
+        <v>41012</v>
+      </c>
+      <c r="F166" s="6">
+        <v>41012</v>
+      </c>
+      <c r="G166" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="H166" s="3">
+        <v>9</v>
+      </c>
+      <c r="I166" s="3">
+        <v>5</v>
+      </c>
+      <c r="J166" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="167" customHeight="1" spans="3:10">
+      <c r="D167" s="3"/>
+      <c r="E167" s="6"/>
+      <c r="F167" s="6"/>
+    </row>
+    <row r="168" customHeight="1" spans="3:10">
+      <c r="C168" s="1">
+        <v>221</v>
+      </c>
+      <c r="D168" s="3">
+        <v>22505801</v>
+      </c>
+      <c r="E168" s="6">
+        <v>42002</v>
+      </c>
+      <c r="F168" s="6">
+        <v>42002</v>
+      </c>
+      <c r="G168" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="H168" s="3">
+        <v>9</v>
+      </c>
+      <c r="I168" s="3">
+        <v>5</v>
+      </c>
+      <c r="J168" s="8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="169" customHeight="1" spans="3:10">
+      <c r="C169" s="1">
+        <v>222</v>
+      </c>
+      <c r="D169" s="3">
+        <v>22505802</v>
+      </c>
+      <c r="E169" s="6">
+        <v>42002</v>
+      </c>
+      <c r="F169" s="6">
+        <v>42002</v>
+      </c>
+      <c r="G169" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="H169" s="3">
+        <v>9</v>
+      </c>
+      <c r="I169" s="3">
+        <v>5</v>
+      </c>
+      <c r="J169" s="8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="170" customHeight="1" spans="3:10">
+      <c r="C170" s="1">
+        <v>223</v>
+      </c>
+      <c r="D170" s="3">
+        <v>22505803</v>
+      </c>
+      <c r="E170" s="6">
+        <v>42008</v>
+      </c>
+      <c r="F170" s="6">
+        <v>42008</v>
+      </c>
+      <c r="G170" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="H170" s="3">
+        <v>9</v>
+      </c>
+      <c r="I170" s="3">
+        <v>5</v>
+      </c>
+      <c r="J170" s="8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="171" customHeight="1" spans="3:10">
+      <c r="C171" s="1">
+        <v>224</v>
+      </c>
+      <c r="D171" s="3">
+        <v>22505804</v>
+      </c>
+      <c r="E171" s="6">
+        <v>42008</v>
+      </c>
+      <c r="F171" s="6">
+        <v>42008</v>
+      </c>
+      <c r="G171" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="H171" s="3">
+        <v>9</v>
+      </c>
+      <c r="I171" s="3">
+        <v>5</v>
+      </c>
+      <c r="J171" s="8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="172" customHeight="1" spans="3:10">
+      <c r="C172" s="1">
+        <v>225</v>
+      </c>
+      <c r="D172" s="3">
+        <v>22505805</v>
+      </c>
+      <c r="E172" s="6">
+        <v>42010</v>
+      </c>
+      <c r="F172" s="6">
+        <v>42010</v>
+      </c>
+      <c r="G172" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="H172" s="3">
+        <v>9</v>
+      </c>
+      <c r="I172" s="3">
+        <v>5</v>
+      </c>
+      <c r="J172" s="8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="173" customHeight="1" spans="3:10">
+      <c r="C173" s="1">
+        <v>226</v>
+      </c>
+      <c r="D173" s="3">
+        <v>22505807</v>
+      </c>
+      <c r="E173" s="6">
+        <v>42011</v>
+      </c>
+      <c r="F173" s="6">
+        <v>42011</v>
+      </c>
+      <c r="G173" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="H173" s="3">
+        <v>9</v>
+      </c>
+      <c r="I173" s="3">
+        <v>5</v>
+      </c>
+      <c r="J173" s="8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="174" customHeight="1" spans="3:10">
+      <c r="C174" s="1">
+        <v>227</v>
+      </c>
+      <c r="D174" s="3">
+        <v>22505809</v>
+      </c>
+      <c r="E174" s="6">
+        <v>42012</v>
+      </c>
+      <c r="F174" s="6">
+        <v>42012</v>
+      </c>
+      <c r="G174" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="H174" s="3">
+        <v>9</v>
+      </c>
+      <c r="I174" s="3">
+        <v>5</v>
+      </c>
+      <c r="J174" s="8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="175" customHeight="1" spans="3:10">
+      <c r="C175" s="1">
+        <v>228</v>
+      </c>
+      <c r="D175" s="3">
+        <v>22505810</v>
+      </c>
+      <c r="E175" s="6">
+        <v>42012</v>
+      </c>
+      <c r="F175" s="6">
+        <v>42012</v>
+      </c>
+      <c r="G175" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="H175" s="3">
+        <v>9</v>
+      </c>
+      <c r="I175" s="3">
+        <v>5</v>
+      </c>
+      <c r="J175" s="8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="176" customHeight="1" spans="3:10">
+      <c r="D176" s="3"/>
+      <c r="E176" s="6"/>
+      <c r="F176" s="6"/>
+    </row>
+    <row r="177" customHeight="1" spans="3:10">
+      <c r="C177" s="1">
+        <v>231</v>
+      </c>
+      <c r="D177" s="3">
+        <v>23505801</v>
+      </c>
+      <c r="E177" s="6">
+        <v>43002</v>
+      </c>
+      <c r="F177" s="6">
+        <v>43002</v>
+      </c>
+      <c r="G177" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H177" s="3">
+        <v>9</v>
+      </c>
+      <c r="I177" s="3">
+        <v>5</v>
+      </c>
+      <c r="J177" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="178" customHeight="1" spans="3:10">
+      <c r="C178" s="1">
+        <v>232</v>
+      </c>
+      <c r="D178" s="3">
+        <v>23505802</v>
+      </c>
+      <c r="E178" s="6">
+        <v>43002</v>
+      </c>
+      <c r="F178" s="6">
+        <v>43002</v>
+      </c>
+      <c r="G178" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H178" s="3">
+        <v>9</v>
+      </c>
+      <c r="I178" s="3">
+        <v>5</v>
+      </c>
+      <c r="J178" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="179" customHeight="1" spans="3:10">
+      <c r="C179" s="1">
+        <v>233</v>
+      </c>
+      <c r="D179" s="3">
+        <v>23505803</v>
+      </c>
+      <c r="E179" s="6">
+        <v>43008</v>
+      </c>
+      <c r="F179" s="6">
+        <v>43008</v>
+      </c>
+      <c r="G179" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H179" s="3">
+        <v>9</v>
+      </c>
+      <c r="I179" s="3">
+        <v>5</v>
+      </c>
+      <c r="J179" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="180" customHeight="1" spans="3:10">
+      <c r="C180" s="1">
+        <v>234</v>
+      </c>
+      <c r="D180" s="3">
+        <v>23505804</v>
+      </c>
+      <c r="E180" s="6">
+        <v>43008</v>
+      </c>
+      <c r="F180" s="6">
+        <v>43008</v>
+      </c>
+      <c r="G180" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H180" s="3">
+        <v>9</v>
+      </c>
+      <c r="I180" s="3">
+        <v>5</v>
+      </c>
+      <c r="J180" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="181" customHeight="1" spans="3:10">
+      <c r="C181" s="1">
+        <v>235</v>
+      </c>
+      <c r="D181" s="3">
+        <v>23505805</v>
+      </c>
+      <c r="E181" s="6">
+        <v>43010</v>
+      </c>
+      <c r="F181" s="6">
+        <v>43010</v>
+      </c>
+      <c r="G181" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H181" s="3">
+        <v>9</v>
+      </c>
+      <c r="I181" s="3">
+        <v>5</v>
+      </c>
+      <c r="J181" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="182" customHeight="1" spans="3:10">
+      <c r="C182" s="1">
+        <v>236</v>
+      </c>
+      <c r="D182" s="3">
+        <v>23505807</v>
+      </c>
+      <c r="E182" s="6">
+        <v>43011</v>
+      </c>
+      <c r="F182" s="6">
+        <v>43011</v>
+      </c>
+      <c r="G182" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H182" s="3">
+        <v>9</v>
+      </c>
+      <c r="I182" s="3">
+        <v>5</v>
+      </c>
+      <c r="J182" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="183" customHeight="1" spans="3:10">
+      <c r="C183" s="1">
+        <v>237</v>
+      </c>
+      <c r="D183" s="3">
+        <v>23505809</v>
+      </c>
+      <c r="E183" s="6">
+        <v>43012</v>
+      </c>
+      <c r="F183" s="6">
+        <v>43012</v>
+      </c>
+      <c r="G183" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H183" s="3">
+        <v>9</v>
+      </c>
+      <c r="I183" s="3">
+        <v>5</v>
+      </c>
+      <c r="J183" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="184" customHeight="1" spans="3:10">
+      <c r="C184" s="1">
+        <v>238</v>
+      </c>
+      <c r="D184" s="3">
+        <v>23505810</v>
+      </c>
+      <c r="E184" s="6">
+        <v>43012</v>
+      </c>
+      <c r="F184" s="6">
+        <v>43012</v>
+      </c>
+      <c r="G184" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H184" s="3">
+        <v>9</v>
+      </c>
+      <c r="I184" s="3">
+        <v>5</v>
+      </c>
+      <c r="J184" s="8" t="s">
         <v>44</v>
       </c>
     </row>

--- a/Excel/GiftPackEquipConfig.xlsx
+++ b/Excel/GiftPackEquipConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="595" uniqueCount="48">
   <si>
     <t>#</t>
   </si>
@@ -5475,7 +5475,21 @@
         <v>44</v>
       </c>
     </row>
+    <row r="158" customHeight="1" spans="1:10">
+      <c r="A158" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B158" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
     <row r="159" customHeight="1" spans="1:10">
+      <c r="A159" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B159" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C159" s="1">
         <v>211</v>
       </c>
@@ -5492,16 +5506,22 @@
         <v>45</v>
       </c>
       <c r="H159" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I159" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J159" s="8" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="160" customHeight="1" spans="1:10">
+      <c r="A160" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B160" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C160" s="1">
         <v>212</v>
       </c>
@@ -5518,16 +5538,22 @@
         <v>45</v>
       </c>
       <c r="H160" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I160" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J160" s="8" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="161" customHeight="1" spans="3:10">
+    <row r="161" customHeight="1" spans="1:10">
+      <c r="A161" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B161" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C161" s="1">
         <v>213</v>
       </c>
@@ -5544,16 +5570,22 @@
         <v>45</v>
       </c>
       <c r="H161" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I161" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J161" s="8" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="162" customHeight="1" spans="3:10">
+    <row r="162" customHeight="1" spans="1:10">
+      <c r="A162" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B162" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C162" s="1">
         <v>214</v>
       </c>
@@ -5570,16 +5602,22 @@
         <v>45</v>
       </c>
       <c r="H162" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I162" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J162" s="8" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="163" customHeight="1" spans="3:10">
+    <row r="163" customHeight="1" spans="1:10">
+      <c r="A163" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B163" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C163" s="1">
         <v>215</v>
       </c>
@@ -5596,16 +5634,22 @@
         <v>45</v>
       </c>
       <c r="H163" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I163" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J163" s="8" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="164" customHeight="1" spans="3:10">
+    <row r="164" customHeight="1" spans="1:10">
+      <c r="A164" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B164" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C164" s="1">
         <v>216</v>
       </c>
@@ -5622,16 +5666,22 @@
         <v>45</v>
       </c>
       <c r="H164" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I164" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J164" s="8" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="165" customHeight="1" spans="3:10">
+    <row r="165" customHeight="1" spans="1:10">
+      <c r="A165" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B165" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C165" s="1">
         <v>217</v>
       </c>
@@ -5648,16 +5698,22 @@
         <v>45</v>
       </c>
       <c r="H165" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I165" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J165" s="8" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="166" customHeight="1" spans="3:10">
+    <row r="166" customHeight="1" spans="1:10">
+      <c r="A166" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B166" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C166" s="1">
         <v>218</v>
       </c>
@@ -5674,21 +5730,33 @@
         <v>45</v>
       </c>
       <c r="H166" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I166" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J166" s="8" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="167" customHeight="1" spans="3:10">
+    <row r="167" customHeight="1" spans="1:10">
+      <c r="A167" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B167" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="D167" s="3"/>
       <c r="E167" s="6"/>
       <c r="F167" s="6"/>
     </row>
-    <row r="168" customHeight="1" spans="3:10">
+    <row r="168" customHeight="1" spans="1:10">
+      <c r="A168" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B168" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C168" s="1">
         <v>221</v>
       </c>
@@ -5705,16 +5773,22 @@
         <v>46</v>
       </c>
       <c r="H168" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I168" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J168" s="8" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="169" customHeight="1" spans="3:10">
+    <row r="169" customHeight="1" spans="1:10">
+      <c r="A169" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B169" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C169" s="1">
         <v>222</v>
       </c>
@@ -5731,16 +5805,22 @@
         <v>46</v>
       </c>
       <c r="H169" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I169" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J169" s="8" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="170" customHeight="1" spans="3:10">
+    <row r="170" customHeight="1" spans="1:10">
+      <c r="A170" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B170" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C170" s="1">
         <v>223</v>
       </c>
@@ -5757,16 +5837,22 @@
         <v>46</v>
       </c>
       <c r="H170" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I170" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J170" s="8" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="171" customHeight="1" spans="3:10">
+    <row r="171" customHeight="1" spans="1:10">
+      <c r="A171" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B171" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C171" s="1">
         <v>224</v>
       </c>
@@ -5783,16 +5869,22 @@
         <v>46</v>
       </c>
       <c r="H171" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I171" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J171" s="8" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="172" customHeight="1" spans="3:10">
+    <row r="172" customHeight="1" spans="1:10">
+      <c r="A172" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B172" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C172" s="1">
         <v>225</v>
       </c>
@@ -5809,16 +5901,22 @@
         <v>46</v>
       </c>
       <c r="H172" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I172" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J172" s="8" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="173" customHeight="1" spans="3:10">
+    <row r="173" customHeight="1" spans="1:10">
+      <c r="A173" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B173" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C173" s="1">
         <v>226</v>
       </c>
@@ -5835,16 +5933,22 @@
         <v>46</v>
       </c>
       <c r="H173" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I173" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J173" s="8" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="174" customHeight="1" spans="3:10">
+    <row r="174" customHeight="1" spans="1:10">
+      <c r="A174" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B174" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C174" s="1">
         <v>227</v>
       </c>
@@ -5861,16 +5965,22 @@
         <v>46</v>
       </c>
       <c r="H174" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I174" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J174" s="8" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="175" customHeight="1" spans="3:10">
+    <row r="175" customHeight="1" spans="1:10">
+      <c r="A175" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B175" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C175" s="1">
         <v>228</v>
       </c>
@@ -5887,21 +5997,33 @@
         <v>46</v>
       </c>
       <c r="H175" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I175" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J175" s="8" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="176" customHeight="1" spans="3:10">
+    <row r="176" customHeight="1" spans="1:10">
+      <c r="A176" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B176" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="D176" s="3"/>
       <c r="E176" s="6"/>
       <c r="F176" s="6"/>
     </row>
-    <row r="177" customHeight="1" spans="3:10">
+    <row r="177" customHeight="1" spans="1:10">
+      <c r="A177" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B177" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C177" s="1">
         <v>231</v>
       </c>
@@ -5918,16 +6040,22 @@
         <v>47</v>
       </c>
       <c r="H177" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I177" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J177" s="8" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="178" customHeight="1" spans="3:10">
+    <row r="178" customHeight="1" spans="1:10">
+      <c r="A178" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B178" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C178" s="1">
         <v>232</v>
       </c>
@@ -5944,16 +6072,22 @@
         <v>47</v>
       </c>
       <c r="H178" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I178" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J178" s="8" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="179" customHeight="1" spans="3:10">
+    <row r="179" customHeight="1" spans="1:10">
+      <c r="A179" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B179" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C179" s="1">
         <v>233</v>
       </c>
@@ -5970,16 +6104,22 @@
         <v>47</v>
       </c>
       <c r="H179" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I179" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J179" s="8" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="180" customHeight="1" spans="3:10">
+    <row r="180" customHeight="1" spans="1:10">
+      <c r="A180" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B180" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C180" s="1">
         <v>234</v>
       </c>
@@ -5996,16 +6136,22 @@
         <v>47</v>
       </c>
       <c r="H180" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I180" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J180" s="8" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="181" customHeight="1" spans="3:10">
+    <row r="181" customHeight="1" spans="1:10">
+      <c r="A181" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B181" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C181" s="1">
         <v>235</v>
       </c>
@@ -6022,16 +6168,22 @@
         <v>47</v>
       </c>
       <c r="H181" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I181" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J181" s="8" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="182" customHeight="1" spans="3:10">
+    <row r="182" customHeight="1" spans="1:10">
+      <c r="A182" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B182" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C182" s="1">
         <v>236</v>
       </c>
@@ -6048,16 +6200,22 @@
         <v>47</v>
       </c>
       <c r="H182" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I182" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J182" s="8" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="183" customHeight="1" spans="3:10">
+    <row r="183" customHeight="1" spans="1:10">
+      <c r="A183" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B183" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C183" s="1">
         <v>237</v>
       </c>
@@ -6074,16 +6232,22 @@
         <v>47</v>
       </c>
       <c r="H183" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I183" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J183" s="8" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="184" customHeight="1" spans="3:10">
+    <row r="184" customHeight="1" spans="1:10">
+      <c r="A184" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B184" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C184" s="1">
         <v>238</v>
       </c>
@@ -6100,10 +6264,10 @@
         <v>47</v>
       </c>
       <c r="H184" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I184" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J184" s="8" t="s">
         <v>44</v>
